--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2383127-1E85-4EB9-9D36-2C234CE24080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{88AD3E2F-0436-436F-B553-A876EE2C867F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15345" xr2:uid="{48EB2D4E-0788-457A-B513-B740CD2D51CD}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15345" xr2:uid="{84E6ECBD-1B40-4FCE-9372-AB89EC33E6D2}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">올라프!$A$1:$T$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">유진!$A$1:$M$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'유진 무기'!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">적!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">적!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">히후미!$A$1:$T$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="715">
   <si>
     <t>Project Abyss — 캐릭터 스킬 스펙 (2026-09-13)</t>
   </si>
@@ -948,10 +948,10 @@
     <t>준비 행동</t>
   </si>
   <si>
-    <t>무기 교체 — 효과는 다음 턴부터</t>
-  </si>
-  <si>
-    <t>도사림 한 칸에 환형(공격) 또는 환형(수비) 하나만 장착</t>
+    <t>무기 교체 — 안 든 무기 2개 중 하나를 고른다(선택 UI). 교체는 다음 턴부터, 카드 보너스는 쓴 그 턴 즉시</t>
+  </si>
+  <si>
+    <t>환형(공격) 또는 환형(수비) 하나만 장착 · 다리 · 머리 어느 도사림 칸에서든 사용</t>
   </si>
   <si>
     <t>재굴림 축</t>
@@ -1164,7 +1164,7 @@
     <t>환형(공격)</t>
   </si>
   <si>
-    <t>무기 교체 + 그 턴 위력 +2 (교체 전 무기 기준)</t>
+    <t>무기 교체(다음 턴) + 그 턴 위력 +2 (교체 전 무기 기준)</t>
   </si>
   <si>
     <t>… +4</t>
@@ -1179,7 +1179,7 @@
     <t>환형(수비)</t>
   </si>
   <si>
-    <t>무기 교체 + 방어도 +30</t>
+    <t>무기 교체(다음 턴) + 그 턴 방어도 +30</t>
   </si>
   <si>
     <t>환형(공격)과 택1 장착</t>
@@ -1572,7 +1572,7 @@
     <t>힘</t>
   </si>
   <si>
-    <t>크기형 (그 턴)</t>
+    <t>크기형 (한 턴 · 이번 턴 / 다음 턴)</t>
   </si>
   <si>
     <t>굴림 위력 +N (범위 전체 이동)</t>
@@ -1623,19 +1623,25 @@
     <t>열기</t>
   </si>
   <si>
-    <t>턴당 위세 게이지 +N</t>
-  </si>
-  <si>
-    <t>+3/턴 권장</t>
+    <t>그 턴 위세 게이지 +N</t>
+  </si>
+  <si>
+    <t>이번 턴이면 즉시 · 다음 턴이면 다음 턴 시작에 지급</t>
+  </si>
+  <si>
+    <t>+3 권장</t>
   </si>
   <si>
     <t>신속</t>
   </si>
   <si>
+    <t>크기형 (한 턴 · 다음 턴으로만)</t>
+  </si>
+  <si>
     <t>속도 최댓값 +N</t>
   </si>
   <si>
-    <t>다음 턴부터 (속도는 턴 시작에 굴림)</t>
+    <t>다음 턴 속도 굴림 (속도는 턴 시작에 굴림)</t>
   </si>
   <si>
     <t>견고</t>
@@ -2148,7 +2154,7 @@
     <t>개체 체력 135 (3마리) / 101 (4마리) · 흐트러짐 100 · 부위 없음</t>
   </si>
   <si>
-    <t>소스 균등 1~8 · 발악 · 파괴 스킬 없음 ⚠</t>
+    <t>소스 균등 1~8 · 발악 없음 · 파괴 스킬은 일부 잡몹만</t>
   </si>
   <si>
     <t>적 공통</t>
@@ -2178,6 +2184,18 @@
     <t>부위 파괴 시 슬롯 감소</t>
   </si>
   <si>
+    <t>엘리트 · 보스</t>
+  </si>
+  <si>
+    <t>부위 구성</t>
+  </si>
+  <si>
+    <t>부위 5개 기준 · 부위마다 이름 · 슬롯 역할(공격 / 도사림 / 겸용) · 약화 · 파괴 디버프를 적 데이터로 정의</t>
+  </si>
+  <si>
+    <t>플레이어 4부위 규칙과 별개</t>
+  </si>
+  <si>
     <t>1스테이지 보스</t>
   </si>
   <si>
@@ -2202,7 +2220,7 @@
     <t>구성</t>
   </si>
   <si>
-    <t>보통 자세 배열 A · A · B (순환) · 조준 랜덤 · 파괴 권한 보유 · 부위 150 × 5 · 전체 1,500 · 흐트러짐 400 · 빛 2</t>
+    <t>보통 자세 배열 A · A · B (순환) · 조준 랜덤 · 파괴 스킬 별도 신설(미정) — A · B는 파괴 권한 없음 · 부위 150 × 5 · 전체 1,500 · 흐트러짐 400 · 빛 2</t>
   </si>
   <si>
     <t>⚠ 체력 임시</t>
@@ -2699,7 +2717,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFA524E1-3C51-472F-9509-7FD96EDAFD3F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72B2AD45-C2D6-4131-BB8E-1894C2C8643C}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2889,7 +2907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C399BB2B-598D-49E4-A955-ED47B1D36571}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74E31B30-B573-44D3-83F6-35C430654F0A}">
   <dimension ref="A1:T52"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6134,14 +6152,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T52" xr:uid="{C399BB2B-598D-49E4-A955-ED47B1D36571}"/>
+  <autoFilter ref="A1:T52" xr:uid="{74E31B30-B573-44D3-83F6-35C430654F0A}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74124F49-7C6E-4FC5-A412-8075DE6D5DD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{131B2685-3F1C-4277-8602-2D3A83F2E707}">
   <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7429,14 +7447,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M31" xr:uid="{74124F49-7C6E-4FC5-A412-8075DE6D5DD8}"/>
+  <autoFilter ref="A1:M31" xr:uid="{131B2685-3F1C-4277-8602-2D3A83F2E707}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ED55255-A0D6-48B7-BB36-B73E0716C7ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F531735-5DA1-4C0A-A46F-D2ADD03B29AE}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7629,14 +7647,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4" xr:uid="{0ED55255-A0D6-48B7-BB36-B73E0716C7ED}"/>
+  <autoFilter ref="A1:N4" xr:uid="{9F531735-5DA1-4C0A-A46F-D2ADD03B29AE}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A12D0FD-877D-41A6-AA5F-3E95DDDE53C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{440416D5-DF77-4C2E-87B9-B8BD639BA288}">
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8898,14 +8916,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T20" xr:uid="{5A12D0FD-877D-41A6-AA5F-3E95DDDE53C9}"/>
+  <autoFilter ref="A1:T20" xr:uid="{440416D5-DF77-4C2E-87B9-B8BD639BA288}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AB2CA46-CC37-4A8E-A552-3EC9B4C988BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81156B09-B873-4EA4-84A2-912C0ABCD832}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9070,139 +9088,139 @@
         <v>514</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>531</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>533</v>
+      <c r="F12" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>535</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12" xr:uid="{9AB2CA46-CC37-4A8E-A552-3EC9B4C988BC}"/>
+  <autoFilter ref="A1:G12" xr:uid="{81156B09-B873-4EA4-84A2-912C0ABCD832}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08077B1F-C8F3-4FF4-8D9E-441FB5D374EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D73AB6-60D4-4CBE-BCDD-98EDFAF17F81}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9216,19 +9234,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>40</v>
@@ -9239,22 +9257,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>49</v>
@@ -9262,22 +9280,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>49</v>
@@ -9285,22 +9303,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>49</v>
@@ -9308,22 +9326,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>96</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>49</v>
@@ -9331,22 +9349,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>49</v>
@@ -9354,22 +9372,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>49</v>
@@ -9377,22 +9395,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>49</v>
@@ -9400,22 +9418,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>49</v>
@@ -9423,22 +9441,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>49</v>
@@ -9446,13 +9464,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>97</v>
@@ -9461,7 +9479,7 @@
         <v>174</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>49</v>
@@ -9469,22 +9487,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>97</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>49</v>
@@ -9492,22 +9510,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>97</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>49</v>
@@ -9515,22 +9533,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>96</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>49</v>
@@ -9538,22 +9556,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>96</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>49</v>
@@ -9561,22 +9579,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>96</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>49</v>
@@ -9584,45 +9602,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>49</v>
@@ -9630,22 +9648,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>49</v>
@@ -9653,22 +9671,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>49</v>
@@ -9676,22 +9694,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>49</v>
@@ -9699,22 +9717,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>49</v>
@@ -9722,22 +9740,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>96</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>49</v>
@@ -9745,22 +9763,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>96</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>49</v>
@@ -9768,22 +9786,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>96</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>49</v>
@@ -9791,22 +9809,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>49</v>
@@ -9814,22 +9832,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>49</v>
@@ -9837,183 +9855,183 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>97</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>97</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="F30" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>607</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>97</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>96</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>96</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>96</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>49</v>
@@ -10021,68 +10039,68 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>49</v>
@@ -10090,22 +10108,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>49</v>
@@ -10113,22 +10131,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>49</v>
@@ -10136,22 +10154,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>96</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>49</v>
@@ -10159,22 +10177,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>96</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>49</v>
@@ -10182,22 +10200,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>96</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>49</v>
@@ -10205,45 +10223,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>49</v>
@@ -10251,22 +10269,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>49</v>
@@ -10274,10 +10292,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>265</v>
@@ -10286,10 +10304,10 @@
         <v>97</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>49</v>
@@ -10297,10 +10315,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>265</v>
@@ -10309,10 +10327,10 @@
         <v>97</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>49</v>
@@ -10320,10 +10338,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>265</v>
@@ -10332,10 +10350,10 @@
         <v>97</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>49</v>
@@ -10343,10 +10361,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>265</v>
@@ -10358,7 +10376,7 @@
         <v>511</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>49</v>
@@ -10366,10 +10384,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>265</v>
@@ -10378,10 +10396,10 @@
         <v>96</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>49</v>
@@ -10389,10 +10407,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>265</v>
@@ -10401,10 +10419,10 @@
         <v>96</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>49</v>
@@ -10412,10 +10430,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>265</v>
@@ -10424,10 +10442,10 @@
         <v>79</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>49</v>
@@ -10435,10 +10453,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>265</v>
@@ -10450,7 +10468,7 @@
         <v>480</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>49</v>
@@ -10458,10 +10476,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>265</v>
@@ -10470,10 +10488,10 @@
         <v>79</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>49</v>
@@ -10481,68 +10499,68 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="F57" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>667</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>49</v>
@@ -10550,22 +10568,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>96</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>49</v>
@@ -10573,22 +10591,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>96</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>49</v>
@@ -10596,22 +10614,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>96</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>49</v>
@@ -10619,22 +10637,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>49</v>
@@ -10642,22 +10660,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>49</v>
@@ -10665,37 +10683,37 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>49</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{08077B1F-C8F3-4FF4-8D9E-441FB5D374EE}"/>
+  <autoFilter ref="A1:G64" xr:uid="{43D73AB6-60D4-4CBE-BCDD-98EDFAF17F81}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{621EB93F-3019-4A44-9078-56A22FF59C19}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C87D75BE-50B2-423F-B8E7-6633105CF6C9}">
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="14.625" customWidth="1"/>
@@ -10708,10 +10726,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>30</v>
@@ -10723,7 +10741,7 @@
         <v>173</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>43</v>
@@ -10731,10 +10749,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>79</v>
@@ -10743,21 +10761,21 @@
         <v>81</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>47</v>
@@ -10766,21 +10784,21 @@
         <v>98</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
@@ -10792,83 +10810,106 @@
         <v>47</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D6" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>692</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>701</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>699</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>703</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="E6" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D7" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>692</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>704</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="E7" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>699</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>706</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="B8" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>707</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>708</v>
+      <c r="F8" s="10" t="s">
+        <v>713</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>714</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{621EB93F-3019-4A44-9078-56A22FF59C19}"/>
+  <autoFilter ref="A1:G8" xr:uid="{C87D75BE-50B2-423F-B8E7-6633105CF6C9}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\w0915\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{033455B9-C0B8-4669-AD63-B16234195671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B80D1625-30AE-4DFB-B301-CB6255B0BC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15345" xr2:uid="{CE3E8DA3-FDF5-435E-92A0-7E7E97314460}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15345" xr2:uid="{BAC606E5-1F95-45DB-BA6A-68BF0CBF1B23}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="738">
   <si>
     <t>Project Abyss — 캐릭터 스킬 스펙 (2026-09-13)</t>
   </si>
@@ -87,7 +87,7 @@
     <t>• 유형 — 파괴형 = 결투 대 결투 교환에서 이기면 파괴 권한 / 유틸형 = 파괴 권한 없음 / 강한 · 약한 = 도사림 분류.</t>
   </si>
   <si>
-    <t>• 트리거 — 사용시 / 매칭시(결투 대 결투 게이트만 서면, 일방타격 포함) / 승리시 / 패배시 / 발동(위세) / 준비 행동.</t>
+    <t>• 트리거 — 사용시(스킬이 발동되는 시점: 공격 스킬은 그 슬롯의 합이 시작될 때, 도사림은 누르는 순간) / 매칭시(결투 대 결투 게이트만 서면, 일방타격 포함) / 승리시 / 패배시 / 합 종료시(합이 끝난 뒤, 합 전체 결과를 조건으로) / 발동(위세) / 준비 행동.</t>
   </si>
   <si>
     <t>• 결투 효과는 전부 결투 대 결투 게이트 안이다. 상대가 평타면 위력만 남는다.</t>
@@ -339,7 +339,7 @@
     <t>10~28</t>
   </si>
   <si>
-    <t>짓눌린 상태에서 승리 시 광기 +1 추가</t>
+    <t>승리시 짓눌린 상태면 광기 +1 추가</t>
   </si>
   <si>
     <t>잠정</t>
@@ -444,7 +444,7 @@
     <t>15~22</t>
   </si>
   <si>
-    <t>1~4번째 승리 출혈 +1 추가 · 5번째 승리 출혈 +2 추가</t>
+    <t>1~4번째 승리시 출혈 +1 추가 · 5번째 승리시 출혈 +2 추가</t>
   </si>
   <si>
     <t>#8</t>
@@ -522,7 +522,7 @@
     <t>16~28</t>
   </si>
   <si>
-    <t>1 · 2번째 승리 상대 균열(다음 턴) · 3번째 승리 시 상대 흐트러짐 ≤ 최대치 25%면 흐트러짐 피해 2배</t>
+    <t>1 · 2번째 승리시 상대 균열(다음 턴) · 3번째 승리시 상대 흐트러짐 ≤ 최대치 25%면 흐트러짐 피해 2배</t>
   </si>
   <si>
     <t>#13</t>
@@ -543,7 +543,7 @@
     <t>18~25</t>
   </si>
   <si>
-    <t>1번째 상대 쇠약(다음 턴) · 2번째 상대 출혈 5+면 균열(다음 턴) · 3번째 위력 = 상대 부정적 상태 개수당 +1</t>
+    <t>1번째 승리시 상대 쇠약(다음 턴) · 2번째 승리시 상대 출혈 5+면 균열(다음 턴) · 3번째 위력 = 상대 부정적 상태 개수당 +1</t>
   </si>
   <si>
     <t>#15</t>
@@ -579,7 +579,7 @@
     <t>17~29</t>
   </si>
   <si>
-    <t>2번째 승리 시 상대 출혈 +1 추가 + 자신 출혈 1</t>
+    <t>2번째 승리시 상대 출혈 +1 추가 + 자신 출혈 1</t>
   </si>
   <si>
     <t>결투</t>
@@ -645,7 +645,7 @@
     <t>승리시 / 패배시</t>
   </si>
   <si>
-    <t>승리 출혈 +1 + 상대 골절(다음 턴) · 패배 광기 +2</t>
+    <t>승리시 출혈 +1 + 상대 골절(다음 턴) · 패배시 광기 +2</t>
   </si>
   <si>
     <t>형2 가교</t>
@@ -672,7 +672,7 @@
     <t>승리시 / 패배시 / 매칭시</t>
   </si>
   <si>
-    <t>1번째: 승리 광기 +1 · 패배 자기 흐트러짐 −20 / 2번째: 매칭시 광기 +4</t>
+    <t>1번째: 승리시 광기 +1 · 패배시 자기 흐트러짐 −20 / 2번째: 매칭시 광기 +4</t>
   </si>
   <si>
     <t>형3 가교</t>
@@ -687,7 +687,7 @@
     <t>13~24</t>
   </si>
   <si>
-    <t>자기 약화 부위 개수당 위력 +2 · 승리 광기 +1 · 패배 광기 +1 (라그나로크 지속 중 +3)</t>
+    <t>자기 약화 부위 개수당 위력 +2 · 승리시 광기 +1 · 패배시 광기 +1 (라그나로크 지속 중 +3)</t>
   </si>
   <si>
     <t>파괴 권한</t>
@@ -699,7 +699,7 @@
     <t>정면승부</t>
   </si>
   <si>
-    <t>이기면 준 피해의 50%만큼 자신도 피해</t>
+    <t>승리시 준 피해의 50%만큼 자신도 피해</t>
   </si>
   <si>
     <t>위세를 지피다</t>
@@ -744,7 +744,7 @@
     <t>승리시 / 매칭시</t>
   </si>
   <si>
-    <t>1 출혈 +2 · 2 상대 쇠약(다음 턴) · 3 매칭시 상대 방어도 전부 제거</t>
+    <t>1 승리시 출혈 +2 · 2 승리시 상대 쇠약(다음 턴) · 3 매칭시 상대 방어도 전부 제거</t>
   </si>
   <si>
     <t>피의 대가</t>
@@ -771,7 +771,7 @@
     <t>4 (가변)</t>
   </si>
   <si>
-    <t>쓸 때마다 이 스킬 빛 비용 −1 (전투 내 누적 · 최소 1)</t>
+    <t>쓸 때마다 이 스킬 빛 비용 −1 (전투 내 누적 · 최소 1) · 사용시 광기 +1</t>
   </si>
   <si>
     <t>명예로운 전투</t>
@@ -783,7 +783,7 @@
     <t>매칭시</t>
   </si>
   <si>
-    <t>결투 대 결투일 때만 — 상대 스킬을 이 스킬로 강제 교체 · 이 굴림은 모든 버프 · 디버프 면역 · 동점 무한 재굴림</t>
+    <t>매칭시 상대 스킬을 이 스킬로 강제 교체 · 이 굴림은 모든 버프 · 디버프 면역 · 동점 무한 재굴림</t>
   </si>
   <si>
     <t>위력은 공식 이탈(의도)</t>
@@ -807,10 +807,7 @@
     <t>전부 되갚다</t>
   </si>
   <si>
-    <t>합 시작 시</t>
-  </si>
-  <si>
-    <t>기세 바가 짓눌림(B≤−70)이면 이 굴림 전체 위력 +6</t>
+    <t>기세 바가 짓눌림(B≤−70)이면 이 스킬의 모든 굴림 위력 +6</t>
   </si>
   <si>
     <t>미구현(근사 필요) · 위력·범위 미정 · 09-14 브레인스토밍</t>
@@ -825,7 +822,10 @@
     <t>19~24</t>
   </si>
   <si>
-    <t>내 다른 슬롯이 같은 상대 슬롯을 조준해도 그 슬롯들의 일방타격은 무효화(포기)</t>
+    <t>사용시 / 승리시</t>
+  </si>
+  <si>
+    <t>내 다른 슬롯이 같은 상대 슬롯을 조준해도 그 슬롯들의 일방타격은 무효화(포기) · 승리시 그 부위 출혈 +1</t>
   </si>
   <si>
     <t>미구현(근사 필요) · 위력은 공식(13) 이탈(의도) · 09-14 브레인스토밍</t>
@@ -1047,19 +1047,19 @@
     <t>뒷조사</t>
   </si>
   <si>
-    <t>이긴 교환마다 표식 +6</t>
-  </si>
-  <si>
-    <t>이긴 교환마다 표식 +12</t>
-  </si>
-  <si>
-    <t>이긴 교환마다 표식 +8</t>
+    <t>승리시 표식 +6</t>
+  </si>
+  <si>
+    <t>승리시 표식 +12</t>
+  </si>
+  <si>
+    <t>승리시 표식 +8</t>
   </si>
   <si>
     <t>숨 고르기</t>
   </si>
   <si>
-    <t>표식 없음 · 이긴 교환마다 살수의 감 +1</t>
+    <t>표식 없음 · 승리시 살수의 감 +1</t>
   </si>
   <si>
     <t>A</t>
@@ -1068,7 +1068,7 @@
     <t>의뢰 대상</t>
   </si>
   <si>
-    <t>이긴 교환마다 표식 +12 · 바 +15</t>
+    <t>승리시 표식 +12 · 바 +15</t>
   </si>
   <si>
     <t>표식 +24 · 바 +15</t>
@@ -1086,7 +1086,7 @@
     <t>잔혹한 마무리</t>
   </si>
   <si>
-    <t>이긴 교환마다 살수의 감 1 소비 → 코인, 앞면이면 무저항 추가타 (상한 강화 표)</t>
+    <t>승리시 살수의 감 1 소비 → 코인, 앞면이면 무저항 추가타 (상한 강화 표)</t>
   </si>
   <si>
     <t>자동 시전</t>
@@ -1503,7 +1503,7 @@
     <t>관통 5</t>
   </si>
   <si>
-    <t>뼈 70 미만 → 다음 턴 받는 피해 +3 (교환당) + 뼈 +100 / 뼈 70 이상 → 뼈 40 소모 · 피해 증가 없음</t>
+    <t>뼈 70 미만이면 → 다음 턴 받는 피해 +3 (교환당) + 뼈 +100 / 뼈 70 이상 → 뼈 40 소모 · 피해 증가 없음</t>
   </si>
   <si>
     <t>①</t>
@@ -1536,7 +1536,10 @@
     <t>절단 1 · 관통 2</t>
   </si>
   <si>
-    <t>완전 차단 · 다음 턴 속도 −1 · 뼈 40 소모 (없으면 뼈 +20) · 완전 차단 보상 뼈 +50</t>
+    <t>사용시 / 합 종료시</t>
+  </si>
+  <si>
+    <t>사용시 뼈 40 소모 (없으면 뼈 +20) · 다음 턴 속도 −1 / 합 종료시 완전 차단(그 합에서 진 교환 0)이면 뼈 +50</t>
   </si>
   <si>
     <t>포커페이스</t>
@@ -2783,7 +2786,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23918BAE-8DFA-4D11-823F-821F60F0EE44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E8B7F9-1647-4579-871F-72006C940C0A}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2973,7 +2976,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F297D8A-510C-4E8F-8845-F49A722D2253}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE064087-F84E-4BD3-B49E-8821B30EA28F}">
   <dimension ref="A1:T56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5225,7 +5228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>175</v>
       </c>
@@ -5458,7 +5461,7 @@
         <v>84</v>
       </c>
       <c r="P40" s="9" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="10" t="s">
         <v>238</v>
@@ -5644,10 +5647,10 @@
         <v>84</v>
       </c>
       <c r="P43" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q43" s="10" t="s">
         <v>250</v>
-      </c>
-      <c r="Q43" s="10" t="s">
-        <v>251</v>
       </c>
       <c r="R43" s="9" t="s">
         <v>1</v>
@@ -5656,7 +5659,7 @@
         <v>95</v>
       </c>
       <c r="T43" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -5667,7 +5670,7 @@
         <v>225</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>1</v>
@@ -5685,13 +5688,13 @@
         <v>99</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J44" s="9" t="s">
         <v>161</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L44" s="9" t="s">
         <v>161</v>
@@ -5706,7 +5709,7 @@
         <v>84</v>
       </c>
       <c r="P44" s="9" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="Q44" s="10" t="s">
         <v>256</v>
@@ -6466,14 +6469,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T56" xr:uid="{8F297D8A-510C-4E8F-8845-F49A722D2253}"/>
+  <autoFilter ref="A1:T56" xr:uid="{FE064087-F84E-4BD3-B49E-8821B30EA28F}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{845F2C28-D350-4D74-9E45-19A6594D2B76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1F7599A-188F-42F7-94DD-01231D4A505D}">
   <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7761,14 +7764,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M31" xr:uid="{845F2C28-D350-4D74-9E45-19A6594D2B76}"/>
+  <autoFilter ref="A1:M31" xr:uid="{A1F7599A-188F-42F7-94DD-01231D4A505D}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B865C08C-4D2A-465D-9A84-581D6E21FD29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD5E11D6-86E0-4B79-ABD4-0553037CDDAD}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7961,14 +7964,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4" xr:uid="{B865C08C-4D2A-465D-9A84-581D6E21FD29}"/>
+  <autoFilter ref="A1:N4" xr:uid="{AD5E11D6-86E0-4B79-ABD4-0553037CDDAD}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F864179E-3CA2-4A87-BBBE-8D7698AD7225}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484AA2C6-5BF7-41F0-8A2D-94C3C143E9A8}">
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8062,7 +8065,7 @@
         <v>450</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>1</v>
@@ -8656,10 +8659,10 @@
         <v>492</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>73</v>
+        <v>493</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="R11" s="11" t="s">
         <v>1</v>
@@ -8803,7 +8806,7 @@
         <v>335</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>1</v>
@@ -8845,7 +8848,7 @@
         <v>149</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="R14" s="13" t="s">
         <v>1</v>
@@ -8854,7 +8857,7 @@
         <v>49</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
@@ -8865,7 +8868,7 @@
         <v>341</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>1</v>
@@ -8907,7 +8910,7 @@
         <v>149</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="R15" s="13" t="s">
         <v>1</v>
@@ -8927,7 +8930,7 @@
         <v>345</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>1</v>
@@ -8969,13 +8972,13 @@
         <v>149</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="R16" s="13" t="s">
         <v>1</v>
       </c>
       <c r="S16" s="13" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="T16" s="14" t="s">
         <v>1</v>
@@ -8986,10 +8989,10 @@
         <v>258</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>1</v>
@@ -9031,7 +9034,7 @@
         <v>149</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="R17" s="13" t="s">
         <v>1</v>
@@ -9040,7 +9043,7 @@
         <v>49</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
@@ -9051,7 +9054,7 @@
         <v>287</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>1</v>
@@ -9093,7 +9096,7 @@
         <v>290</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="R18" s="11" t="s">
         <v>1</v>
@@ -9113,7 +9116,7 @@
         <v>292</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>1</v>
@@ -9155,7 +9158,7 @@
         <v>290</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="R19" s="11" t="s">
         <v>1</v>
@@ -9175,7 +9178,7 @@
         <v>296</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>1</v>
@@ -9217,7 +9220,7 @@
         <v>290</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="R20" s="11" t="s">
         <v>1</v>
@@ -9230,14 +9233,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T20" xr:uid="{F864179E-3CA2-4A87-BBBE-8D7698AD7225}"/>
+  <autoFilter ref="A1:T20" xr:uid="{484AA2C6-5BF7-41F0-8A2D-94C3C143E9A8}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D7DDC6C-8511-4516-9CD8-15707420E6E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734AD395-189B-4428-9F26-259ACFB5EF00}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9252,7 +9255,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>26</v>
@@ -9261,13 +9264,13 @@
         <v>24</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>43</v>
@@ -9275,91 +9278,91 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>524</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>525</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>1</v>
@@ -9367,22 +9370,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>1</v>
@@ -9390,22 +9393,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>1</v>
@@ -9413,39 +9416,39 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>47</v>
@@ -9454,87 +9457,87 @@
         <v>79</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12" xr:uid="{0D7DDC6C-8511-4516-9CD8-15707420E6E4}"/>
+  <autoFilter ref="A1:G12" xr:uid="{734AD395-189B-4428-9F26-259ACFB5EF00}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3554B52-42DC-4D1E-9AE9-2A7C48480A22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9372995-27A0-4EAD-A9D7-E4DEF189AE4D}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9548,19 +9551,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>40</v>
@@ -9571,22 +9574,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>49</v>
@@ -9594,22 +9597,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>49</v>
@@ -9617,22 +9620,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>49</v>
@@ -9640,22 +9643,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>49</v>
@@ -9663,22 +9666,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>49</v>
@@ -9686,22 +9689,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>49</v>
@@ -9709,22 +9712,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>49</v>
@@ -9732,22 +9735,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>49</v>
@@ -9755,22 +9758,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>49</v>
@@ -9778,13 +9781,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>99</v>
@@ -9793,7 +9796,7 @@
         <v>176</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>49</v>
@@ -9801,22 +9804,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>49</v>
@@ -9824,22 +9827,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>49</v>
@@ -9847,22 +9850,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>49</v>
@@ -9870,22 +9873,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>98</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>49</v>
@@ -9893,22 +9896,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>49</v>
@@ -9916,45 +9919,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>49</v>
@@ -9962,22 +9965,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>49</v>
@@ -9985,22 +9988,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>49</v>
@@ -10008,22 +10011,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>49</v>
@@ -10031,22 +10034,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>49</v>
@@ -10054,22 +10057,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>49</v>
@@ -10077,22 +10080,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>49</v>
@@ -10100,22 +10103,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>49</v>
@@ -10123,22 +10126,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>49</v>
@@ -10146,22 +10149,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>49</v>
@@ -10169,183 +10172,183 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E30" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>630</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>98</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>98</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>98</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>49</v>
@@ -10353,68 +10356,68 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>49</v>
@@ -10422,22 +10425,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>49</v>
@@ -10445,22 +10448,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>49</v>
@@ -10468,22 +10471,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>49</v>
@@ -10491,22 +10494,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>49</v>
@@ -10514,22 +10517,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>49</v>
@@ -10537,45 +10540,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>49</v>
@@ -10583,22 +10586,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>49</v>
@@ -10606,10 +10609,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>286</v>
@@ -10618,10 +10621,10 @@
         <v>99</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>49</v>
@@ -10629,10 +10632,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>286</v>
@@ -10641,10 +10644,10 @@
         <v>99</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>49</v>
@@ -10652,10 +10655,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>286</v>
@@ -10664,10 +10667,10 @@
         <v>99</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>49</v>
@@ -10675,10 +10678,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>286</v>
@@ -10687,10 +10690,10 @@
         <v>98</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>49</v>
@@ -10698,10 +10701,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>286</v>
@@ -10710,10 +10713,10 @@
         <v>98</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>49</v>
@@ -10721,10 +10724,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>286</v>
@@ -10733,10 +10736,10 @@
         <v>98</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>49</v>
@@ -10744,10 +10747,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>286</v>
@@ -10756,10 +10759,10 @@
         <v>79</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>49</v>
@@ -10767,10 +10770,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>286</v>
@@ -10779,10 +10782,10 @@
         <v>79</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>49</v>
@@ -10790,10 +10793,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>286</v>
@@ -10802,10 +10805,10 @@
         <v>79</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>49</v>
@@ -10813,68 +10816,68 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>690</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>691</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>49</v>
@@ -10882,22 +10885,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>49</v>
@@ -10905,22 +10908,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>49</v>
@@ -10928,22 +10931,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>49</v>
@@ -10951,22 +10954,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>49</v>
@@ -10974,22 +10977,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>49</v>
@@ -10997,36 +11000,36 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>49</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{D3554B52-42DC-4D1E-9AE9-2A7C48480A22}"/>
+  <autoFilter ref="A1:G64" xr:uid="{A9372995-27A0-4EAD-A9D7-E4DEF189AE4D}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A78A4D-69F8-453A-A4EE-5A106808F8B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002C133B-9FE1-4F0C-B438-7D4B6C85E1B2}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11040,10 +11043,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>30</v>
@@ -11055,7 +11058,7 @@
         <v>175</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>43</v>
@@ -11063,10 +11066,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>79</v>
@@ -11075,21 +11078,21 @@
         <v>81</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>47</v>
@@ -11098,21 +11101,21 @@
         <v>100</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
@@ -11124,18 +11127,18 @@
         <v>47</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>47</v>
@@ -11147,18 +11150,18 @@
         <v>47</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>79</v>
@@ -11167,21 +11170,21 @@
         <v>153</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>98</v>
@@ -11190,21 +11193,21 @@
         <v>100</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>47</v>
@@ -11216,14 +11219,14 @@
         <v>47</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{57A78A4D-69F8-453A-A4EE-5A106808F8B8}"/>
+  <autoFilter ref="A1:G8" xr:uid="{002C133B-9FE1-4F0C-B438-7D4B6C85E1B2}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-onedrive-desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\w0916\build6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-onedrive-desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\w0916\build9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB933CBA-06FB-4212-93AA-A54A13AE4F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0765A8-87D0-431C-9DAA-9D43374334E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" activeTab="1" xr2:uid="{7AA41AD5-58C0-40E4-A758-A338A1BB80B4}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="816">
   <si>
     <t>Project Abyss — 캐릭터 스킬 스펙 (2026-09-13)</t>
   </si>
@@ -363,9 +363,6 @@
     <t>15~20</t>
   </si>
   <si>
-    <t>15~24</t>
-  </si>
-  <si>
     <t>없음 (순수 화력)</t>
   </si>
   <si>
@@ -429,24 +426,12 @@
     <t>10</t>
   </si>
   <si>
-    <t>8~14</t>
-  </si>
-  <si>
-    <t>10~16</t>
-  </si>
-  <si>
     <t>12~17</t>
   </si>
   <si>
-    <t>13~19</t>
-  </si>
-  <si>
     <t>15~22</t>
   </si>
   <si>
-    <t>1~4번째 승리시 출혈 +1 추가 · 5번째 승리시 출혈 +2 추가</t>
-  </si>
-  <si>
     <t>#8</t>
   </si>
   <si>
@@ -513,9 +498,6 @@
     <t>13</t>
   </si>
   <si>
-    <t>16~28</t>
-  </si>
-  <si>
     <t>1 · 2번째 승리시 상대 균열(다음 턴) · 3번째 승리시 상대 흐트러짐 ≤ 최대치 25%면 흐트러짐 피해 2배</t>
   </si>
   <si>
@@ -564,12 +546,6 @@
     <t>저며내기</t>
   </si>
   <si>
-    <t>13~16</t>
-  </si>
-  <si>
-    <t>17~29</t>
-  </si>
-  <si>
     <t>2번째 승리시 상대 출혈 +1 추가 + 자신 출혈 1</t>
   </si>
   <si>
@@ -690,9 +666,6 @@
     <t>정면승부</t>
   </si>
   <si>
-    <t>승리시 준 피해의 50%만큼 자신도 피해</t>
-  </si>
-  <si>
     <t>위세를 지피다</t>
   </si>
   <si>
@@ -765,16 +738,7 @@
     <t>명예로운 전투</t>
   </si>
   <si>
-    <t>19~21</t>
-  </si>
-  <si>
     <t>매칭시</t>
-  </si>
-  <si>
-    <t>매칭시 상대 스킬을 이 스킬로 강제 교체 · 이 굴림은 모든 버프 · 디버프 면역 · 동점 무한 재굴림</t>
-  </si>
-  <si>
-    <t>위력은 공식 이탈(의도)</t>
   </si>
   <si>
     <t>피의 맹세</t>
@@ -2485,6 +2449,134 @@
   </si>
   <si>
     <t>방어도 09-15 조정(15 → 10)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>16~23</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>17~22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>승리시 준 피해의 25%만큼 자신도 피해</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>09-15 조정(위력 12 → 15, 자해 50% → 25%)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>16</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>17~22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>17~26</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>위력 09-16 조정(+2)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>15~22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>13~19</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10~16</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8~14</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1번째 승리시 출혈 +2 추가 · 2~5번째 승리시 출혈 +1 추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>09-16 굴림 역순(강 → 약) · 효과도 굴림을 따라 옮김</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>14</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>13~18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>17~29</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>위력 09-16 조정(+1)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>17~24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>18~23</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>17</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>16~19</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20~32</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>위력 09-16 조정(+3)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>14</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>15~22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>16~21</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>위력 09-16 조정(+2)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>17~23</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>매칭시 상대 스킬을 이 스킬로 강제 교체(양쪽 모두 이 스킬의 굴림 1개) · 버프 · 디버프는 그대로 적용 · 동점 무한 재굴림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>09-16 개정(19~21 버프 면역 → 17~23 버프 적용) · 위력은 공식 이탈(의도)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3761,13 +3853,13 @@
         <v>99</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>100</v>
+        <v>789</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>101</v>
+        <v>790</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>102</v>
+        <v>791</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>1</v>
@@ -3785,7 +3877,7 @@
         <v>47</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>1</v>
@@ -3794,7 +3886,7 @@
         <v>95</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>1</v>
+        <v>792</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
@@ -3802,10 +3894,10 @@
         <v>75</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>1</v>
@@ -3826,10 +3918,10 @@
         <v>100</v>
       </c>
       <c r="J11" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>1</v>
@@ -3847,7 +3939,7 @@
         <v>73</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>1</v>
@@ -3864,10 +3956,10 @@
         <v>75</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>1</v>
@@ -3885,13 +3977,13 @@
         <v>80</v>
       </c>
       <c r="I12" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="K12" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>1</v>
@@ -3909,7 +4001,7 @@
         <v>73</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>1</v>
@@ -3926,10 +4018,10 @@
         <v>75</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>1</v>
@@ -3947,13 +4039,13 @@
         <v>80</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>111</v>
+        <v>809</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>117</v>
+        <v>810</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>118</v>
+        <v>811</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>1</v>
@@ -3971,7 +4063,7 @@
         <v>47</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>1</v>
@@ -3980,18 +4072,18 @@
         <v>95</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>75</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>1</v>
@@ -4003,28 +4095,28 @@
         <v>1</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>99</v>
       </c>
       <c r="I14" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="L14" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="J14" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="M14" s="6" t="s">
-        <v>127</v>
+        <v>795</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>128</v>
+        <v>796</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>84</v>
@@ -4033,7 +4125,7 @@
         <v>73</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>129</v>
+        <v>797</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>1</v>
@@ -4042,7 +4134,7 @@
         <v>95</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>1</v>
+        <v>798</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
@@ -4050,10 +4142,10 @@
         <v>75</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>1</v>
@@ -4065,25 +4157,25 @@
         <v>1</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>99</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>1</v>
@@ -4092,10 +4184,10 @@
         <v>84</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>1</v>
@@ -4104,7 +4196,7 @@
         <v>95</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
@@ -4112,10 +4204,10 @@
         <v>75</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>1</v>
@@ -4133,10 +4225,10 @@
         <v>98</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>1</v>
@@ -4157,7 +4249,7 @@
         <v>73</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>1</v>
@@ -4166,7 +4258,7 @@
         <v>95</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -4174,10 +4266,10 @@
         <v>75</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>1</v>
@@ -4195,13 +4287,13 @@
         <v>98</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>1</v>
@@ -4216,10 +4308,10 @@
         <v>84</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>1</v>
@@ -4236,10 +4328,10 @@
         <v>75</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>1</v>
@@ -4257,16 +4349,16 @@
         <v>99</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>151</v>
+        <v>799</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>126</v>
+        <v>800</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>146</v>
+        <v>793</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>152</v>
+        <v>801</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>1</v>
@@ -4281,7 +4373,7 @@
         <v>73</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>1</v>
@@ -4290,7 +4382,7 @@
         <v>95</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>1</v>
+        <v>802</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -4298,10 +4390,10 @@
         <v>75</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>1</v>
@@ -4319,13 +4411,13 @@
         <v>80</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>1</v>
@@ -4343,7 +4435,7 @@
         <v>73</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>1</v>
@@ -4360,10 +4452,10 @@
         <v>75</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>1</v>
@@ -4381,16 +4473,16 @@
         <v>99</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>1</v>
@@ -4405,7 +4497,7 @@
         <v>73</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>1</v>
@@ -4422,10 +4514,10 @@
         <v>75</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>1</v>
@@ -4443,13 +4535,13 @@
         <v>99</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>100</v>
+        <v>789</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>128</v>
+        <v>803</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>163</v>
+        <v>804</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>1</v>
@@ -4467,7 +4559,7 @@
         <v>73</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>1</v>
@@ -4476,7 +4568,7 @@
         <v>95</v>
       </c>
       <c r="T21" s="7" t="s">
-        <v>1</v>
+        <v>792</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
@@ -4484,10 +4576,10 @@
         <v>75</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>1</v>
@@ -4508,10 +4600,10 @@
         <v>100</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>1</v>
@@ -4526,10 +4618,10 @@
         <v>84</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>1</v>
@@ -4538,7 +4630,7 @@
         <v>95</v>
       </c>
       <c r="T22" s="7" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
@@ -4546,10 +4638,10 @@
         <v>75</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>1</v>
@@ -4567,13 +4659,13 @@
         <v>99</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>100</v>
+        <v>805</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>169</v>
+        <v>806</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>170</v>
+        <v>807</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>1</v>
@@ -4591,7 +4683,7 @@
         <v>73</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>1</v>
@@ -4600,27 +4692,27 @@
         <v>95</v>
       </c>
       <c r="T23" s="7" t="s">
-        <v>1</v>
+        <v>808</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>78</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>98</v>
@@ -4629,13 +4721,13 @@
         <v>98</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J24" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>117</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>118</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>1</v>
@@ -4653,10 +4745,10 @@
         <v>73</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="S24" s="8" t="s">
         <v>95</v>
@@ -4667,22 +4759,22 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>172</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>180</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>90</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>79</v>
@@ -4694,13 +4786,13 @@
         <v>100</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M25" s="8" t="s">
         <v>1</v>
@@ -4715,7 +4807,7 @@
         <v>73</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="R25" s="8" t="s">
         <v>1</v>
@@ -4729,13 +4821,13 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>1</v>
@@ -4744,7 +4836,7 @@
         <v>78</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>99</v>
@@ -4753,10 +4845,10 @@
         <v>99</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>1</v>
@@ -4777,27 +4869,27 @@
         <v>73</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="R26" s="8" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="S26" s="8" t="s">
         <v>95</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>1</v>
@@ -4806,7 +4898,7 @@
         <v>90</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>79</v>
@@ -4815,16 +4907,16 @@
         <v>99</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="M27" s="8" t="s">
         <v>1</v>
@@ -4839,7 +4931,7 @@
         <v>73</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="R27" s="8" t="s">
         <v>1</v>
@@ -4853,13 +4945,13 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>1</v>
@@ -4868,7 +4960,7 @@
         <v>78</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>98</v>
@@ -4880,7 +4972,7 @@
         <v>100</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>92</v>
@@ -4898,10 +4990,10 @@
         <v>84</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="R28" s="8" t="s">
         <v>1</v>
@@ -4915,13 +5007,13 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>1</v>
@@ -4930,7 +5022,7 @@
         <v>90</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>79</v>
@@ -4939,16 +5031,16 @@
         <v>99</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>92</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M29" s="8" t="s">
         <v>1</v>
@@ -4963,7 +5055,7 @@
         <v>73</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="R29" s="8" t="s">
         <v>1</v>
@@ -4977,13 +5069,13 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>1</v>
@@ -4992,7 +5084,7 @@
         <v>90</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>98</v>
@@ -5001,13 +5093,13 @@
         <v>98</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>1</v>
@@ -5022,10 +5114,10 @@
         <v>84</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="R30" s="8" t="s">
         <v>1</v>
@@ -5039,13 +5131,13 @@
     </row>
     <row r="31" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>1</v>
@@ -5054,7 +5146,7 @@
         <v>78</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>98</v>
@@ -5066,10 +5158,10 @@
         <v>100</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>1</v>
@@ -5084,13 +5176,13 @@
         <v>84</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="S31" s="8" t="s">
         <v>95</v>
@@ -5099,15 +5191,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>1</v>
@@ -5116,7 +5208,7 @@
         <v>78</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>98</v>
@@ -5125,13 +5217,13 @@
         <v>80</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>111</v>
+        <v>784</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>117</v>
+        <v>785</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>118</v>
+        <v>786</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>1</v>
@@ -5149,27 +5241,27 @@
         <v>73</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>211</v>
+        <v>787</v>
       </c>
       <c r="R32" s="8" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="S32" s="8" t="s">
         <v>95</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>1</v>
+        <v>788</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>1</v>
@@ -5178,7 +5270,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>98</v>
@@ -5190,10 +5282,10 @@
         <v>100</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="L33" s="8" t="s">
         <v>1</v>
@@ -5211,7 +5303,7 @@
         <v>73</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="R33" s="8" t="s">
         <v>1</v>
@@ -5225,13 +5317,13 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>1</v>
@@ -5240,7 +5332,7 @@
         <v>90</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>79</v>
@@ -5249,16 +5341,16 @@
         <v>98</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M34" s="8" t="s">
         <v>1</v>
@@ -5273,7 +5365,7 @@
         <v>73</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="R34" s="8" t="s">
         <v>1</v>
@@ -5287,13 +5379,13 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>1</v>
@@ -5302,7 +5394,7 @@
         <v>90</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>98</v>
@@ -5311,13 +5403,13 @@
         <v>98</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="L35" s="8" t="s">
         <v>1</v>
@@ -5335,7 +5427,7 @@
         <v>73</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="R35" s="8" t="s">
         <v>1</v>
@@ -5344,18 +5436,18 @@
         <v>95</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>1</v>
@@ -5364,7 +5456,7 @@
         <v>78</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>98</v>
@@ -5373,13 +5465,13 @@
         <v>80</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J36" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="K36" s="8" t="s">
         <v>117</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>118</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>1</v>
@@ -5397,10 +5489,10 @@
         <v>73</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="R36" s="8" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="S36" s="8" t="s">
         <v>95</v>
@@ -5411,13 +5503,13 @@
     </row>
     <row r="37" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>1</v>
@@ -5426,7 +5518,7 @@
         <v>78</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>79</v>
@@ -5435,16 +5527,16 @@
         <v>98</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="M37" s="8" t="s">
         <v>1</v>
@@ -5456,10 +5548,10 @@
         <v>84</v>
       </c>
       <c r="P37" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="R37" s="8" t="s">
         <v>1</v>
@@ -5468,18 +5560,18 @@
         <v>95</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>1</v>
@@ -5488,7 +5580,7 @@
         <v>90</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>98</v>
@@ -5497,13 +5589,13 @@
         <v>98</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="L38" s="8" t="s">
         <v>1</v>
@@ -5518,10 +5610,10 @@
         <v>84</v>
       </c>
       <c r="P38" s="8" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="R38" s="8" t="s">
         <v>1</v>
@@ -5535,13 +5627,13 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>1</v>
@@ -5550,7 +5642,7 @@
         <v>90</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>98</v>
@@ -5562,7 +5654,7 @@
         <v>100</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>101</v>
@@ -5580,10 +5672,10 @@
         <v>84</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="R39" s="8" t="s">
         <v>1</v>
@@ -5597,13 +5689,13 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>1</v>
@@ -5612,43 +5704,43 @@
         <v>78</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="N40" s="8" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="O40" s="8" t="s">
         <v>84</v>
       </c>
       <c r="P40" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="R40" s="8" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="S40" s="8" t="s">
         <v>95</v>
@@ -5659,13 +5751,13 @@
     </row>
     <row r="41" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>1</v>
@@ -5674,7 +5766,7 @@
         <v>78</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>99</v>
@@ -5686,7 +5778,7 @@
         <v>47</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>236</v>
+        <v>813</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>1</v>
@@ -5704,30 +5796,30 @@
         <v>84</v>
       </c>
       <c r="P41" s="8" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>238</v>
+        <v>814</v>
       </c>
       <c r="R41" s="8" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="S41" s="8" t="s">
         <v>95</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>239</v>
+        <v>815</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>1</v>
@@ -5736,7 +5828,7 @@
         <v>78</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>98</v>
@@ -5745,13 +5837,13 @@
         <v>99</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J42" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="K42" s="8" t="s">
         <v>117</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>118</v>
       </c>
       <c r="L42" s="8" t="s">
         <v>1</v>
@@ -5766,30 +5858,30 @@
         <v>84</v>
       </c>
       <c r="P42" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="R42" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="S42" s="8" t="s">
         <v>95</v>
       </c>
       <c r="T42" s="9" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>1</v>
@@ -5798,7 +5890,7 @@
         <v>78</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>98</v>
@@ -5810,10 +5902,10 @@
         <v>100</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="L43" s="8" t="s">
         <v>1</v>
@@ -5828,10 +5920,10 @@
         <v>84</v>
       </c>
       <c r="P43" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="R43" s="8" t="s">
         <v>1</v>
@@ -5840,18 +5932,18 @@
         <v>95</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>1</v>
@@ -5860,7 +5952,7 @@
         <v>78</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G44" s="8" t="s">
         <v>79</v>
@@ -5869,16 +5961,16 @@
         <v>99</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="M44" s="8" t="s">
         <v>1</v>
@@ -5890,30 +5982,30 @@
         <v>84</v>
       </c>
       <c r="P44" s="8" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="R44" s="8" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="S44" s="8" t="s">
         <v>95</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>782</v>
+        <v>770</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>1</v>
@@ -5922,7 +6014,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>1</v>
@@ -5952,10 +6044,10 @@
         <v>47</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>1</v>
@@ -5964,18 +6056,18 @@
         <v>49</v>
       </c>
       <c r="T45" s="7" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>1</v>
@@ -5984,7 +6076,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>1</v>
@@ -6014,10 +6106,10 @@
         <v>1</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>1</v>
@@ -6026,27 +6118,27 @@
         <v>49</v>
       </c>
       <c r="T46" s="7" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
     </row>
     <row r="47" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>1</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>1</v>
@@ -6076,10 +6168,10 @@
         <v>1</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>1</v>
@@ -6088,18 +6180,18 @@
         <v>49</v>
       </c>
       <c r="T47" s="7" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>1</v>
@@ -6108,7 +6200,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>1</v>
@@ -6138,10 +6230,10 @@
         <v>1</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>1</v>
@@ -6155,14 +6247,14 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B49" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>264</v>
-      </c>
       <c r="D49" s="6" t="s">
         <v>1</v>
       </c>
@@ -6170,7 +6262,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>1</v>
@@ -6200,10 +6292,10 @@
         <v>1</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>1</v>
@@ -6217,13 +6309,13 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>1</v>
@@ -6232,7 +6324,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>1</v>
@@ -6262,10 +6354,10 @@
         <v>1</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>1</v>
@@ -6279,13 +6371,13 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>1</v>
@@ -6294,7 +6386,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>1</v>
@@ -6324,10 +6416,10 @@
         <v>1</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>1</v>
@@ -6341,13 +6433,13 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>1</v>
@@ -6356,7 +6448,7 @@
         <v>1</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>1</v>
@@ -6386,10 +6478,10 @@
         <v>1</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>1</v>
@@ -6403,13 +6495,13 @@
     </row>
     <row r="53" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>1</v>
@@ -6418,7 +6510,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>1</v>
@@ -6448,30 +6540,30 @@
         <v>1</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="S53" s="6" t="s">
         <v>95</v>
       </c>
       <c r="T53" s="7" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>1</v>
@@ -6480,7 +6572,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>1</v>
@@ -6510,10 +6602,10 @@
         <v>1</v>
       </c>
       <c r="P54" s="8" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="R54" s="8" t="s">
         <v>1</v>
@@ -6527,13 +6619,13 @@
     </row>
     <row r="55" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>1</v>
@@ -6542,7 +6634,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>1</v>
@@ -6572,10 +6664,10 @@
         <v>1</v>
       </c>
       <c r="P55" s="8" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="Q55" s="9" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="R55" s="8" t="s">
         <v>1</v>
@@ -6589,23 +6681,23 @@
     </row>
     <row r="56" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>288</v>
-      </c>
       <c r="G56" s="8" t="s">
         <v>1</v>
       </c>
@@ -6634,10 +6726,10 @@
         <v>1</v>
       </c>
       <c r="P56" s="8" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="Q56" s="9" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="R56" s="8" t="s">
         <v>1</v>
@@ -6696,13 +6788,13 @@
         <v>39</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>41</v>
@@ -6722,7 +6814,7 @@
         <v>44</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>1</v>
@@ -6737,13 +6829,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>1</v>
@@ -6752,7 +6844,7 @@
         <v>49</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -6763,7 +6855,7 @@
         <v>51</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>1</v>
@@ -6778,13 +6870,13 @@
         <v>1</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>1</v>
@@ -6793,7 +6885,7 @@
         <v>49</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -6804,7 +6896,7 @@
         <v>51</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -6816,16 +6908,16 @@
         <v>1</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>1</v>
@@ -6842,10 +6934,10 @@
         <v>50</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>1</v>
@@ -6857,16 +6949,16 @@
         <v>99</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>1</v>
@@ -6875,7 +6967,7 @@
         <v>49</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="67.5" x14ac:dyDescent="0.3">
@@ -6883,10 +6975,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>1</v>
@@ -6901,13 +6993,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>1</v>
@@ -6916,7 +7008,7 @@
         <v>49</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -6924,10 +7016,10 @@
         <v>66</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>1</v>
@@ -6948,7 +7040,7 @@
         <v>47</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>1</v>
@@ -6965,10 +7057,10 @@
         <v>66</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>1</v>
@@ -6989,10 +7081,10 @@
         <v>47</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>49</v>
@@ -7009,7 +7101,7 @@
         <v>47</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>78</v>
@@ -7024,13 +7116,13 @@
         <v>73</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>1</v>
@@ -7050,7 +7142,7 @@
         <v>47</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>90</v>
@@ -7065,13 +7157,13 @@
         <v>73</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>1</v>
@@ -7091,7 +7183,7 @@
         <v>47</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>78</v>
@@ -7103,16 +7195,16 @@
         <v>80</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>1</v>
@@ -7121,7 +7213,7 @@
         <v>49</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -7132,7 +7224,7 @@
         <v>47</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>90</v>
@@ -7144,16 +7236,16 @@
         <v>80</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>1</v>
@@ -7162,7 +7254,7 @@
         <v>49</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7173,7 +7265,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>78</v>
@@ -7188,22 +7280,22 @@
         <v>73</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>49</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -7214,7 +7306,7 @@
         <v>47</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>78</v>
@@ -7229,13 +7321,13 @@
         <v>73</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>1</v>
@@ -7244,7 +7336,7 @@
         <v>49</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -7255,7 +7347,7 @@
         <v>47</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>90</v>
@@ -7267,16 +7359,16 @@
         <v>80</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>1</v>
@@ -7285,7 +7377,7 @@
         <v>49</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7296,7 +7388,7 @@
         <v>47</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>78</v>
@@ -7308,25 +7400,25 @@
         <v>99</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>49</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7337,7 +7429,7 @@
         <v>47</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>90</v>
@@ -7352,33 +7444,33 @@
         <v>73</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>49</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>78</v>
@@ -7393,13 +7485,13 @@
         <v>73</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>1</v>
@@ -7408,18 +7500,18 @@
         <v>49</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>78</v>
@@ -7434,13 +7526,13 @@
         <v>73</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>1</v>
@@ -7449,18 +7541,18 @@
         <v>49</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>90</v>
@@ -7472,16 +7564,16 @@
         <v>99</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K20" s="8" t="s">
         <v>1</v>
@@ -7495,13 +7587,13 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>90</v>
@@ -7513,16 +7605,16 @@
         <v>99</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>1</v>
@@ -7531,18 +7623,18 @@
         <v>49</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>90</v>
@@ -7554,16 +7646,16 @@
         <v>99</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>1</v>
@@ -7577,13 +7669,13 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>78</v>
@@ -7598,13 +7690,13 @@
         <v>73</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>1</v>
@@ -7613,18 +7705,18 @@
         <v>49</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>78</v>
@@ -7639,13 +7731,13 @@
         <v>73</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>1</v>
@@ -7659,13 +7751,13 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>90</v>
@@ -7680,13 +7772,13 @@
         <v>73</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>1</v>
@@ -7695,18 +7787,18 @@
         <v>49</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>78</v>
@@ -7718,16 +7810,16 @@
         <v>99</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>1</v>
@@ -7741,13 +7833,13 @@
     </row>
     <row r="27" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>78</v>
@@ -7759,16 +7851,16 @@
         <v>98</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>1</v>
@@ -7777,18 +7869,18 @@
         <v>49</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>78</v>
@@ -7803,13 +7895,13 @@
         <v>73</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>1</v>
@@ -7818,18 +7910,18 @@
         <v>49</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>90</v>
@@ -7844,13 +7936,13 @@
         <v>73</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="K29" s="8" t="s">
         <v>1</v>
@@ -7859,18 +7951,18 @@
         <v>49</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>90</v>
@@ -7882,16 +7974,16 @@
         <v>98</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>1</v>
@@ -7900,18 +7992,18 @@
         <v>49</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>78</v>
@@ -7926,54 +8018,54 @@
         <v>73</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>49</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>80</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>1</v>
@@ -7987,34 +8079,34 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>99</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>1</v>
@@ -8028,34 +8120,34 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>99</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>1</v>
@@ -8069,34 +8161,34 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>99</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>1</v>
@@ -8110,34 +8202,34 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>99</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>1</v>
@@ -8146,39 +8238,39 @@
         <v>49</v>
       </c>
       <c r="M36" s="7" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>99</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>1</v>
@@ -8187,39 +8279,39 @@
         <v>49</v>
       </c>
       <c r="M37" s="7" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>80</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>1</v>
@@ -8228,39 +8320,39 @@
         <v>49</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>80</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>1</v>
@@ -8269,39 +8361,39 @@
         <v>49</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>80</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>1</v>
@@ -8310,39 +8402,39 @@
         <v>49</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>1</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>1</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>1</v>
@@ -8356,34 +8448,34 @@
     </row>
     <row r="42" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>1</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>1</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K42" s="8" t="s">
         <v>1</v>
@@ -8397,34 +8489,34 @@
     </row>
     <row r="43" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>1</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>1</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="K43" s="8" t="s">
         <v>1</v>
@@ -8462,190 +8554,190 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>79</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="G3" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>474</v>
-      </c>
       <c r="I3" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>464</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>476</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>47</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>99</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>47</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -8747,10 +8839,10 @@
         <v>44</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>1</v>
@@ -8789,7 +8881,7 @@
         <v>47</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="R2" s="12" t="s">
         <v>1</v>
@@ -8798,7 +8890,7 @@
         <v>49</v>
       </c>
       <c r="T2" s="13" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -8806,10 +8898,10 @@
         <v>66</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>1</v>
@@ -8851,7 +8943,7 @@
         <v>47</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="R3" s="10" t="s">
         <v>1</v>
@@ -8871,7 +8963,7 @@
         <v>58</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>1</v>
@@ -8913,7 +9005,7 @@
         <v>47</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="R4" s="12" t="s">
         <v>1</v>
@@ -8922,7 +9014,7 @@
         <v>49</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="54" x14ac:dyDescent="0.3">
@@ -8930,10 +9022,10 @@
         <v>66</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>1</v>
@@ -8972,10 +9064,10 @@
         <v>1</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="R5" s="10" t="s">
         <v>1</v>
@@ -8995,7 +9087,7 @@
         <v>67</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>1</v>
@@ -9037,13 +9129,13 @@
         <v>73</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="R6" s="10" t="s">
         <v>1</v>
       </c>
       <c r="S6" s="10" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="T6" s="11" t="s">
         <v>1</v>
@@ -9051,84 +9143,84 @@
     </row>
     <row r="7" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>84</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>99</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="N7" s="12" t="s">
         <v>1</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="S7" s="12" t="s">
         <v>49</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>84</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>98</v>
@@ -9137,13 +9229,13 @@
         <v>99</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>1</v>
@@ -9155,33 +9247,33 @@
         <v>1</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="Q8" s="13" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>49</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>1</v>
@@ -9193,37 +9285,37 @@
         <v>1</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>98</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="R9" s="12" t="s">
         <v>1</v>
@@ -9232,7 +9324,7 @@
         <v>49</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9240,10 +9332,10 @@
         <v>75</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>1</v>
@@ -9252,7 +9344,7 @@
         <v>84</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>98</v>
@@ -9261,13 +9353,13 @@
         <v>80</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="L10" s="11" t="s">
         <v>1</v>
@@ -9279,22 +9371,22 @@
         <v>1</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="R10" s="10" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="S10" s="10" t="s">
         <v>49</v>
       </c>
       <c r="T10" s="11" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9302,10 +9394,10 @@
         <v>75</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>1</v>
@@ -9326,13 +9418,13 @@
         <v>100</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>1</v>
@@ -9341,13 +9433,13 @@
         <v>1</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="Q11" s="11" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="R11" s="10" t="s">
         <v>1</v>
@@ -9361,13 +9453,13 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>1</v>
@@ -9376,7 +9468,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>1</v>
@@ -9406,10 +9498,10 @@
         <v>47</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q12" s="13" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="R12" s="12" t="s">
         <v>1</v>
@@ -9423,13 +9515,13 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>1</v>
@@ -9438,7 +9530,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>1</v>
@@ -9468,10 +9560,10 @@
         <v>1</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="R13" s="12" t="s">
         <v>1</v>
@@ -9485,13 +9577,13 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>1</v>
@@ -9500,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>1</v>
@@ -9530,10 +9622,10 @@
         <v>1</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q14" s="13" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="R14" s="12" t="s">
         <v>1</v>
@@ -9542,18 +9634,18 @@
         <v>49</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>1</v>
@@ -9562,7 +9654,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>1</v>
@@ -9592,10 +9684,10 @@
         <v>1</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="R15" s="12" t="s">
         <v>1</v>
@@ -9609,13 +9701,13 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>1</v>
@@ -9624,7 +9716,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>1</v>
@@ -9654,16 +9746,16 @@
         <v>1</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q16" s="13" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="R16" s="12" t="s">
         <v>1</v>
       </c>
       <c r="S16" s="12" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="T16" s="13" t="s">
         <v>1</v>
@@ -9671,13 +9763,13 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>1</v>
@@ -9686,7 +9778,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>1</v>
@@ -9716,10 +9808,10 @@
         <v>1</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="R17" s="12" t="s">
         <v>1</v>
@@ -9728,18 +9820,18 @@
         <v>49</v>
       </c>
       <c r="T17" s="13" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>1</v>
@@ -9748,7 +9840,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>1</v>
@@ -9778,10 +9870,10 @@
         <v>1</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="R18" s="10" t="s">
         <v>1</v>
@@ -9795,13 +9887,13 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>1</v>
@@ -9810,7 +9902,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>1</v>
@@ -9840,10 +9932,10 @@
         <v>1</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="R19" s="10" t="s">
         <v>1</v>
@@ -9857,13 +9949,13 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>1</v>
@@ -9872,7 +9964,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>1</v>
@@ -9902,10 +9994,10 @@
         <v>1</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="R20" s="10" t="s">
         <v>1</v>
@@ -9940,7 +10032,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>26</v>
@@ -9949,13 +10041,13 @@
         <v>24</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>43</v>
@@ -9963,91 +10055,91 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>569</v>
-      </c>
       <c r="C5" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>571</v>
-      </c>
       <c r="F5" s="8" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>1</v>
@@ -10055,22 +10147,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>574</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>571</v>
-      </c>
       <c r="F6" s="8" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>1</v>
@@ -10078,22 +10170,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>1</v>
@@ -10101,117 +10193,117 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>47</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>584</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>571</v>
-      </c>
       <c r="F9" s="8" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>571</v>
-      </c>
       <c r="F10" s="8" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>47</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -10236,19 +10328,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>40</v>
@@ -10259,22 +10351,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>49</v>
@@ -10282,22 +10374,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>49</v>
@@ -10305,22 +10397,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>49</v>
@@ -10328,22 +10420,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>49</v>
@@ -10351,22 +10443,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>49</v>
@@ -10374,22 +10466,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>49</v>
@@ -10397,22 +10489,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>49</v>
@@ -10420,22 +10512,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>49</v>
@@ -10443,22 +10535,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>49</v>
@@ -10466,22 +10558,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>49</v>
@@ -10489,22 +10581,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>49</v>
@@ -10512,22 +10604,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>49</v>
@@ -10535,22 +10627,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>49</v>
@@ -10558,22 +10650,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>49</v>
@@ -10581,22 +10673,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>49</v>
@@ -10604,45 +10696,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>49</v>
@@ -10650,22 +10742,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>49</v>
@@ -10673,22 +10765,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>49</v>
@@ -10696,22 +10788,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>49</v>
@@ -10719,22 +10811,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>49</v>
@@ -10742,22 +10834,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>49</v>
@@ -10765,22 +10857,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>49</v>
@@ -10788,22 +10880,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>49</v>
@@ -10811,22 +10903,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>49</v>
@@ -10834,22 +10926,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>49</v>
@@ -10857,183 +10949,183 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>49</v>
@@ -11041,68 +11133,68 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>49</v>
@@ -11110,22 +11202,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>49</v>
@@ -11133,22 +11225,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>49</v>
@@ -11156,22 +11248,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>49</v>
@@ -11179,22 +11271,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>49</v>
@@ -11202,22 +11294,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>49</v>
@@ -11225,45 +11317,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>704</v>
+        <v>692</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>49</v>
@@ -11271,22 +11363,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>49</v>
@@ -11294,22 +11386,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>49</v>
@@ -11317,22 +11409,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>49</v>
@@ -11340,22 +11432,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>49</v>
@@ -11363,22 +11455,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>49</v>
@@ -11386,22 +11478,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>49</v>
@@ -11409,22 +11501,22 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>49</v>
@@ -11432,22 +11524,22 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>49</v>
@@ -11455,22 +11547,22 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>49</v>
@@ -11478,22 +11570,22 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>49</v>
@@ -11501,68 +11593,68 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="G58" s="8" t="s">
         <v>49</v>
@@ -11570,22 +11662,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="G59" s="8" t="s">
         <v>49</v>
@@ -11593,22 +11685,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="G60" s="8" t="s">
         <v>49</v>
@@ -11616,22 +11708,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="G61" s="8" t="s">
         <v>49</v>
@@ -11639,22 +11731,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="G62" s="8" t="s">
         <v>49</v>
@@ -11662,22 +11754,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>49</v>
@@ -11685,22 +11777,22 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
       <c r="G64" s="8" t="s">
         <v>49</v>
@@ -11728,10 +11820,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>30</v>
@@ -11740,10 +11832,10 @@
         <v>32</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>43</v>
@@ -11751,10 +11843,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>79</v>
@@ -11763,21 +11855,21 @@
         <v>81</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>753</v>
+        <v>741</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>47</v>
@@ -11786,21 +11878,21 @@
         <v>100</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>47</v>
@@ -11812,18 +11904,18 @@
         <v>47</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>47</v>
@@ -11835,41 +11927,41 @@
         <v>47</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>98</v>
@@ -11878,21 +11970,21 @@
         <v>100</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>47</v>
@@ -11904,10 +11996,10 @@
         <v>47</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-onedrive-desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\w0916\build9\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\w0917\build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0765A8-87D0-431C-9DAA-9D43374334E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2D29FA-A195-4192-85D6-10E671ED1769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" activeTab="1" xr2:uid="{7AA41AD5-58C0-40E4-A758-A338A1BB80B4}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2773" uniqueCount="844">
   <si>
     <t>Project Abyss — 캐릭터 스킬 스펙 (2026-09-13)</t>
   </si>
@@ -330,15 +330,9 @@
     <t>BLUE</t>
   </si>
   <si>
-    <t>12~15</t>
-  </si>
-  <si>
     <t>12~19</t>
   </si>
   <si>
-    <t>10~28</t>
-  </si>
-  <si>
     <t>승리시 짓눌린 상태면 광기 +1 추가</t>
   </si>
   <si>
@@ -756,9 +750,6 @@
     <t>전부 되갚다</t>
   </si>
   <si>
-    <t>기세 바가 짓눌림(B≤−70)이면 이 스킬의 모든 굴림 위력 +6</t>
-  </si>
-  <si>
     <t>일기토</t>
   </si>
   <si>
@@ -1263,79 +1254,7 @@
     <t>미구현(무기별 조건 분기 필요) · 09-15 신설, 낙일 전용 처형 시너지 첫 카드 · 낙일=보스전/백우·적설=다수전 특화</t>
   </si>
   <si>
-    <t>노림수</t>
-  </si>
-  <si>
-    <t>그 턴 코인 앞면 확률 +10%p</t>
-  </si>
-  <si>
-    <t>선금 받기</t>
-  </si>
-  <si>
-    <t>그 턴 코인 뒷면 값 +2</t>
-  </si>
-  <si>
-    <t>환형(공격)</t>
-  </si>
-  <si>
-    <t>무기 교체(다음 턴) + 그 턴 위력 +2 (교체 전 무기 기준)</t>
-  </si>
-  <si>
-    <t>… +4</t>
-  </si>
-  <si>
-    <t>… +8</t>
-  </si>
-  <si>
-    <t>환형(수비)와 택1 장착</t>
-  </si>
-  <si>
-    <t>환형(수비)</t>
-  </si>
-  <si>
-    <t>무기 교체(다음 턴) + 그 턴 방어도 +30</t>
-  </si>
-  <si>
-    <t>환형(공격)과 택1 장착</t>
-  </si>
-  <si>
-    <t>기회를 엿보다</t>
-  </si>
-  <si>
-    <t>09-15 신설, 도사림 최초의 살수의 감 획득 카드</t>
-  </si>
-  <si>
-    <t>숨을 죽이다</t>
-  </si>
-  <si>
-    <t>표식 10 소모 → 방어도 +20</t>
-  </si>
-  <si>
-    <t>미구현(표식 소모 전환 코드 신설 필요) · 09-15 신설</t>
-  </si>
-  <si>
-    <t>칼을 갈다</t>
-  </si>
-  <si>
-    <t>표식 10 소모 → 다음 턴 신속 1</t>
-  </si>
-  <si>
-    <t>미구현(표식 소모 전환 코드 신설 필요) · 09-15 신설, 힘→신속 정정(캐릭터별 크기형 배정)</t>
-  </si>
-  <si>
-    <t>밑작업 착수</t>
-  </si>
-  <si>
     <t>임계 50</t>
-  </si>
-  <si>
-    <t>조준 부위에 크리값(7)만큼 표식 + 그 턴 이긴 교환마다 표식 +3</t>
-  </si>
-  <si>
-    <t>… 크리값(8)만큼 두 곳</t>
-  </si>
-  <si>
-    <t>… 크리값(24)만큼</t>
   </si>
   <si>
     <t>확실한 일처리</t>
@@ -2380,10 +2299,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>위력·범위 미정 · 09-14 브레인스토밍</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>13</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2577,6 +2492,230 @@
   </si>
   <si>
     <t>09-16 개정(19~21 버프 면역 → 17~23 버프 적용) · 위력은 공식 이탈(의도)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10~28</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>12~15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>09-16 굴림 역순(강 → 약)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>결투</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>때를 앞당기다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RED</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>살수의 감 4 소모 → 조준 부위 표식 즉시 44까지 채워 발화(무기별 효과 즉시 발동)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미구현(표식 강제 발화 처리 신설 필요) · 09-16 신설, K·L과 달리 발화 자체를 직접 일으킴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>끝장을 보다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4(쓸 때마다 −1, 최소 1, 누적)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>살수의 감 전부 소모 → 이 스킬 위력 +2(소모한 살수의 감 1당)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미구현(전량소모 위력전환 신설 필요) · 09-16 신설, 닥치는 대로(올라프)와 같은 비용 감소 구조</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>웅크리기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>약한</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어도 +12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>노려보기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 턴 모든 합 판정값 +1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>노림수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 턴 코인 앞면 확률 +10%p</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>〃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>선금 받기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 턴 코인 뒷면 값 +2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>환형(공격)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>준비 행동</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기 교체(다음 턴) + 그 턴 위력 +2 (교체 전 무기 기준)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>… +4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>… +8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>환형(수비)와 택1 장착</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>환형(수비)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기 교체(다음 턴) + 그 턴 방어도 +30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>환형(공격)과 택1 장착</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기회를 엿보다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>살수의 감 +1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>09-15 신설, 도사림 최초의 살수의 감 획득 카드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>도사림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강한</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>숨을 죽이다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>표식 10 소모 → 방어도 +20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미구현(표식 소모 전환 코드 신설 필요) · 09-15 신설</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>칼을 갈다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>표식 10 소모 → 다음 턴 신속 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미구현(표식 소모 전환 코드 신설 필요) · 09-15 신설, 힘→신속 정정(캐릭터별 크기형 배정)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>형1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>밑작업 착수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조준 부위에 크리값(7)만큼 표식 + 그 턴 이긴 교환마다 표식 +3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 크리값(8)만큼 두 곳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 크리값(24)만큼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기세 바가 열세 이하(B ≤ −30)이면 이 스킬의 모든 굴림 위력 +4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>위력·범위 미정 · 09-16 문턱 −70 → −30 · 보너스 6 → 4 · 09-14 브레인스토밍</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2683,7 +2822,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2725,6 +2864,12 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3794,13 +3939,13 @@
         <v>81</v>
       </c>
       <c r="J9" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="K9" s="6" t="s">
-        <v>92</v>
-      </c>
       <c r="L9" s="6" t="s">
-        <v>93</v>
+        <v>789</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>1</v>
@@ -3815,16 +3960,16 @@
         <v>73</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>1</v>
+        <v>790</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
@@ -3832,10 +3977,10 @@
         <v>75</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>1</v>
@@ -3847,19 +3992,19 @@
         <v>1</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>789</v>
+        <v>761</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>790</v>
+        <v>762</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>791</v>
+        <v>763</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>1</v>
@@ -3877,16 +4022,16 @@
         <v>47</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>792</v>
+        <v>764</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
@@ -3894,10 +4039,10 @@
         <v>75</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>1</v>
@@ -3909,19 +4054,19 @@
         <v>1</v>
       </c>
       <c r="G11" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>100</v>
-      </c>
       <c r="J11" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>1</v>
@@ -3939,13 +4084,13 @@
         <v>73</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T11" s="7" t="s">
         <v>1</v>
@@ -3956,10 +4101,10 @@
         <v>75</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>1</v>
@@ -3971,19 +4116,19 @@
         <v>1</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>80</v>
       </c>
       <c r="I12" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="K12" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>1</v>
@@ -4001,13 +4146,13 @@
         <v>73</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T12" s="7" t="s">
         <v>1</v>
@@ -4018,10 +4163,10 @@
         <v>75</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>1</v>
@@ -4033,19 +4178,19 @@
         <v>1</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>80</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>809</v>
+        <v>781</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>810</v>
+        <v>782</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>811</v>
+        <v>783</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>1</v>
@@ -4063,16 +4208,16 @@
         <v>47</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>812</v>
+        <v>784</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -4080,10 +4225,10 @@
         <v>75</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>1</v>
@@ -4095,28 +4240,28 @@
         <v>1</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="L14" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>794</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="M14" s="6" t="s">
-        <v>795</v>
+        <v>767</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>796</v>
+        <v>768</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>84</v>
@@ -4125,16 +4270,16 @@
         <v>73</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>797</v>
+        <v>769</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>798</v>
+        <v>770</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
@@ -4142,10 +4287,10 @@
         <v>75</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>1</v>
@@ -4157,25 +4302,25 @@
         <v>1</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>771</v>
+        <v>743</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>772</v>
+        <v>744</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>773</v>
+        <v>745</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>774</v>
+        <v>746</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>775</v>
+        <v>747</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>1</v>
@@ -4184,19 +4329,19 @@
         <v>84</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>776</v>
+        <v>748</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
@@ -4204,10 +4349,10 @@
         <v>75</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>1</v>
@@ -4219,16 +4364,16 @@
         <v>1</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>1</v>
@@ -4249,16 +4394,16 @@
         <v>73</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -4266,10 +4411,10 @@
         <v>75</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>1</v>
@@ -4281,19 +4426,19 @@
         <v>1</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I17" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="K17" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>1</v>
@@ -4308,16 +4453,16 @@
         <v>84</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T17" s="7" t="s">
         <v>1</v>
@@ -4328,10 +4473,10 @@
         <v>75</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>1</v>
@@ -4346,19 +4491,19 @@
         <v>79</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>799</v>
+        <v>771</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>800</v>
+        <v>772</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>793</v>
+        <v>765</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>801</v>
+        <v>773</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>1</v>
@@ -4373,16 +4518,16 @@
         <v>73</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S18" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>802</v>
+        <v>774</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -4390,10 +4535,10 @@
         <v>75</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>1</v>
@@ -4405,19 +4550,19 @@
         <v>1</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>80</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>1</v>
@@ -4435,13 +4580,13 @@
         <v>73</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T19" s="7" t="s">
         <v>1</v>
@@ -4452,10 +4597,10 @@
         <v>75</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>1</v>
@@ -4470,19 +4615,19 @@
         <v>79</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>1</v>
@@ -4497,13 +4642,13 @@
         <v>73</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T20" s="7" t="s">
         <v>1</v>
@@ -4514,10 +4659,10 @@
         <v>75</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>1</v>
@@ -4529,19 +4674,19 @@
         <v>1</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>789</v>
+        <v>761</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>803</v>
+        <v>775</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>804</v>
+        <v>776</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>1</v>
@@ -4559,16 +4704,16 @@
         <v>73</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T21" s="7" t="s">
-        <v>792</v>
+        <v>764</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
@@ -4576,10 +4721,10 @@
         <v>75</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>1</v>
@@ -4591,19 +4736,19 @@
         <v>1</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>100</v>
-      </c>
       <c r="J22" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>1</v>
@@ -4618,19 +4763,19 @@
         <v>84</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>782</v>
+        <v>754</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S22" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T22" s="7" t="s">
-        <v>783</v>
+        <v>755</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
@@ -4638,10 +4783,10 @@
         <v>75</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>1</v>
@@ -4653,19 +4798,19 @@
         <v>1</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>805</v>
+        <v>777</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>806</v>
+        <v>778</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>807</v>
+        <v>779</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>1</v>
@@ -4683,51 +4828,51 @@
         <v>73</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T23" s="7" t="s">
-        <v>808</v>
+        <v>780</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>78</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>1</v>
@@ -4745,13 +4890,13 @@
         <v>73</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T24" s="9" t="s">
         <v>1</v>
@@ -4759,40 +4904,40 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>90</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>79</v>
       </c>
       <c r="H25" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I25" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="J25" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M25" s="8" t="s">
         <v>1</v>
@@ -4807,13 +4952,13 @@
         <v>73</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R25" s="8" t="s">
         <v>1</v>
       </c>
       <c r="S25" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T25" s="9" t="s">
         <v>1</v>
@@ -4821,13 +4966,13 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>1</v>
@@ -4836,19 +4981,19 @@
         <v>78</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>1</v>
@@ -4869,27 +5014,27 @@
         <v>73</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R26" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="S26" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>1</v>
@@ -4898,25 +5043,25 @@
         <v>90</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>79</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M27" s="8" t="s">
         <v>1</v>
@@ -4931,13 +5076,13 @@
         <v>73</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R27" s="8" t="s">
         <v>1</v>
       </c>
       <c r="S27" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>1</v>
@@ -4945,13 +5090,13 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>1</v>
@@ -4960,22 +5105,22 @@
         <v>78</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G28" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="J28" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>1</v>
@@ -4990,16 +5135,16 @@
         <v>84</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R28" s="8" t="s">
         <v>1</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T28" s="9" t="s">
         <v>1</v>
@@ -5007,13 +5152,13 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>1</v>
@@ -5022,25 +5167,25 @@
         <v>90</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>79</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M29" s="8" t="s">
         <v>1</v>
@@ -5055,13 +5200,13 @@
         <v>73</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R29" s="8" t="s">
         <v>1</v>
       </c>
       <c r="S29" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T29" s="9" t="s">
         <v>1</v>
@@ -5069,13 +5214,13 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>1</v>
@@ -5084,22 +5229,22 @@
         <v>90</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>1</v>
@@ -5114,16 +5259,16 @@
         <v>84</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R30" s="8" t="s">
         <v>1</v>
       </c>
       <c r="S30" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T30" s="9" t="s">
         <v>1</v>
@@ -5131,13 +5276,13 @@
     </row>
     <row r="31" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>1</v>
@@ -5146,22 +5291,22 @@
         <v>78</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G31" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="H31" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="J31" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>1</v>
@@ -5176,16 +5321,16 @@
         <v>84</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S31" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T31" s="9" t="s">
         <v>1</v>
@@ -5193,13 +5338,13 @@
     </row>
     <row r="32" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>1</v>
@@ -5208,22 +5353,22 @@
         <v>78</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>80</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>784</v>
+        <v>756</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>785</v>
+        <v>757</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>786</v>
+        <v>758</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>1</v>
@@ -5241,27 +5386,27 @@
         <v>73</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>787</v>
+        <v>759</v>
       </c>
       <c r="R32" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S32" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>788</v>
+        <v>760</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B33" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>201</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>203</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>1</v>
@@ -5270,22 +5415,22 @@
         <v>90</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G33" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="H33" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="J33" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L33" s="8" t="s">
         <v>1</v>
@@ -5303,13 +5448,13 @@
         <v>73</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="R33" s="8" t="s">
         <v>1</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T33" s="9" t="s">
         <v>1</v>
@@ -5317,13 +5462,13 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>1</v>
@@ -5332,25 +5477,25 @@
         <v>90</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>79</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M34" s="8" t="s">
         <v>1</v>
@@ -5365,13 +5510,13 @@
         <v>73</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="R34" s="8" t="s">
         <v>1</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T34" s="9" t="s">
         <v>1</v>
@@ -5379,13 +5524,13 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>1</v>
@@ -5394,22 +5539,22 @@
         <v>90</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L35" s="8" t="s">
         <v>1</v>
@@ -5427,27 +5572,27 @@
         <v>73</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="R35" s="8" t="s">
         <v>1</v>
       </c>
       <c r="S35" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>1</v>
@@ -5456,22 +5601,22 @@
         <v>78</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>80</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>1</v>
@@ -5489,13 +5634,13 @@
         <v>73</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="R36" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S36" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T36" s="9" t="s">
         <v>1</v>
@@ -5503,13 +5648,13 @@
     </row>
     <row r="37" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>1</v>
@@ -5518,25 +5663,25 @@
         <v>78</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>79</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>777</v>
+        <v>749</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>778</v>
+        <v>750</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>779</v>
+        <v>751</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>780</v>
+        <v>752</v>
       </c>
       <c r="M37" s="8" t="s">
         <v>1</v>
@@ -5548,30 +5693,30 @@
         <v>84</v>
       </c>
       <c r="P37" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R37" s="8" t="s">
         <v>1</v>
       </c>
       <c r="S37" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>781</v>
+        <v>753</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>1</v>
@@ -5580,22 +5725,22 @@
         <v>90</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L38" s="8" t="s">
         <v>1</v>
@@ -5610,16 +5755,16 @@
         <v>84</v>
       </c>
       <c r="P38" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="R38" s="8" t="s">
         <v>1</v>
       </c>
       <c r="S38" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T38" s="9" t="s">
         <v>1</v>
@@ -5627,13 +5772,13 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>1</v>
@@ -5642,22 +5787,22 @@
         <v>90</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G39" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I39" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="J39" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="K39" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>101</v>
       </c>
       <c r="L39" s="8" t="s">
         <v>1</v>
@@ -5672,16 +5817,16 @@
         <v>84</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="R39" s="8" t="s">
         <v>1</v>
       </c>
       <c r="S39" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T39" s="9" t="s">
         <v>1</v>
@@ -5689,13 +5834,13 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>1</v>
@@ -5704,46 +5849,46 @@
         <v>78</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N40" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="O40" s="8" t="s">
         <v>84</v>
       </c>
       <c r="P40" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R40" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S40" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T40" s="9" t="s">
         <v>1</v>
@@ -5751,13 +5896,13 @@
     </row>
     <row r="41" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>1</v>
@@ -5766,10 +5911,10 @@
         <v>78</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H41" s="8" t="s">
         <v>79</v>
@@ -5778,7 +5923,7 @@
         <v>47</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>813</v>
+        <v>785</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>1</v>
@@ -5796,30 +5941,30 @@
         <v>84</v>
       </c>
       <c r="P41" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>814</v>
+        <v>786</v>
       </c>
       <c r="R41" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S41" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>815</v>
+        <v>787</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>1</v>
@@ -5828,22 +5973,22 @@
         <v>78</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L42" s="8" t="s">
         <v>1</v>
@@ -5858,30 +6003,30 @@
         <v>84</v>
       </c>
       <c r="P42" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q42" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="R42" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="S42" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="T42" s="9" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="27" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>230</v>
-      </c>
-      <c r="R42" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="S42" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="T42" s="9" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>232</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>1</v>
@@ -5890,22 +6035,22 @@
         <v>78</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G43" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I43" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="H43" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="J43" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L43" s="8" t="s">
         <v>1</v>
@@ -5920,30 +6065,30 @@
         <v>84</v>
       </c>
       <c r="P43" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>233</v>
+        <v>842</v>
       </c>
       <c r="R43" s="8" t="s">
         <v>1</v>
       </c>
       <c r="S43" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>766</v>
+        <v>843</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>1</v>
@@ -5952,25 +6097,25 @@
         <v>78</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G44" s="8" t="s">
         <v>79</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>767</v>
+        <v>739</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>768</v>
+        <v>740</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>769</v>
+        <v>741</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>768</v>
+        <v>740</v>
       </c>
       <c r="M44" s="8" t="s">
         <v>1</v>
@@ -5982,39 +6127,39 @@
         <v>84</v>
       </c>
       <c r="P44" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="R44" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S44" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>770</v>
+        <v>742</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>240</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>1</v>
@@ -6044,10 +6189,10 @@
         <v>47</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>1</v>
@@ -6056,33 +6201,33 @@
         <v>49</v>
       </c>
       <c r="T45" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>240</v>
-      </c>
       <c r="G46" s="6" t="s">
         <v>1</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I46" s="6" t="s">
         <v>1</v>
@@ -6106,10 +6251,10 @@
         <v>1</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>1</v>
@@ -6118,60 +6263,60 @@
         <v>49</v>
       </c>
       <c r="T46" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="47" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B47" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q47" s="7" t="s">
         <v>245</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K47" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L47" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M47" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N47" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="O47" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="P47" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q47" s="7" t="s">
-        <v>248</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>1</v>
@@ -6180,18 +6325,18 @@
         <v>49</v>
       </c>
       <c r="T47" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>1</v>
@@ -6200,13 +6345,13 @@
         <v>1</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>1</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>1</v>
@@ -6230,16 +6375,16 @@
         <v>1</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S48" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T48" s="7" t="s">
         <v>1</v>
@@ -6247,13 +6392,13 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>240</v>
-      </c>
       <c r="C49" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>1</v>
@@ -6262,7 +6407,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>1</v>
@@ -6292,16 +6437,16 @@
         <v>1</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S49" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T49" s="7" t="s">
         <v>1</v>
@@ -6309,13 +6454,13 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>1</v>
@@ -6324,7 +6469,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>1</v>
@@ -6354,16 +6499,16 @@
         <v>1</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S50" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T50" s="7" t="s">
         <v>1</v>
@@ -6371,13 +6516,13 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>1</v>
@@ -6386,13 +6531,13 @@
         <v>1</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>1</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>1</v>
@@ -6416,16 +6561,16 @@
         <v>1</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S51" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T51" s="7" t="s">
         <v>1</v>
@@ -6433,13 +6578,13 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>1</v>
@@ -6448,13 +6593,13 @@
         <v>1</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>1</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>1</v>
@@ -6478,16 +6623,16 @@
         <v>1</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>1</v>
       </c>
       <c r="S52" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T52" s="7" t="s">
         <v>1</v>
@@ -6495,117 +6640,117 @@
     </row>
     <row r="53" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C53" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M53" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N53" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="O53" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q53" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="R53" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K53" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L53" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M53" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N53" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="O53" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="P53" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q53" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="R53" s="6" t="s">
-        <v>263</v>
-      </c>
       <c r="S53" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T53" s="7" t="s">
-        <v>765</v>
+        <v>738</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="G54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P54" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="Q54" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="L54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="M54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="O54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="P54" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q54" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="R54" s="8" t="s">
         <v>1</v>
@@ -6619,55 +6764,55 @@
     </row>
     <row r="55" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B55" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O55" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P55" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q55" s="9" t="s">
         <v>270</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="H55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="L55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="M55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="O55" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="P55" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q55" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="R55" s="8" t="s">
         <v>1</v>
@@ -6681,55 +6826,55 @@
     </row>
     <row r="56" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B56" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P56" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q56" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="H56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="L56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="M56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="O56" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="P56" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q56" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="R56" s="8" t="s">
         <v>1</v>
@@ -6750,7 +6895,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71C7899C-D187-4591-9FE9-273F4C7CCBD5}">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.625" customWidth="1"/>
@@ -6788,13 +6933,13 @@
         <v>39</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>41</v>
@@ -6814,7 +6959,7 @@
         <v>44</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>1</v>
@@ -6829,13 +6974,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>1</v>
@@ -6844,7 +6989,7 @@
         <v>49</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -6855,28 +7000,28 @@
         <v>51</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>285</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>288</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>1</v>
@@ -6885,7 +7030,7 @@
         <v>49</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -6896,7 +7041,7 @@
         <v>51</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -6908,16 +7053,16 @@
         <v>1</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>1</v>
@@ -6934,31 +7079,31 @@
         <v>50</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>296</v>
-      </c>
       <c r="I5" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>1</v>
@@ -6967,7 +7112,7 @@
         <v>49</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="67.5" x14ac:dyDescent="0.3">
@@ -6975,10 +7120,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>1</v>
@@ -6993,13 +7138,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>1</v>
@@ -7008,7 +7153,7 @@
         <v>49</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7016,10 +7161,10 @@
         <v>66</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>1</v>
@@ -7040,7 +7185,7 @@
         <v>47</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>1</v>
@@ -7057,10 +7202,10 @@
         <v>66</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>302</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>305</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>1</v>
@@ -7081,10 +7226,10 @@
         <v>47</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>49</v>
@@ -7101,7 +7246,7 @@
         <v>47</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>78</v>
@@ -7116,13 +7261,13 @@
         <v>73</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>1</v>
@@ -7142,7 +7287,7 @@
         <v>47</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>90</v>
@@ -7151,19 +7296,19 @@
         <v>1</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>73</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>1</v>
@@ -7183,7 +7328,7 @@
         <v>47</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>78</v>
@@ -7195,16 +7340,16 @@
         <v>80</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>1</v>
@@ -7213,7 +7358,7 @@
         <v>49</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -7224,7 +7369,7 @@
         <v>47</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>90</v>
@@ -7236,16 +7381,16 @@
         <v>80</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>1</v>
@@ -7254,7 +7399,7 @@
         <v>49</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7265,7 +7410,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>78</v>
@@ -7274,28 +7419,28 @@
         <v>1</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>73</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="K13" s="6" t="s">
         <v>320</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>323</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>49</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -7306,7 +7451,7 @@
         <v>47</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>78</v>
@@ -7315,19 +7460,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>73</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>1</v>
@@ -7336,7 +7481,7 @@
         <v>49</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -7347,7 +7492,7 @@
         <v>47</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>90</v>
@@ -7359,16 +7504,16 @@
         <v>80</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>1</v>
@@ -7377,7 +7522,7 @@
         <v>49</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7388,7 +7533,7 @@
         <v>47</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>78</v>
@@ -7397,28 +7542,28 @@
         <v>1</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>49</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7429,7 +7574,7 @@
         <v>47</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>90</v>
@@ -7438,39 +7583,39 @@
         <v>1</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>73</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>49</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>78</v>
@@ -7479,19 +7624,19 @@
         <v>1</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>73</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>1</v>
@@ -7500,18 +7645,18 @@
         <v>49</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>78</v>
@@ -7520,19 +7665,19 @@
         <v>1</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>73</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>1</v>
@@ -7541,18 +7686,18 @@
         <v>49</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>90</v>
@@ -7561,19 +7706,19 @@
         <v>1</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K20" s="8" t="s">
         <v>1</v>
@@ -7587,13 +7732,13 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>90</v>
@@ -7602,19 +7747,19 @@
         <v>1</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>1</v>
@@ -7623,18 +7768,18 @@
         <v>49</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>90</v>
@@ -7643,19 +7788,19 @@
         <v>1</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>1</v>
@@ -7669,13 +7814,13 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>78</v>
@@ -7684,19 +7829,19 @@
         <v>1</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>73</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>1</v>
@@ -7705,18 +7850,18 @@
         <v>49</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>78</v>
@@ -7725,19 +7870,19 @@
         <v>1</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>73</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>1</v>
@@ -7751,13 +7896,13 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>90</v>
@@ -7766,19 +7911,19 @@
         <v>1</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>73</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>1</v>
@@ -7787,18 +7932,18 @@
         <v>49</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>78</v>
@@ -7807,19 +7952,19 @@
         <v>1</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>1</v>
@@ -7833,13 +7978,13 @@
     </row>
     <row r="27" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>78</v>
@@ -7848,19 +7993,19 @@
         <v>1</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>1</v>
@@ -7869,18 +8014,18 @@
         <v>49</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>78</v>
@@ -7889,19 +8034,19 @@
         <v>1</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>73</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>1</v>
@@ -7910,18 +8055,18 @@
         <v>49</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>90</v>
@@ -7930,19 +8075,19 @@
         <v>1</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>73</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="K29" s="8" t="s">
         <v>1</v>
@@ -7951,18 +8096,18 @@
         <v>49</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>90</v>
@@ -7971,19 +8116,19 @@
         <v>1</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>1</v>
@@ -7992,18 +8137,18 @@
         <v>49</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>78</v>
@@ -8012,60 +8157,60 @@
         <v>1</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>73</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>49</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>237</v>
+        <v>791</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>238</v>
+        <v>792</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>239</v>
+        <v>793</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>1</v>
+        <v>794</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>80</v>
+        <v>795</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>241</v>
+        <v>796</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>1</v>
@@ -8074,39 +8219,39 @@
         <v>49</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>237</v>
+        <v>791</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>238</v>
+        <v>798</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>243</v>
+        <v>799</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>1</v>
+        <v>794</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>99</v>
+        <v>800</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>244</v>
+        <v>801</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>1</v>
@@ -8115,39 +8260,39 @@
         <v>49</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>1</v>
+        <v>802</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>245</v>
+        <v>803</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>402</v>
+        <v>804</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>245</v>
+        <v>805</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>99</v>
+        <v>806</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>403</v>
+        <v>807</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>1</v>
@@ -8161,34 +8306,34 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>245</v>
+        <v>803</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>404</v>
+        <v>808</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>245</v>
+        <v>805</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>405</v>
+        <v>809</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>1</v>
@@ -8202,34 +8347,34 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>406</v>
+        <v>810</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>295</v>
+        <v>811</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>407</v>
+        <v>812</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>408</v>
+        <v>813</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>409</v>
+        <v>813</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>1</v>
@@ -8238,39 +8383,39 @@
         <v>49</v>
       </c>
       <c r="M36" s="7" t="s">
-        <v>410</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>411</v>
+        <v>814</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>295</v>
+        <v>811</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>412</v>
+        <v>815</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>1</v>
@@ -8279,39 +8424,39 @@
         <v>49</v>
       </c>
       <c r="M37" s="7" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>414</v>
+        <v>816</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>80</v>
+        <v>817</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>142</v>
+        <v>818</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>362</v>
+        <v>819</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>283</v>
+        <v>820</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>283</v>
+        <v>821</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>1</v>
@@ -8320,39 +8465,39 @@
         <v>49</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>416</v>
+        <v>823</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>80</v>
+        <v>817</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>142</v>
+        <v>818</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>417</v>
+        <v>824</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>1</v>
@@ -8361,39 +8506,39 @@
         <v>49</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>419</v>
+        <v>826</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>80</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>420</v>
+        <v>827</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>1</v>
@@ -8402,39 +8547,39 @@
         <v>49</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>421</v>
+        <v>828</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>264</v>
+        <v>829</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>265</v>
+        <v>830</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>422</v>
+        <v>831</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>1</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>423</v>
+        <v>830</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>1</v>
+        <v>806</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>268</v>
+        <v>811</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>424</v>
+        <v>832</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>425</v>
+        <v>813</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>426</v>
+        <v>813</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>1</v>
@@ -8443,39 +8588,39 @@
         <v>49</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>264</v>
+        <v>829</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>270</v>
+        <v>830</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>427</v>
+        <v>834</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>1</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>423</v>
+        <v>830</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>1</v>
+        <v>806</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>268</v>
+        <v>811</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>428</v>
+        <v>835</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K42" s="8" t="s">
         <v>1</v>
@@ -8484,39 +8629,39 @@
         <v>49</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>1</v>
+        <v>836</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>274</v>
+        <v>837</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>429</v>
+        <v>838</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>1</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>1</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>430</v>
+        <v>839</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>283</v>
+        <v>840</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>283</v>
+        <v>841</v>
       </c>
       <c r="K43" s="8" t="s">
         <v>1</v>
@@ -8526,6 +8671,64 @@
       </c>
       <c r="M43" s="9" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="33" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="H44" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="J44" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="L44" s="14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="33" x14ac:dyDescent="0.3">
+      <c r="A45" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="I45" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="J45" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="L45" s="14" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -8554,190 +8757,190 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>431</v>
+        <v>404</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>432</v>
+        <v>405</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>433</v>
+        <v>406</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>435</v>
+        <v>408</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>38</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>438</v>
+        <v>411</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>439</v>
+        <v>412</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>442</v>
+        <v>415</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>445</v>
+        <v>418</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>79</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>453</v>
+        <v>426</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>455</v>
+        <v>428</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>460</v>
+        <v>433</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>463</v>
+        <v>436</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>464</v>
+        <v>437</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>47</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>465</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>466</v>
+        <v>439</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>467</v>
+        <v>440</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>468</v>
+        <v>441</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>469</v>
+        <v>442</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>470</v>
+        <v>443</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>471</v>
+        <v>444</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>473</v>
+        <v>446</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>47</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>476</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -8839,10 +9042,10 @@
         <v>44</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>540</v>
+        <v>513</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>1</v>
@@ -8881,7 +9084,7 @@
         <v>47</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="R2" s="12" t="s">
         <v>1</v>
@@ -8890,7 +9093,7 @@
         <v>49</v>
       </c>
       <c r="T2" s="13" t="s">
-        <v>479</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -8898,10 +9101,10 @@
         <v>66</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>481</v>
+        <v>454</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>1</v>
@@ -8943,7 +9146,7 @@
         <v>47</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="R3" s="10" t="s">
         <v>1</v>
@@ -8963,7 +9166,7 @@
         <v>58</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>1</v>
@@ -9005,7 +9208,7 @@
         <v>47</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="R4" s="12" t="s">
         <v>1</v>
@@ -9014,7 +9217,7 @@
         <v>49</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="54" x14ac:dyDescent="0.3">
@@ -9022,10 +9225,10 @@
         <v>66</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>1</v>
@@ -9064,10 +9267,10 @@
         <v>1</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="R5" s="10" t="s">
         <v>1</v>
@@ -9087,7 +9290,7 @@
         <v>67</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>1</v>
@@ -9129,13 +9332,13 @@
         <v>73</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="R6" s="10" t="s">
         <v>1</v>
       </c>
       <c r="S6" s="10" t="s">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="T6" s="11" t="s">
         <v>1</v>
@@ -9143,99 +9346,99 @@
     </row>
     <row r="7" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>84</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="G7" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="P7" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="H7" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>495</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>495</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>495</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>495</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>129</v>
-      </c>
       <c r="Q7" s="13" t="s">
-        <v>497</v>
+        <v>470</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="S7" s="12" t="s">
         <v>49</v>
       </c>
       <c r="T7" s="13" t="s">
-        <v>498</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>500</v>
+        <v>473</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>84</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>1</v>
@@ -9247,33 +9450,33 @@
         <v>1</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>503</v>
+        <v>476</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q8" s="13" t="s">
-        <v>504</v>
+        <v>477</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>49</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>498</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>1</v>
@@ -9285,37 +9488,37 @@
         <v>1</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>509</v>
+        <v>482</v>
       </c>
       <c r="R9" s="12" t="s">
         <v>1</v>
@@ -9324,7 +9527,7 @@
         <v>49</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>498</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9332,10 +9535,10 @@
         <v>75</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>510</v>
+        <v>483</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>511</v>
+        <v>484</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>1</v>
@@ -9344,22 +9547,22 @@
         <v>84</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>80</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>512</v>
+        <v>485</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="L10" s="11" t="s">
         <v>1</v>
@@ -9371,22 +9574,22 @@
         <v>1</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>514</v>
+        <v>487</v>
       </c>
       <c r="R10" s="10" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="S10" s="10" t="s">
         <v>49</v>
       </c>
       <c r="T10" s="11" t="s">
-        <v>515</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9394,10 +9597,10 @@
         <v>75</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>516</v>
+        <v>489</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>517</v>
+        <v>490</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>1</v>
@@ -9412,19 +9615,19 @@
         <v>79</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>518</v>
+        <v>491</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>518</v>
+        <v>491</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>518</v>
+        <v>491</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>1</v>
@@ -9433,13 +9636,13 @@
         <v>1</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>519</v>
+        <v>492</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>520</v>
+        <v>493</v>
       </c>
       <c r="Q11" s="11" t="s">
-        <v>521</v>
+        <v>494</v>
       </c>
       <c r="R11" s="10" t="s">
         <v>1</v>
@@ -9453,22 +9656,22 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="12" t="s">
         <v>237</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>240</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>1</v>
@@ -9498,10 +9701,10 @@
         <v>47</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q12" s="13" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="R12" s="12" t="s">
         <v>1</v>
@@ -9515,28 +9718,28 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>240</v>
-      </c>
       <c r="G13" s="12" t="s">
         <v>1</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>1</v>
@@ -9560,10 +9763,10 @@
         <v>1</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="R13" s="12" t="s">
         <v>1</v>
@@ -9577,13 +9780,13 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>522</v>
+        <v>495</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>1</v>
@@ -9592,13 +9795,13 @@
         <v>1</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>1</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>1</v>
@@ -9622,10 +9825,10 @@
         <v>1</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q14" s="13" t="s">
-        <v>523</v>
+        <v>496</v>
       </c>
       <c r="R14" s="12" t="s">
         <v>1</v>
@@ -9634,18 +9837,18 @@
         <v>49</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>524</v>
+        <v>497</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>525</v>
+        <v>498</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>1</v>
@@ -9654,13 +9857,13 @@
         <v>1</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>1</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I15" s="12" t="s">
         <v>1</v>
@@ -9684,10 +9887,10 @@
         <v>1</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>526</v>
+        <v>499</v>
       </c>
       <c r="R15" s="12" t="s">
         <v>1</v>
@@ -9701,13 +9904,13 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>1</v>
@@ -9716,13 +9919,13 @@
         <v>1</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>1</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>1</v>
@@ -9746,16 +9949,16 @@
         <v>1</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q16" s="13" t="s">
-        <v>528</v>
+        <v>501</v>
       </c>
       <c r="R16" s="12" t="s">
         <v>1</v>
       </c>
       <c r="S16" s="12" t="s">
-        <v>529</v>
+        <v>502</v>
       </c>
       <c r="T16" s="13" t="s">
         <v>1</v>
@@ -9763,13 +9966,13 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>530</v>
+        <v>503</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>531</v>
+        <v>504</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>1</v>
@@ -9778,7 +9981,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>1</v>
@@ -9808,10 +10011,10 @@
         <v>1</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>532</v>
+        <v>505</v>
       </c>
       <c r="R17" s="12" t="s">
         <v>1</v>
@@ -9820,60 +10023,60 @@
         <v>49</v>
       </c>
       <c r="T17" s="13" t="s">
-        <v>533</v>
+        <v>506</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B18" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>534</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="O18" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="P18" s="10" t="s">
-        <v>268</v>
-      </c>
       <c r="Q18" s="11" t="s">
-        <v>535</v>
+        <v>508</v>
       </c>
       <c r="R18" s="10" t="s">
         <v>1</v>
@@ -9887,13 +10090,13 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>536</v>
+        <v>509</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>1</v>
@@ -9902,7 +10105,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>1</v>
@@ -9932,10 +10135,10 @@
         <v>1</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>537</v>
+        <v>510</v>
       </c>
       <c r="R19" s="10" t="s">
         <v>1</v>
@@ -9949,13 +10152,13 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>538</v>
+        <v>511</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>1</v>
@@ -9964,7 +10167,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>1</v>
@@ -9994,10 +10197,10 @@
         <v>1</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>539</v>
+        <v>512</v>
       </c>
       <c r="R20" s="10" t="s">
         <v>1</v>
@@ -10032,7 +10235,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>26</v>
@@ -10041,13 +10244,13 @@
         <v>24</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>542</v>
+        <v>515</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>543</v>
+        <v>516</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>544</v>
+        <v>517</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>43</v>
@@ -10055,91 +10258,91 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>546</v>
+        <v>519</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>548</v>
+        <v>521</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>549</v>
+        <v>522</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>550</v>
+        <v>523</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>551</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>552</v>
+        <v>525</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>553</v>
+        <v>526</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>549</v>
+        <v>522</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>550</v>
+        <v>523</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>551</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>554</v>
+        <v>527</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>555</v>
+        <v>528</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>549</v>
+        <v>522</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>550</v>
+        <v>523</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>556</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>557</v>
+        <v>530</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>558</v>
+        <v>531</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>559</v>
+        <v>532</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>560</v>
+        <v>533</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>1</v>
@@ -10147,22 +10350,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>561</v>
+        <v>534</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>562</v>
+        <v>535</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>559</v>
+        <v>532</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>550</v>
+        <v>523</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>1</v>
@@ -10170,22 +10373,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>563</v>
+        <v>536</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>564</v>
+        <v>537</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>565</v>
+        <v>538</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>566</v>
+        <v>539</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>1</v>
@@ -10193,117 +10396,117 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>567</v>
+        <v>540</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>568</v>
+        <v>541</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>569</v>
+        <v>542</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>570</v>
+        <v>543</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>47</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>556</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>572</v>
-      </c>
       <c r="E9" s="8" t="s">
-        <v>559</v>
+        <v>532</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>550</v>
+        <v>523</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>573</v>
+        <v>546</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>574</v>
+        <v>547</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>575</v>
+        <v>548</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>559</v>
+        <v>532</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>550</v>
+        <v>523</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>576</v>
+        <v>549</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>577</v>
+        <v>550</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>578</v>
+        <v>551</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>579</v>
+        <v>552</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>580</v>
+        <v>553</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>47</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>581</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>582</v>
+        <v>555</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>578</v>
+        <v>551</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>583</v>
+        <v>556</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>559</v>
+        <v>532</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>584</v>
+        <v>557</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>585</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -10328,19 +10531,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>586</v>
+        <v>559</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>587</v>
+        <v>560</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>588</v>
+        <v>561</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>589</v>
+        <v>562</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>590</v>
+        <v>563</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>40</v>
@@ -10351,22 +10554,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>577</v>
+        <v>550</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>594</v>
+        <v>567</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>49</v>
@@ -10374,22 +10577,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>595</v>
+        <v>568</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>596</v>
+        <v>569</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>49</v>
@@ -10397,22 +10600,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>597</v>
+        <v>570</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>598</v>
+        <v>571</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>49</v>
@@ -10420,22 +10623,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>599</v>
+        <v>572</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>600</v>
+        <v>573</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>49</v>
@@ -10443,22 +10646,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>601</v>
+        <v>574</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>602</v>
+        <v>575</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>49</v>
@@ -10466,22 +10669,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>603</v>
+        <v>576</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>604</v>
+        <v>577</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>49</v>
@@ -10489,22 +10692,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>605</v>
+        <v>578</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>606</v>
+        <v>579</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>49</v>
@@ -10512,22 +10715,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>607</v>
+        <v>580</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>608</v>
+        <v>581</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>49</v>
@@ -10535,22 +10738,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>609</v>
+        <v>582</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>610</v>
+        <v>583</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>49</v>
@@ -10558,22 +10761,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>614</v>
+        <v>587</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>49</v>
@@ -10581,22 +10784,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>615</v>
+        <v>588</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>616</v>
+        <v>589</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>49</v>
@@ -10604,22 +10807,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>617</v>
+        <v>590</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>618</v>
+        <v>591</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>49</v>
@@ -10627,22 +10830,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>619</v>
+        <v>592</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>620</v>
+        <v>593</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>49</v>
@@ -10650,22 +10853,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>621</v>
+        <v>594</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>622</v>
+        <v>595</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>49</v>
@@ -10673,22 +10876,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>623</v>
+        <v>596</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>624</v>
+        <v>597</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>49</v>
@@ -10696,45 +10899,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>625</v>
+        <v>598</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>626</v>
+        <v>599</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>627</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>628</v>
+        <v>601</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>629</v>
+        <v>602</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>49</v>
@@ -10742,22 +10945,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>605</v>
+        <v>578</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>630</v>
+        <v>603</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>49</v>
@@ -10765,22 +10968,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>634</v>
+        <v>607</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>635</v>
+        <v>608</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>49</v>
@@ -10788,22 +10991,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>636</v>
+        <v>609</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>637</v>
+        <v>610</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>49</v>
@@ -10811,22 +11014,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>639</v>
+        <v>612</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>49</v>
@@ -10834,22 +11037,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>640</v>
+        <v>613</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>641</v>
+        <v>614</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>49</v>
@@ -10857,22 +11060,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>642</v>
+        <v>615</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>643</v>
+        <v>616</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>49</v>
@@ -10880,22 +11083,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>644</v>
+        <v>617</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>645</v>
+        <v>618</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>49</v>
@@ -10903,22 +11106,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>646</v>
+        <v>619</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>647</v>
+        <v>620</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>49</v>
@@ -10926,22 +11129,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>648</v>
+        <v>621</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>649</v>
+        <v>622</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>49</v>
@@ -10949,183 +11152,183 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>650</v>
+        <v>623</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>651</v>
+        <v>624</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>652</v>
+        <v>625</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>655</v>
+        <v>628</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>656</v>
+        <v>629</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>657</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>658</v>
+        <v>631</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>659</v>
+        <v>632</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>657</v>
+        <v>630</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>660</v>
+        <v>633</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>657</v>
+        <v>630</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>662</v>
+        <v>635</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>663</v>
+        <v>636</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>657</v>
+        <v>630</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>664</v>
+        <v>637</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>665</v>
+        <v>638</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>657</v>
+        <v>630</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>666</v>
+        <v>639</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>667</v>
+        <v>640</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>657</v>
+        <v>630</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>668</v>
+        <v>641</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>669</v>
+        <v>642</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>49</v>
@@ -11133,68 +11336,68 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>670</v>
+        <v>643</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>671</v>
+        <v>644</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>672</v>
+        <v>645</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>673</v>
+        <v>646</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>674</v>
+        <v>647</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>675</v>
+        <v>648</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>678</v>
+        <v>651</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>679</v>
+        <v>652</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>49</v>
@@ -11202,22 +11405,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>680</v>
+        <v>653</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>681</v>
+        <v>654</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>49</v>
@@ -11225,22 +11428,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>682</v>
+        <v>655</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>683</v>
+        <v>656</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>49</v>
@@ -11248,22 +11451,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>684</v>
+        <v>657</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>685</v>
+        <v>658</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>49</v>
@@ -11271,22 +11474,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>686</v>
+        <v>659</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>687</v>
+        <v>660</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>49</v>
@@ -11294,22 +11497,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>688</v>
+        <v>661</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>689</v>
+        <v>662</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>49</v>
@@ -11317,45 +11520,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>690</v>
+        <v>663</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>691</v>
+        <v>664</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>692</v>
+        <v>665</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>693</v>
+        <v>666</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>694</v>
+        <v>667</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>49</v>
@@ -11363,22 +11566,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>695</v>
+        <v>668</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>696</v>
+        <v>669</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>49</v>
@@ -11386,22 +11589,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>697</v>
+        <v>670</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>698</v>
+        <v>671</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>699</v>
+        <v>672</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>49</v>
@@ -11409,22 +11612,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>697</v>
+        <v>670</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>700</v>
+        <v>673</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>701</v>
+        <v>674</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>49</v>
@@ -11432,22 +11635,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>697</v>
+        <v>670</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>702</v>
+        <v>675</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>703</v>
+        <v>676</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>49</v>
@@ -11455,22 +11658,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>697</v>
+        <v>670</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>561</v>
+        <v>534</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>704</v>
+        <v>677</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>49</v>
@@ -11478,22 +11681,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>697</v>
+        <v>670</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>705</v>
+        <v>678</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>706</v>
+        <v>679</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>49</v>
@@ -11501,22 +11704,22 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>697</v>
+        <v>670</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>619</v>
+        <v>592</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>707</v>
+        <v>680</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>49</v>
@@ -11524,22 +11727,22 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>697</v>
+        <v>670</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>708</v>
+        <v>681</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>709</v>
+        <v>682</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>49</v>
@@ -11547,22 +11750,22 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>697</v>
+        <v>670</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>530</v>
+        <v>503</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>710</v>
+        <v>683</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>49</v>
@@ -11570,22 +11773,22 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>697</v>
+        <v>670</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>605</v>
+        <v>578</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>711</v>
+        <v>684</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>49</v>
@@ -11593,68 +11796,68 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>715</v>
+        <v>688</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>716</v>
+        <v>689</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>717</v>
+        <v>690</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>718</v>
+        <v>691</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>719</v>
+        <v>692</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>717</v>
+        <v>690</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>720</v>
+        <v>693</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>721</v>
+        <v>694</v>
       </c>
       <c r="G58" s="8" t="s">
         <v>49</v>
@@ -11662,22 +11865,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>722</v>
+        <v>695</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>723</v>
+        <v>696</v>
       </c>
       <c r="G59" s="8" t="s">
         <v>49</v>
@@ -11685,22 +11888,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>724</v>
+        <v>697</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>725</v>
+        <v>698</v>
       </c>
       <c r="G60" s="8" t="s">
         <v>49</v>
@@ -11708,22 +11911,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>726</v>
+        <v>699</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>727</v>
+        <v>700</v>
       </c>
       <c r="G61" s="8" t="s">
         <v>49</v>
@@ -11731,22 +11934,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>728</v>
+        <v>701</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>729</v>
+        <v>702</v>
       </c>
       <c r="G62" s="8" t="s">
         <v>49</v>
@@ -11754,22 +11957,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>730</v>
+        <v>703</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>731</v>
+        <v>704</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>49</v>
@@ -11777,22 +11980,22 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>732</v>
+        <v>705</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>733</v>
+        <v>706</v>
       </c>
       <c r="G64" s="8" t="s">
         <v>49</v>
@@ -11820,10 +12023,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>734</v>
+        <v>707</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>735</v>
+        <v>708</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>30</v>
@@ -11832,10 +12035,10 @@
         <v>32</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>736</v>
+        <v>709</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>43</v>
@@ -11843,10 +12046,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>737</v>
+        <v>710</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>738</v>
+        <v>711</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>79</v>
@@ -11855,44 +12058,44 @@
         <v>81</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>739</v>
+        <v>712</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>740</v>
+        <v>713</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>741</v>
+        <v>714</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>742</v>
+        <v>715</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>743</v>
+        <v>716</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>744</v>
+        <v>717</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>745</v>
+        <v>718</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>746</v>
+        <v>719</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>747</v>
+        <v>720</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>748</v>
+        <v>721</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>47</v>
@@ -11904,18 +12107,18 @@
         <v>47</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>749</v>
+        <v>722</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>750</v>
+        <v>723</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>751</v>
+        <v>724</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>752</v>
+        <v>725</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>47</v>
@@ -11927,64 +12130,64 @@
         <v>47</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>753</v>
+        <v>726</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>754</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>755</v>
+        <v>728</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>756</v>
+        <v>729</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>744</v>
+        <v>717</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>757</v>
+        <v>730</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>758</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>755</v>
+        <v>728</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>759</v>
+        <v>732</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="E7" s="8" t="s">
-        <v>744</v>
+        <v>717</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>760</v>
+        <v>733</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>761</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>755</v>
+        <v>728</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>762</v>
+        <v>735</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>47</v>
@@ -11996,10 +12199,10 @@
         <v>47</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>763</v>
+        <v>736</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>764</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\w0917\build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2D29FA-A195-4192-85D6-10E671ED1769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8642E5F2-B573-4D5D-999F-B91ADFA5756F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" activeTab="1" xr2:uid="{7AA41AD5-58C0-40E4-A758-A338A1BB80B4}"/>
   </bookViews>
@@ -2551,10 +2551,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>미구현(전량소모 위력전환 신설 필요) · 09-16 신설, 닥치는 대로(올라프)와 같은 비용 감소 구조</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>공용</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2716,6 +2712,10 @@
   </si>
   <si>
     <t>위력·범위 미정 · 09-16 문턱 −70 → −30 · 보너스 6 → 4 · 09-14 브레인스토밍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본위력은 빛 2 기준 고정(09-17) · 09-16 신설, 닥치는 대로(올라프)와 같은 비용 감소 구조</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6068,7 +6068,7 @@
         <v>140</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="R43" s="8" t="s">
         <v>1</v>
@@ -6077,7 +6077,7 @@
         <v>93</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -8260,7 +8260,7 @@
         <v>49</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -8268,25 +8268,25 @@
         <v>234</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>803</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="D34" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>804</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="6" t="s">
+      <c r="F34" s="6" t="s">
         <v>805</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>806</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>280</v>
@@ -8309,16 +8309,16 @@
         <v>234</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>97</v>
@@ -8327,7 +8327,7 @@
         <v>140</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>280</v>
@@ -8353,7 +8353,7 @@
         <v>242</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>1</v>
@@ -8365,16 +8365,16 @@
         <v>97</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="H36" s="7" t="s">
         <v>811</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="I36" s="7" t="s">
         <v>812</v>
       </c>
-      <c r="I36" s="7" t="s">
-        <v>813</v>
-      </c>
       <c r="J36" s="7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>1</v>
@@ -8394,7 +8394,7 @@
         <v>242</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>1</v>
@@ -8406,10 +8406,10 @@
         <v>97</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>280</v>
@@ -8435,7 +8435,7 @@
         <v>242</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>1</v>
@@ -8444,19 +8444,19 @@
         <v>242</v>
       </c>
       <c r="F38" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>817</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="7" t="s">
         <v>818</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="I38" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="J38" s="7" t="s">
         <v>820</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>821</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>1</v>
@@ -8465,7 +8465,7 @@
         <v>49</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -8476,7 +8476,7 @@
         <v>242</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>1</v>
@@ -8485,13 +8485,13 @@
         <v>242</v>
       </c>
       <c r="F39" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="G39" s="6" t="s">
         <v>817</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>818</v>
-      </c>
       <c r="H39" s="7" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I39" s="7" t="s">
         <v>280</v>
@@ -8506,7 +8506,7 @@
         <v>49</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -8517,7 +8517,7 @@
         <v>242</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>1</v>
@@ -8532,7 +8532,7 @@
         <v>140</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>280</v>
@@ -8547,39 +8547,39 @@
         <v>49</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="C41" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="D41" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>831</v>
       </c>
-      <c r="D41" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>830</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>806</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>832</v>
-      </c>
       <c r="I41" s="9" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>1</v>
@@ -8588,33 +8588,33 @@
         <v>49</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="B42" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>830</v>
-      </c>
       <c r="C42" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="H42" s="9" t="s">
         <v>834</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>830</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>806</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>835</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>280</v>
@@ -8629,7 +8629,7 @@
         <v>49</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -8637,10 +8637,10 @@
         <v>261</v>
       </c>
       <c r="B43" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>837</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>838</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>1</v>
@@ -8655,13 +8655,13 @@
         <v>265</v>
       </c>
       <c r="H43" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="I43" s="9" t="s">
         <v>839</v>
       </c>
-      <c r="I43" s="9" t="s">
+      <c r="J43" s="9" t="s">
         <v>840</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>841</v>
       </c>
       <c r="K43" s="8" t="s">
         <v>1</v>

--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\rules0920\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{789276CE-6A7E-4613-9CD5-5FD9195B588A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5ACC519-25E7-450A-B3BF-084B66D2F19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{E6D2DAD6-2FAD-43BB-8864-AC0B94FE5C92}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{8D45844E-E7DF-4998-91E8-83D1A27C05A5}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -2981,7 +2981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{548EC55A-DB1F-4798-ACF9-DD6576905F0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32CDDAE4-47F2-4BC0-91FA-953FAB634DDC}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3171,7 +3171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD3B705-EEA5-4DA0-94E8-BBF60FA1016F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6374CB9F-5415-4648-AFAA-E79F8EF00482}">
   <dimension ref="A1:T56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5821,13 +5821,13 @@
         <v>100</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="L43" s="9" t="s">
         <v>1</v>
@@ -5883,16 +5883,16 @@
         <v>100</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="M44" s="9" t="s">
         <v>1</v>
@@ -6664,14 +6664,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T56" xr:uid="{BBD3B705-EEA5-4DA0-94E8-BBF60FA1016F}"/>
+  <autoFilter ref="A1:T56" xr:uid="{6374CB9F-5415-4648-AFAA-E79F8EF00482}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CDC2679-C050-4188-BF80-BA1FFF8A3621}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE14A73D-48F8-460B-B958-9FF719EBEC8B}">
   <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8533,14 +8533,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M45" xr:uid="{3CDC2679-C050-4188-BF80-BA1FFF8A3621}"/>
+  <autoFilter ref="A1:M45" xr:uid="{BE14A73D-48F8-460B-B958-9FF719EBEC8B}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28565A5-6F83-40D2-89A4-FC64B234BBB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FDBBE40-185C-4626-B767-4BC61171D75B}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8745,14 +8745,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{B28565A5-6F83-40D2-89A4-FC64B234BBB2}"/>
+  <autoFilter ref="A1:O4" xr:uid="{7FDBBE40-185C-4626-B767-4BC61171D75B}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ACB417E-F64B-4311-A7DD-F576F86A6080}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68926BD8-3232-4A6B-9846-9CDAEF3EE25D}">
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10014,14 +10014,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T20" xr:uid="{3ACB417E-F64B-4311-A7DD-F576F86A6080}"/>
+  <autoFilter ref="A1:T20" xr:uid="{68926BD8-3232-4A6B-9846-9CDAEF3EE25D}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02D69DB4-5D8E-491F-B00D-182737D8F2DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BBD6ABB-C5BA-40E2-9C63-9B7CE9D50924}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10311,14 +10311,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12" xr:uid="{02D69DB4-5D8E-491F-B00D-182737D8F2DD}"/>
+  <autoFilter ref="A1:G12" xr:uid="{1BBD6ABB-C5BA-40E2-9C63-9B7CE9D50924}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B609ECA7-D028-4A91-BED9-622DB03B9FB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E8861A8-F2F3-4EDF-A52C-0BF345E8CC5A}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11803,14 +11803,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{B609ECA7-D028-4A91-BED9-622DB03B9FB7}"/>
+  <autoFilter ref="A1:G64" xr:uid="{4E8861A8-F2F3-4EDF-A52C-0BF345E8CC5A}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{711062FF-3F2F-4E91-97CE-63DA61CE1180}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFE908E-1435-4116-AC8E-93AEE648C994}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12007,7 +12007,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{711062FF-3F2F-4E91-97CE-63DA61CE1180}"/>
+  <autoFilter ref="A1:G8" xr:uid="{DDFE908E-1435-4116-AC8E-93AEE648C994}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\rules0920\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5ACC519-25E7-450A-B3BF-084B66D2F19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD5AFB26-2B6F-44F4-BE27-8553BF05E813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{8D45844E-E7DF-4998-91E8-83D1A27C05A5}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{B25AA7F4-E330-47F0-A9A5-8C0CF9C4D4EF}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -651,7 +651,7 @@
     <t>단칼</t>
   </si>
   <si>
-    <t>22</t>
+    <t>24~29</t>
   </si>
   <si>
     <t>위력 22~27 시뮬 검증 대기</t>
@@ -672,6 +672,9 @@
     <t>피의돌진</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>승리시 / 패배시</t>
   </si>
   <si>
@@ -721,9 +724,6 @@
   </si>
   <si>
     <t>정면승부</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>승리시 준 피해의 25%만큼 자신도 피해</t>
@@ -2981,7 +2981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32CDDAE4-47F2-4BC0-91FA-953FAB634DDC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D6F3CB-9FE0-404D-BB2C-0AF7B2A35ED9}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3171,7 +3171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6374CB9F-5415-4648-AFAA-E79F8EF00482}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1C1BE60-2E2B-4015-A613-CABDBACBC969}">
   <dimension ref="A1:T56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4767,10 +4767,10 @@
         <v>100</v>
       </c>
       <c r="I26" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>109</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>1</v>
@@ -4891,13 +4891,13 @@
         <v>100</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>108</v>
+        <v>205</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="L28" s="9" t="s">
         <v>1</v>
@@ -4912,10 +4912,10 @@
         <v>84</v>
       </c>
       <c r="P28" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q28" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R28" s="9" t="s">
         <v>1</v>
@@ -4932,10 +4932,10 @@
         <v>184</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>1</v>
@@ -4977,7 +4977,7 @@
         <v>73</v>
       </c>
       <c r="Q29" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R29" s="9" t="s">
         <v>1</v>
@@ -4994,10 +4994,10 @@
         <v>184</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>1</v>
@@ -5036,10 +5036,10 @@
         <v>84</v>
       </c>
       <c r="P30" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q30" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R30" s="9" t="s">
         <v>1</v>
@@ -5056,10 +5056,10 @@
         <v>184</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>1</v>
@@ -5080,10 +5080,10 @@
         <v>108</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L31" s="9" t="s">
         <v>1</v>
@@ -5098,13 +5098,13 @@
         <v>84</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q31" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R31" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S31" s="9" t="s">
         <v>95</v>
@@ -5118,10 +5118,10 @@
         <v>184</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>1</v>
@@ -5139,7 +5139,7 @@
         <v>80</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>116</v>
@@ -5166,7 +5166,7 @@
         <v>223</v>
       </c>
       <c r="R32" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S32" s="9" t="s">
         <v>95</v>
@@ -5180,7 +5180,7 @@
         <v>184</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>225</v>
@@ -5242,7 +5242,7 @@
         <v>184</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>227</v>
@@ -5263,7 +5263,7 @@
         <v>99</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>116</v>
@@ -5304,7 +5304,7 @@
         <v>184</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>229</v>
@@ -5366,7 +5366,7 @@
         <v>184</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>232</v>
@@ -5414,7 +5414,7 @@
         <v>233</v>
       </c>
       <c r="R36" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S36" s="9" t="s">
         <v>95</v>
@@ -5662,7 +5662,7 @@
         <v>250</v>
       </c>
       <c r="R40" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S40" s="9" t="s">
         <v>95</v>
@@ -5724,7 +5724,7 @@
         <v>254</v>
       </c>
       <c r="R41" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S41" s="9" t="s">
         <v>95</v>
@@ -5910,7 +5910,7 @@
         <v>266</v>
       </c>
       <c r="R44" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S44" s="9" t="s">
         <v>95</v>
@@ -6664,14 +6664,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T56" xr:uid="{6374CB9F-5415-4648-AFAA-E79F8EF00482}"/>
+  <autoFilter ref="A1:T56" xr:uid="{D1C1BE60-2E2B-4015-A613-CABDBACBC969}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE14A73D-48F8-460B-B958-9FF719EBEC8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32692565-A92E-405F-B272-AC126496E59D}">
   <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7006,7 +7006,7 @@
         <v>337</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>49</v>
@@ -7700,7 +7700,7 @@
         <v>403</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>1</v>
@@ -8533,14 +8533,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M45" xr:uid="{BE14A73D-48F8-460B-B958-9FF719EBEC8B}"/>
+  <autoFilter ref="A1:M45" xr:uid="{32692565-A92E-405F-B272-AC126496E59D}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FDBBE40-185C-4626-B767-4BC61171D75B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3933B33D-4A07-4D1C-B129-3E8AF763D579}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8745,14 +8745,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{7FDBBE40-185C-4626-B767-4BC61171D75B}"/>
+  <autoFilter ref="A1:O4" xr:uid="{3933B33D-4A07-4D1C-B129-3E8AF763D579}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68926BD8-3232-4A6B-9846-9CDAEF3EE25D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C976EFE9-178F-400D-88BF-CE4BB0F2C150}">
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10014,14 +10014,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T20" xr:uid="{68926BD8-3232-4A6B-9846-9CDAEF3EE25D}"/>
+  <autoFilter ref="A1:T20" xr:uid="{C976EFE9-178F-400D-88BF-CE4BB0F2C150}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BBD6ABB-C5BA-40E2-9C63-9B7CE9D50924}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92E5AFF6-675A-4CE8-AE1B-11034D6F1098}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10311,14 +10311,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12" xr:uid="{1BBD6ABB-C5BA-40E2-9C63-9B7CE9D50924}"/>
+  <autoFilter ref="A1:G12" xr:uid="{92E5AFF6-675A-4CE8-AE1B-11034D6F1098}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E8861A8-F2F3-4EDF-A52C-0BF345E8CC5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDCDF39B-34CC-407C-AA0C-B72C3BCC442B}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11803,14 +11803,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{4E8861A8-F2F3-4EDF-A52C-0BF345E8CC5A}"/>
+  <autoFilter ref="A1:G64" xr:uid="{DDCDF39B-34CC-407C-AA0C-B72C3BCC442B}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFE908E-1435-4116-AC8E-93AEE648C994}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B593E7CD-4A6C-4D86-A2A5-73857F43EC2F}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12007,7 +12007,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{DDFE908E-1435-4116-AC8E-93AEE648C994}"/>
+  <autoFilter ref="A1:G8" xr:uid="{B593E7CD-4A6C-4D86-A2A5-73857F43EC2F}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\rules0920\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD5AFB26-2B6F-44F4-BE27-8553BF05E813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{258701BA-1633-4C90-B9F6-1C88FFB03845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{B25AA7F4-E330-47F0-A9A5-8C0CF9C4D4EF}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{10BC4F5A-0440-41CD-A1D9-E2289C41BC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -2981,7 +2981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D6F3CB-9FE0-404D-BB2C-0AF7B2A35ED9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DFC3BFE-2383-41FC-85D4-01BD810F74C0}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3171,7 +3171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1C1BE60-2E2B-4015-A613-CABDBACBC969}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4FF32DF-2DF4-412F-A302-55337ACC824B}">
   <dimension ref="A1:T56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5387,13 +5387,13 @@
         <v>80</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>189</v>
+        <v>121</v>
       </c>
       <c r="L36" s="9" t="s">
         <v>1</v>
@@ -6664,14 +6664,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T56" xr:uid="{D1C1BE60-2E2B-4015-A613-CABDBACBC969}"/>
+  <autoFilter ref="A1:T56" xr:uid="{F4FF32DF-2DF4-412F-A302-55337ACC824B}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32692565-A92E-405F-B272-AC126496E59D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{498ECBB7-5962-43B6-83FC-747230D569D5}">
   <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8533,14 +8533,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M45" xr:uid="{32692565-A92E-405F-B272-AC126496E59D}"/>
+  <autoFilter ref="A1:M45" xr:uid="{498ECBB7-5962-43B6-83FC-747230D569D5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3933B33D-4A07-4D1C-B129-3E8AF763D579}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6CA4652-9A0E-46F6-B9FC-D3BB3D5510F8}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8745,14 +8745,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{3933B33D-4A07-4D1C-B129-3E8AF763D579}"/>
+  <autoFilter ref="A1:O4" xr:uid="{B6CA4652-9A0E-46F6-B9FC-D3BB3D5510F8}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C976EFE9-178F-400D-88BF-CE4BB0F2C150}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE4B0A8-202D-41B9-81E3-1C481053300A}">
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10014,14 +10014,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T20" xr:uid="{C976EFE9-178F-400D-88BF-CE4BB0F2C150}"/>
+  <autoFilter ref="A1:T20" xr:uid="{FAE4B0A8-202D-41B9-81E3-1C481053300A}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92E5AFF6-675A-4CE8-AE1B-11034D6F1098}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99AF16C9-9EED-44D6-87BE-ADD8E201269A}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10311,14 +10311,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12" xr:uid="{92E5AFF6-675A-4CE8-AE1B-11034D6F1098}"/>
+  <autoFilter ref="A1:G12" xr:uid="{99AF16C9-9EED-44D6-87BE-ADD8E201269A}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDCDF39B-34CC-407C-AA0C-B72C3BCC442B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF797D89-C39E-48D6-B08F-B448D7BDD043}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11803,14 +11803,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{DDCDF39B-34CC-407C-AA0C-B72C3BCC442B}"/>
+  <autoFilter ref="A1:G64" xr:uid="{BF797D89-C39E-48D6-B08F-B448D7BDD043}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B593E7CD-4A6C-4D86-A2A5-73857F43EC2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB41508-BF67-448B-82D5-CDC8C7CA3A99}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12007,7 +12007,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{B593E7CD-4A6C-4D86-A2A5-73857F43EC2F}"/>
+  <autoFilter ref="A1:G8" xr:uid="{4FB41508-BF67-448B-82D5-CDC8C7CA3A99}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\rules0920\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{258701BA-1633-4C90-B9F6-1C88FFB03845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{834CF73F-4920-4130-AAF9-30ACB9C81563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{10BC4F5A-0440-41CD-A1D9-E2289C41BC7F}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{896209DD-570F-4AD5-A340-1FF40D3A2D84}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -726,7 +726,7 @@
     <t>정면승부</t>
   </si>
   <si>
-    <t>승리시 준 피해의 25%만큼 자신도 피해</t>
+    <t>승리시 준 피해의 10%만큼 자신도 피해</t>
   </si>
   <si>
     <t>09-15 조정(위력 12 → 15, 자해 50% → 25%)</t>
@@ -765,7 +765,7 @@
     <t>전부 걸다</t>
   </si>
   <si>
-    <t>19~26</t>
+    <t>11~18</t>
   </si>
   <si>
     <t>승리시 / 매칭시</t>
@@ -2981,7 +2981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DFC3BFE-2383-41FC-85D4-01BD810F74C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90C5F7C-03DD-421D-89F6-1E00EA0121EA}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3171,7 +3171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4FF32DF-2DF4-412F-A302-55337ACC824B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33565FB0-C4EA-453C-8BA9-CFC616FC051E}">
   <dimension ref="A1:T56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5449,16 +5449,16 @@
         <v>99</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>92</v>
+        <v>236</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>236</v>
+        <v>165</v>
       </c>
       <c r="M37" s="9" t="s">
         <v>1</v>
@@ -6664,14 +6664,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T56" xr:uid="{F4FF32DF-2DF4-412F-A302-55337ACC824B}"/>
+  <autoFilter ref="A1:T56" xr:uid="{33565FB0-C4EA-453C-8BA9-CFC616FC051E}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{498ECBB7-5962-43B6-83FC-747230D569D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F00B95F-8D4B-4D75-9B62-28E919616EAD}">
   <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8533,14 +8533,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M45" xr:uid="{498ECBB7-5962-43B6-83FC-747230D569D5}"/>
+  <autoFilter ref="A1:M45" xr:uid="{0F00B95F-8D4B-4D75-9B62-28E919616EAD}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6CA4652-9A0E-46F6-B9FC-D3BB3D5510F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC72440-4B50-4472-AF6F-3CD7035E73BB}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8745,14 +8745,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{B6CA4652-9A0E-46F6-B9FC-D3BB3D5510F8}"/>
+  <autoFilter ref="A1:O4" xr:uid="{8AC72440-4B50-4472-AF6F-3CD7035E73BB}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE4B0A8-202D-41B9-81E3-1C481053300A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A98747F9-AF54-4C30-8E77-0E4445E58771}">
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10014,14 +10014,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T20" xr:uid="{FAE4B0A8-202D-41B9-81E3-1C481053300A}"/>
+  <autoFilter ref="A1:T20" xr:uid="{A98747F9-AF54-4C30-8E77-0E4445E58771}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99AF16C9-9EED-44D6-87BE-ADD8E201269A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96CBB6C7-525A-4F0E-95E3-7F07E1034BD0}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10311,14 +10311,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12" xr:uid="{99AF16C9-9EED-44D6-87BE-ADD8E201269A}"/>
+  <autoFilter ref="A1:G12" xr:uid="{96CBB6C7-525A-4F0E-95E3-7F07E1034BD0}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF797D89-C39E-48D6-B08F-B448D7BDD043}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A59096FA-140B-4BF1-B7E7-CE7C321DFA0F}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11803,14 +11803,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{BF797D89-C39E-48D6-B08F-B448D7BDD043}"/>
+  <autoFilter ref="A1:G64" xr:uid="{A59096FA-140B-4BF1-B7E7-CE7C321DFA0F}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB41508-BF67-448B-82D5-CDC8C7CA3A99}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD57149B-6272-446B-B134-BE871BBCC578}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12007,7 +12007,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{4FB41508-BF67-448B-82D5-CDC8C7CA3A99}"/>
+  <autoFilter ref="A1:G8" xr:uid="{FD57149B-6272-446B-B134-BE871BBCC578}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\rules0920\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{834CF73F-4920-4130-AAF9-30ACB9C81563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D42C7F3F-5361-4231-AA05-7487D852E88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{896209DD-570F-4AD5-A340-1FF40D3A2D84}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{C3F1349F-CDDF-4C54-A7A7-1DCD15F95085}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="804">
   <si>
     <t>Project Abyss — 캐릭터 스킬 스펙 (2026-09-13)</t>
   </si>
@@ -663,6 +663,9 @@
     <t>미쳐물어뜯기</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>출혈 1~3 무작위</t>
   </si>
   <si>
@@ -672,9 +675,6 @@
     <t>피의돌진</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>승리시 / 패배시</t>
   </si>
   <si>
@@ -687,586 +687,589 @@
     <t>물고 늘어지기</t>
   </si>
   <si>
+    <t>다음 턴 상대에게 균열 2만큼 2턴 부여</t>
+  </si>
+  <si>
+    <t>형3 심화</t>
+  </si>
+  <si>
+    <t>제살깎기</t>
+  </si>
+  <si>
+    <t>승리시 / 패배시 / 매칭시</t>
+  </si>
+  <si>
+    <t>1번째: 승리시 광기 +1 · 패배시 자기 흐트러짐 −20 / 2번째: 매칭시 광기 +4</t>
+  </si>
+  <si>
+    <t>형3 가교</t>
+  </si>
+  <si>
+    <t>물러서지않기</t>
+  </si>
+  <si>
+    <t>12~25</t>
+  </si>
+  <si>
+    <t>13~24</t>
+  </si>
+  <si>
+    <t>자기 약화 부위 개수당 위력 +2 · 승리시 광기 +1 · 패배시 광기 +1 (라그나로크 지속 중 +3)</t>
+  </si>
+  <si>
+    <t>파괴 권한</t>
+  </si>
+  <si>
+    <t>유연</t>
+  </si>
+  <si>
+    <t>정면승부</t>
+  </si>
+  <si>
+    <t>승리시 준 피해의 10%만큼 자신도 피해</t>
+  </si>
+  <si>
+    <t>09-15 조정(위력 12 → 15, 자해 50% → 25%)</t>
+  </si>
+  <si>
+    <t>위세를 지피다</t>
+  </si>
+  <si>
+    <t>위세 게이지 충전 — 상대 출혈 0~4 / 5~9 / 10+ → +3 / +6 / +10</t>
+  </si>
+  <si>
+    <t>굳히기</t>
+  </si>
+  <si>
+    <t>자신 힘(다음 턴) — 상대 출혈 0~4 / 5~9 / 10+ → +1 / +2 / +3</t>
+  </si>
+  <si>
+    <t>몸을 사리다</t>
+  </si>
+  <si>
+    <t>다음 턴 자신에게 보호 1만큼 1턴 부여</t>
+  </si>
+  <si>
+    <t>빛 09-20 조정(2 -&gt; 1)</t>
+  </si>
+  <si>
+    <t>허를 찌르다</t>
+  </si>
+  <si>
+    <t>상대 균열 / 골절 / 쇠약 무작위 1 (다음 턴). 이 스킬로 부위 파괴 · 처치 시 빛 +1 즉시 + 광기 +2</t>
+  </si>
+  <si>
+    <t>신규</t>
+  </si>
+  <si>
+    <t>전부 걸다</t>
+  </si>
+  <si>
+    <t>11~18</t>
+  </si>
+  <si>
+    <t>승리시 / 매칭시</t>
+  </si>
+  <si>
+    <t>1 승리시 출혈 +2 · 2 승리시 상대 쇠약(다음 턴) · 3 매칭시 상대 방어도 전부 제거</t>
+  </si>
+  <si>
+    <t>위력 09-15 조정(15 → 14)</t>
+  </si>
+  <si>
+    <t>피의 대가</t>
+  </si>
+  <si>
+    <t>21~28</t>
+  </si>
+  <si>
+    <t>사용시 / 매칭시</t>
+  </si>
+  <si>
+    <t>1 사용시 자신 출혈 4 · 2 매칭시 자기 출혈 0~4 / 5~9 / 10+ → 상대 균열(다음 턴) +0 / +1 / +2</t>
+  </si>
+  <si>
+    <t>피를 흡수하다</t>
+  </si>
+  <si>
+    <t>15~20</t>
+  </si>
+  <si>
+    <t>상대 출혈 5 이상이면 5 제거하고 빛 +2</t>
+  </si>
+  <si>
+    <t>효과 09-20 조정</t>
+  </si>
+  <si>
+    <t>닥치는 대로</t>
+  </si>
+  <si>
+    <t>4 (가변)</t>
+  </si>
+  <si>
+    <t>쓸 때마다 이 스킬 빛 비용 −1 (전투 내 누적 · 최소 1) · 사용시 광기 +1</t>
+  </si>
+  <si>
+    <t>명예로운 전투</t>
+  </si>
+  <si>
+    <t>17~23</t>
+  </si>
+  <si>
+    <t>매칭시</t>
+  </si>
+  <si>
+    <t>매칭시 상대 스킬을 이 스킬로 강제 교체(양쪽 모두 이 스킬의 굴림 1개) · 버프 · 디버프는 그대로 적용 · 동점 무한 재굴림</t>
+  </si>
+  <si>
+    <t>09-16 개정(19~21 버프 면역 → 17~23 버프 적용) · 위력은 공식 이탈(의도)</t>
+  </si>
+  <si>
+    <t>피의 맹세</t>
+  </si>
+  <si>
+    <t>파괴형(조건부)</t>
+  </si>
+  <si>
+    <t>자기 출혈 전부 제거. 제거 직전 수치 — 0~4: 유틸형(파괴 권한 없음) / 5~9: 파괴형(일반) / 10+: 파괴형 + 약화 선행 없이 바로 파괴</t>
+  </si>
+  <si>
+    <t>파괴 권한(조건부)</t>
+  </si>
+  <si>
+    <t>09-14 브레인스토밍</t>
+  </si>
+  <si>
+    <t>전부 되갚다</t>
+  </si>
+  <si>
+    <t>기세 바가 열세 이하(B ≤ −30)이면 이 스킬의 모든 굴림 위력 +4</t>
+  </si>
+  <si>
+    <t>위력·범위 미정 · 09-16 문턱 −70 → −30 · 보너스 6 → 4 · 09-14 브레인스토밍</t>
+  </si>
+  <si>
+    <t>일기토</t>
+  </si>
+  <si>
+    <t>사용시 / 승리시</t>
+  </si>
+  <si>
+    <t>내 다른 슬롯이 같은 상대 슬롯을 조준해도 그 슬롯들의 일방타격은 무효화(포기) · 승리시 그 부위 출혈 +1</t>
+  </si>
+  <si>
+    <t>위력 09-15 조정(17 → 13, 공식값) · 09-14 브레인스토밍</t>
+  </si>
+  <si>
+    <t>도사림</t>
+  </si>
+  <si>
+    <t>공용</t>
+  </si>
+  <si>
+    <t>웅크리기</t>
+  </si>
+  <si>
+    <t>약한</t>
+  </si>
+  <si>
+    <t>방어도 +12</t>
+  </si>
+  <si>
+    <t>전 캐릭터 공용</t>
+  </si>
+  <si>
+    <t>노려보기</t>
+  </si>
+  <si>
+    <t>그 턴 모든 합 판정값 +1</t>
+  </si>
+  <si>
+    <t>강한</t>
+  </si>
+  <si>
+    <t>블로토</t>
+  </si>
+  <si>
+    <t>blót</t>
+  </si>
+  <si>
+    <t>자기 최저 체력 부위 1개 약화 (동점: 팔 → 다리 → 머리) + 광기 +1 + 적에게 공포</t>
+  </si>
+  <si>
+    <t>전투당 1회 사용 기준 수치</t>
+  </si>
+  <si>
+    <t>피의 서약</t>
+  </si>
+  <si>
+    <t>자신에게 출혈 3 + 재생 4 (둘 다 1씩 감쇠)</t>
+  </si>
+  <si>
+    <t>피로 사는 숨</t>
+  </si>
+  <si>
+    <t>자신에게 출혈 2 + 빛 +1</t>
+  </si>
+  <si>
+    <t>광기를 가라앉히다</t>
+  </si>
+  <si>
+    <t>광기 2 소모 → 빛 +1</t>
+  </si>
+  <si>
+    <t>상처를 지우다</t>
+  </si>
+  <si>
+    <t>자기 출혈 10 이상이면 10 제거 → 이번 턴 위력 +4 / 미만이면 방어도 +5</t>
+  </si>
+  <si>
+    <t>흐트러짐을 삼키다</t>
+  </si>
+  <si>
+    <t>자기 흐트러짐 20 소모 → 체력 20 회복 (부족하면 있는 만큼)</t>
+  </si>
+  <si>
+    <t>최후의 저항</t>
+  </si>
+  <si>
+    <t>조건부(짓눌림 종료)</t>
+  </si>
+  <si>
+    <t>지난 턴을 짓눌림(B ≤ −70)으로 끝냈을 때만 사용 가능. 이번 턴 내 전체 공격 슬롯 속도 무한(판정 보정 항상 +2)</t>
+  </si>
+  <si>
+    <t>속도 무한</t>
+  </si>
+  <si>
+    <t>위세</t>
+  </si>
+  <si>
+    <t>형1</t>
+  </si>
+  <si>
+    <t>룬 새기기</t>
+  </si>
+  <si>
+    <t>임계 60</t>
+  </si>
+  <si>
+    <t>발동</t>
+  </si>
+  <si>
+    <t>조준 부위에 출혈 3 + 광기 단계당 +1 (총 3~5)</t>
+  </si>
+  <si>
+    <t>형2</t>
+  </si>
+  <si>
+    <t>베르세르크</t>
+  </si>
+  <si>
+    <t>임계 65</t>
+  </si>
+  <si>
+    <t>광기 +2 → 현재 광기 × 5 피해 + 대상 부위 출혈 스택만큼 가산 (출혈 소비 없음 · 파괴 권한 없음)</t>
+  </si>
+  <si>
+    <t>형3</t>
+  </si>
+  <si>
+    <t>라그나로크</t>
+  </si>
+  <si>
+    <t>임계 70</t>
+  </si>
+  <si>
+    <t>한 턴 불사 — 자기 부위 파괴 안 됨 · 체력 1 아래로 안 내려감 (사망 · 적 파괴 스킬 포함) · 불사 턴 동안 맞은 교환당 광기 +1</t>
+  </si>
+  <si>
+    <t>효과 (백우)</t>
+  </si>
+  <si>
+    <t>효과 (적설)</t>
+  </si>
+  <si>
+    <t>효과 (낙일)</t>
+  </si>
+  <si>
+    <t>군자불어괴력난신(君子不語怪力亂神)</t>
+  </si>
+  <si>
+    <t>표식(낙점) · 환형 · 살수의 감 세 축을 묶는다</t>
+  </si>
+  <si>
+    <t>〃</t>
+  </si>
+  <si>
+    <t>출전 = 한문 고전(논어 술이편) · 09-15 개명</t>
+  </si>
+  <si>
+    <t>표식 (낙점)</t>
+  </si>
+  <si>
+    <t>이긴 교환마다 적립 · 상한 44에서 소비하고 발화: 바 푸시 50</t>
+  </si>
+  <si>
+    <t>… 발화: 봉인 1턴 (두 곳 동시 가능)</t>
+  </si>
+  <si>
+    <t>… 발화: 즉시 약화 (처형의 문)</t>
+  </si>
+  <si>
+    <t>대상 수 제한 없음 · 무기를 바꿔도 유지</t>
+  </si>
+  <si>
+    <t>지정</t>
+  </si>
+  <si>
+    <t>사용시(목표 지정)</t>
+  </si>
+  <si>
+    <t>상대 부위 하나에 3턴. 지속 중 그 부위 표식 획득마다 +2</t>
+  </si>
+  <si>
+    <t>코인 축</t>
+  </si>
+  <si>
+    <t>환형</t>
+  </si>
+  <si>
+    <t>준비 행동</t>
+  </si>
+  <si>
+    <t>무기 교체 — 안 든 무기 2개 중 하나를 고른다(선택 UI). 교체는 다음 턴부터, 카드 보너스는 쓴 그 턴 즉시</t>
+  </si>
+  <si>
+    <t>환형(공격) 또는 환형(수비) 하나만 장착 · 다리 · 머리 어느 도사림 칸에서든 사용</t>
+  </si>
+  <si>
+    <t>재굴림 축</t>
+  </si>
+  <si>
+    <t>살수의 감</t>
+  </si>
+  <si>
+    <t>획득: 매 턴 +1 (유비무환) · 숨 고르기 · 흔들어놓다 · 파괴 · 처치. 상한 없음 · 전투 종료 초기화. 사용: ① 슬롯 배치 때 지정 → 그 슬롯의 지는 교환 자동 재굴림 ② 잔혹한 마무리 추가타 ③ 패 보기(결투 한정 — 상대 결과를 보고 스택 1로 그 굴림을 접는다)</t>
+  </si>
+  <si>
+    <t>⚠ ③은 결투 도중 선택 UI</t>
+  </si>
+  <si>
+    <t>무기 효과</t>
+  </si>
+  <si>
+    <t>낙일 — 남은 굴림 삭제</t>
+  </si>
+  <si>
+    <t>교환 승리시 상대의 남은 굴림 전부 삭제 (평타 포함)</t>
+  </si>
+  <si>
+    <t>처형</t>
+  </si>
+  <si>
+    <t>앞면(크리)이 이미 약화된 부위를 치면 파괴</t>
+  </si>
+  <si>
+    <t>뒷조사</t>
+  </si>
+  <si>
+    <t>승리시 표식 +6</t>
+  </si>
+  <si>
+    <t>승리시 표식 +12</t>
+  </si>
+  <si>
+    <t>승리시 표식 +8</t>
+  </si>
+  <si>
+    <t>숨 고르기</t>
+  </si>
+  <si>
+    <t>표식 없음 · 승리시 살수의 감 +1</t>
+  </si>
+  <si>
+    <t>장부 정리</t>
+  </si>
+  <si>
+    <t>표식 20 이상일 때만 사용 가능 · 사용시 표식 20 소모 → 빛 +1</t>
+  </si>
+  <si>
+    <t>미구현(사용 조건 게이트 필요) · 09-15 브레인스토밍</t>
+  </si>
+  <si>
+    <t>한 발 물러서다</t>
+  </si>
+  <si>
+    <t>09-15 브레인스토밍</t>
+  </si>
+  <si>
+    <t>정조준</t>
+  </si>
+  <si>
+    <t>크리(앞면)면 표식 +6 추가</t>
+  </si>
+  <si>
+    <t>크리(앞면)면 골절(다음 턴)</t>
+  </si>
+  <si>
+    <t>크리(앞면)면 확정 추가 피해 +8</t>
+  </si>
+  <si>
+    <t>무기별 분기</t>
+  </si>
+  <si>
+    <t>미구현(크리 조건 효과 코드 신설 필요) · 09-15 브레인스토밍</t>
+  </si>
+  <si>
+    <t>확인 사살</t>
+  </si>
+  <si>
+    <t>조준 부위가 「지정」 상태면 바 +10 추가 획득</t>
+  </si>
+  <si>
+    <t>미구현(지정 조건 효과 코드 신설 필요) · 09-15 브레인스토밍, 지정 연계 카드 추가 예정</t>
+  </si>
+  <si>
+    <t>손에 익히다</t>
+  </si>
+  <si>
+    <t>지난 턴 환형 완료(새 무기 활성화 첫 턴)여야 사용 가능 · 사용시 살수의 감 +1</t>
+  </si>
+  <si>
+    <t>미구현(사용 조건 게이트 필요) · 코더 WeaponChanged 이벤트 재사용 가능 · 09-15 브레인스토밍</t>
+  </si>
+  <si>
+    <t>믿는 구석</t>
+  </si>
+  <si>
+    <t>살수의 감 3 소모 → 코인 3개 전부 확정 크리</t>
+  </si>
+  <si>
+    <t>살수의 감 2 소모 → 코인 2개 전부 확정 크리</t>
+  </si>
+  <si>
+    <t>살수의 감 2 소모 → 코인 1개 확정 크리</t>
+  </si>
+  <si>
+    <t>미구현(전체 굴림 강제 크리 처리 신설 필요) · 09-15 브레인스토밍</t>
+  </si>
+  <si>
+    <t>현상수배</t>
+  </si>
+  <si>
+    <t>모든 적에게 쇠약(다음 턴)</t>
+  </si>
+  <si>
+    <t>모든 적에게 골절(다음 턴)</t>
+  </si>
+  <si>
+    <t>모든 적에게 균열(다음 턴)</t>
+  </si>
+  <si>
+    <t>미구현(전체 적 대상 처리 필요) · 09-15 브레인스토밍</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>의뢰 대상</t>
+  </si>
+  <si>
+    <t>승리시 표식 +12 · 바 +15</t>
+  </si>
+  <si>
+    <t>표식 +24 · 바 +15</t>
+  </si>
+  <si>
+    <t>표식 +16 · 바 +15</t>
+  </si>
+  <si>
+    <t>바 +15는 v5 스케일 재확인</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>잔혹한 마무리</t>
+  </si>
+  <si>
+    <t>승리시 살수의 감 1 소비 → 코인, 앞면이면 무저항 추가타 (상한 강화 표)</t>
+  </si>
+  <si>
+    <t>자동 시전</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>목표 지정</t>
+  </si>
+  <si>
+    <t>상대 부위에 「지정」(3턴)</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>그림자 속으로</t>
+  </si>
+  <si>
+    <t>사용시 / 패배시</t>
+  </si>
+  <si>
+    <t>자신에게 방어도 +15. 패배시 살수의 감 +1</t>
+  </si>
+  <si>
+    <t>09-15: 패배시 라이더 추가</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>흔들어놓다</t>
+  </si>
+  <si>
+    <t>승리시(결투 대 결투)</t>
+  </si>
+  <si>
+    <t>살수의 감 +1</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>숨통을 끊다</t>
+  </si>
+  <si>
+    <t>이 타격으로 부위 약화 또는 파괴 시 그 대상 표식 +20</t>
+  </si>
+  <si>
+    <t>타격당 1회 · 잡몹은 처치 = 파괴</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>소문을 내다</t>
+  </si>
+  <si>
+    <t>같은 조건으로 모든 적에게 표식 +8</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>약점을 캐내다</t>
+  </si>
+  <si>
+    <t>상대 쇠약(다음 턴)</t>
+  </si>
+  <si>
+    <t>상대 골절(다음 턴)</t>
+  </si>
+  <si>
     <t>상대 균열(다음 턴)</t>
-  </si>
-  <si>
-    <t>형3 심화</t>
-  </si>
-  <si>
-    <t>제살깎기</t>
-  </si>
-  <si>
-    <t>승리시 / 패배시 / 매칭시</t>
-  </si>
-  <si>
-    <t>1번째: 승리시 광기 +1 · 패배시 자기 흐트러짐 −20 / 2번째: 매칭시 광기 +4</t>
-  </si>
-  <si>
-    <t>형3 가교</t>
-  </si>
-  <si>
-    <t>물러서지않기</t>
-  </si>
-  <si>
-    <t>12~25</t>
-  </si>
-  <si>
-    <t>13~24</t>
-  </si>
-  <si>
-    <t>자기 약화 부위 개수당 위력 +2 · 승리시 광기 +1 · 패배시 광기 +1 (라그나로크 지속 중 +3)</t>
-  </si>
-  <si>
-    <t>파괴 권한</t>
-  </si>
-  <si>
-    <t>유연</t>
-  </si>
-  <si>
-    <t>정면승부</t>
-  </si>
-  <si>
-    <t>승리시 준 피해의 10%만큼 자신도 피해</t>
-  </si>
-  <si>
-    <t>09-15 조정(위력 12 → 15, 자해 50% → 25%)</t>
-  </si>
-  <si>
-    <t>위세를 지피다</t>
-  </si>
-  <si>
-    <t>위세 게이지 충전 — 상대 출혈 0~4 / 5~9 / 10+ → +3 / +6 / +10</t>
-  </si>
-  <si>
-    <t>굳히기</t>
-  </si>
-  <si>
-    <t>자신 힘(다음 턴) — 상대 출혈 0~4 / 5~9 / 10+ → +0 / +1 / +2</t>
-  </si>
-  <si>
-    <t>몸을 사리다</t>
-  </si>
-  <si>
-    <t>다음 턴 자신에게 보호 1만큼 1턴 부여</t>
-  </si>
-  <si>
-    <t>빛 09-20 조정(2 -&gt; 1)</t>
-  </si>
-  <si>
-    <t>허를 찌르다</t>
-  </si>
-  <si>
-    <t>상대 균열 / 골절 / 쇠약 무작위 1 (다음 턴). 이 스킬로 부위 파괴 · 처치 시 빛 +1 즉시 + 광기 +2</t>
-  </si>
-  <si>
-    <t>신규</t>
-  </si>
-  <si>
-    <t>전부 걸다</t>
-  </si>
-  <si>
-    <t>11~18</t>
-  </si>
-  <si>
-    <t>승리시 / 매칭시</t>
-  </si>
-  <si>
-    <t>1 승리시 출혈 +2 · 2 승리시 상대 쇠약(다음 턴) · 3 매칭시 상대 방어도 전부 제거</t>
-  </si>
-  <si>
-    <t>위력 09-15 조정(15 → 14)</t>
-  </si>
-  <si>
-    <t>피의 대가</t>
-  </si>
-  <si>
-    <t>21~28</t>
-  </si>
-  <si>
-    <t>사용시 / 매칭시</t>
-  </si>
-  <si>
-    <t>1 사용시 자신 출혈 4 · 2 매칭시 자기 출혈 0~4 / 5~9 / 10+ → 상대 균열(다음 턴) +0 / +1 / +2</t>
-  </si>
-  <si>
-    <t>피를 흡수하다</t>
-  </si>
-  <si>
-    <t>15~20</t>
-  </si>
-  <si>
-    <t>상대 출혈 5 이상이면 5 제거하고 빛 +2</t>
-  </si>
-  <si>
-    <t>효과 09-20 조정</t>
-  </si>
-  <si>
-    <t>닥치는 대로</t>
-  </si>
-  <si>
-    <t>4 (가변)</t>
-  </si>
-  <si>
-    <t>쓸 때마다 이 스킬 빛 비용 −1 (전투 내 누적 · 최소 1) · 사용시 광기 +1</t>
-  </si>
-  <si>
-    <t>명예로운 전투</t>
-  </si>
-  <si>
-    <t>17~23</t>
-  </si>
-  <si>
-    <t>매칭시</t>
-  </si>
-  <si>
-    <t>매칭시 상대 스킬을 이 스킬로 강제 교체(양쪽 모두 이 스킬의 굴림 1개) · 버프 · 디버프는 그대로 적용 · 동점 무한 재굴림</t>
-  </si>
-  <si>
-    <t>09-16 개정(19~21 버프 면역 → 17~23 버프 적용) · 위력은 공식 이탈(의도)</t>
-  </si>
-  <si>
-    <t>피의 맹세</t>
-  </si>
-  <si>
-    <t>파괴형(조건부)</t>
-  </si>
-  <si>
-    <t>자기 출혈 전부 제거. 제거 직전 수치 — 0~4: 유틸형(파괴 권한 없음) / 5~9: 파괴형(일반) / 10+: 파괴형 + 약화 선행 없이 바로 파괴</t>
-  </si>
-  <si>
-    <t>파괴 권한(조건부)</t>
-  </si>
-  <si>
-    <t>09-14 브레인스토밍</t>
-  </si>
-  <si>
-    <t>전부 되갚다</t>
-  </si>
-  <si>
-    <t>기세 바가 열세 이하(B ≤ −30)이면 이 스킬의 모든 굴림 위력 +4</t>
-  </si>
-  <si>
-    <t>위력·범위 미정 · 09-16 문턱 −70 → −30 · 보너스 6 → 4 · 09-14 브레인스토밍</t>
-  </si>
-  <si>
-    <t>일기토</t>
-  </si>
-  <si>
-    <t>사용시 / 승리시</t>
-  </si>
-  <si>
-    <t>내 다른 슬롯이 같은 상대 슬롯을 조준해도 그 슬롯들의 일방타격은 무효화(포기) · 승리시 그 부위 출혈 +1</t>
-  </si>
-  <si>
-    <t>위력 09-15 조정(17 → 13, 공식값) · 09-14 브레인스토밍</t>
-  </si>
-  <si>
-    <t>도사림</t>
-  </si>
-  <si>
-    <t>공용</t>
-  </si>
-  <si>
-    <t>웅크리기</t>
-  </si>
-  <si>
-    <t>약한</t>
-  </si>
-  <si>
-    <t>방어도 +12</t>
-  </si>
-  <si>
-    <t>전 캐릭터 공용</t>
-  </si>
-  <si>
-    <t>노려보기</t>
-  </si>
-  <si>
-    <t>그 턴 모든 합 판정값 +1</t>
-  </si>
-  <si>
-    <t>강한</t>
-  </si>
-  <si>
-    <t>블로토</t>
-  </si>
-  <si>
-    <t>blót</t>
-  </si>
-  <si>
-    <t>자기 최저 체력 부위 1개 약화 (동점: 팔 → 다리 → 머리) + 광기 +1 + 적에게 공포</t>
-  </si>
-  <si>
-    <t>전투당 1회 사용 기준 수치</t>
-  </si>
-  <si>
-    <t>피의 서약</t>
-  </si>
-  <si>
-    <t>자신에게 출혈 3 + 재생 4 (둘 다 1씩 감쇠)</t>
-  </si>
-  <si>
-    <t>피로 사는 숨</t>
-  </si>
-  <si>
-    <t>자신에게 출혈 2 + 빛 +1</t>
-  </si>
-  <si>
-    <t>광기를 가라앉히다</t>
-  </si>
-  <si>
-    <t>광기 2 소모 → 빛 +1</t>
-  </si>
-  <si>
-    <t>상처를 지우다</t>
-  </si>
-  <si>
-    <t>자기 출혈 10 이상이면 10 제거 → 이번 턴 위력 +4 / 미만이면 방어도 +5</t>
-  </si>
-  <si>
-    <t>흐트러짐을 삼키다</t>
-  </si>
-  <si>
-    <t>자기 흐트러짐 20 소모 → 체력 20 회복 (부족하면 있는 만큼)</t>
-  </si>
-  <si>
-    <t>최후의 저항</t>
-  </si>
-  <si>
-    <t>조건부(짓눌림 종료)</t>
-  </si>
-  <si>
-    <t>지난 턴을 짓눌림(B ≤ −70)으로 끝냈을 때만 사용 가능. 이번 턴 내 전체 공격 슬롯 속도 무한(판정 보정 항상 +2)</t>
-  </si>
-  <si>
-    <t>속도 무한</t>
-  </si>
-  <si>
-    <t>위세</t>
-  </si>
-  <si>
-    <t>형1</t>
-  </si>
-  <si>
-    <t>룬 새기기</t>
-  </si>
-  <si>
-    <t>임계 60</t>
-  </si>
-  <si>
-    <t>발동</t>
-  </si>
-  <si>
-    <t>조준 부위에 출혈 3 + 광기 단계당 +1 (총 3~5)</t>
-  </si>
-  <si>
-    <t>형2</t>
-  </si>
-  <si>
-    <t>베르세르크</t>
-  </si>
-  <si>
-    <t>임계 65</t>
-  </si>
-  <si>
-    <t>광기 +2 → 현재 광기 × 5 피해 + 대상 부위 출혈 스택만큼 가산 (출혈 소비 없음 · 파괴 권한 없음)</t>
-  </si>
-  <si>
-    <t>형3</t>
-  </si>
-  <si>
-    <t>라그나로크</t>
-  </si>
-  <si>
-    <t>임계 70</t>
-  </si>
-  <si>
-    <t>한 턴 불사 — 자기 부위 파괴 안 됨 · 체력 1 아래로 안 내려감 (사망 · 적 파괴 스킬 포함) · 불사 턴 동안 맞은 교환당 광기 +1</t>
-  </si>
-  <si>
-    <t>효과 (백우)</t>
-  </si>
-  <si>
-    <t>효과 (적설)</t>
-  </si>
-  <si>
-    <t>효과 (낙일)</t>
-  </si>
-  <si>
-    <t>군자불어괴력난신(君子不語怪力亂神)</t>
-  </si>
-  <si>
-    <t>표식(낙점) · 환형 · 살수의 감 세 축을 묶는다</t>
-  </si>
-  <si>
-    <t>〃</t>
-  </si>
-  <si>
-    <t>출전 = 한문 고전(논어 술이편) · 09-15 개명</t>
-  </si>
-  <si>
-    <t>표식 (낙점)</t>
-  </si>
-  <si>
-    <t>이긴 교환마다 적립 · 상한 44에서 소비하고 발화: 바 푸시 50</t>
-  </si>
-  <si>
-    <t>… 발화: 봉인 1턴 (두 곳 동시 가능)</t>
-  </si>
-  <si>
-    <t>… 발화: 즉시 약화 (처형의 문)</t>
-  </si>
-  <si>
-    <t>대상 수 제한 없음 · 무기를 바꿔도 유지</t>
-  </si>
-  <si>
-    <t>지정</t>
-  </si>
-  <si>
-    <t>사용시(목표 지정)</t>
-  </si>
-  <si>
-    <t>상대 부위 하나에 3턴. 지속 중 그 부위 표식 획득마다 +2</t>
-  </si>
-  <si>
-    <t>코인 축</t>
-  </si>
-  <si>
-    <t>환형</t>
-  </si>
-  <si>
-    <t>준비 행동</t>
-  </si>
-  <si>
-    <t>무기 교체 — 안 든 무기 2개 중 하나를 고른다(선택 UI). 교체는 다음 턴부터, 카드 보너스는 쓴 그 턴 즉시</t>
-  </si>
-  <si>
-    <t>환형(공격) 또는 환형(수비) 하나만 장착 · 다리 · 머리 어느 도사림 칸에서든 사용</t>
-  </si>
-  <si>
-    <t>재굴림 축</t>
-  </si>
-  <si>
-    <t>살수의 감</t>
-  </si>
-  <si>
-    <t>획득: 매 턴 +1 (유비무환) · 숨 고르기 · 흔들어놓다 · 파괴 · 처치. 상한 없음 · 전투 종료 초기화. 사용: ① 슬롯 배치 때 지정 → 그 슬롯의 지는 교환 자동 재굴림 ② 잔혹한 마무리 추가타 ③ 패 보기(결투 한정 — 상대 결과를 보고 스택 1로 그 굴림을 접는다)</t>
-  </si>
-  <si>
-    <t>⚠ ③은 결투 도중 선택 UI</t>
-  </si>
-  <si>
-    <t>무기 효과</t>
-  </si>
-  <si>
-    <t>낙일 — 남은 굴림 삭제</t>
-  </si>
-  <si>
-    <t>교환 승리시 상대의 남은 굴림 전부 삭제 (평타 포함)</t>
-  </si>
-  <si>
-    <t>처형</t>
-  </si>
-  <si>
-    <t>앞면(크리)이 이미 약화된 부위를 치면 파괴</t>
-  </si>
-  <si>
-    <t>뒷조사</t>
-  </si>
-  <si>
-    <t>승리시 표식 +6</t>
-  </si>
-  <si>
-    <t>승리시 표식 +12</t>
-  </si>
-  <si>
-    <t>승리시 표식 +8</t>
-  </si>
-  <si>
-    <t>숨 고르기</t>
-  </si>
-  <si>
-    <t>표식 없음 · 승리시 살수의 감 +1</t>
-  </si>
-  <si>
-    <t>장부 정리</t>
-  </si>
-  <si>
-    <t>표식 20 이상일 때만 사용 가능 · 사용시 표식 20 소모 → 빛 +1</t>
-  </si>
-  <si>
-    <t>미구현(사용 조건 게이트 필요) · 09-15 브레인스토밍</t>
-  </si>
-  <si>
-    <t>한 발 물러서다</t>
-  </si>
-  <si>
-    <t>09-15 브레인스토밍</t>
-  </si>
-  <si>
-    <t>정조준</t>
-  </si>
-  <si>
-    <t>크리(앞면)면 표식 +6 추가</t>
-  </si>
-  <si>
-    <t>크리(앞면)면 골절(다음 턴)</t>
-  </si>
-  <si>
-    <t>크리(앞면)면 확정 추가 피해 +8</t>
-  </si>
-  <si>
-    <t>무기별 분기</t>
-  </si>
-  <si>
-    <t>미구현(크리 조건 효과 코드 신설 필요) · 09-15 브레인스토밍</t>
-  </si>
-  <si>
-    <t>확인 사살</t>
-  </si>
-  <si>
-    <t>조준 부위가 「지정」 상태면 바 +10 추가 획득</t>
-  </si>
-  <si>
-    <t>미구현(지정 조건 효과 코드 신설 필요) · 09-15 브레인스토밍, 지정 연계 카드 추가 예정</t>
-  </si>
-  <si>
-    <t>손에 익히다</t>
-  </si>
-  <si>
-    <t>지난 턴 환형 완료(새 무기 활성화 첫 턴)여야 사용 가능 · 사용시 살수의 감 +1</t>
-  </si>
-  <si>
-    <t>미구현(사용 조건 게이트 필요) · 코더 WeaponChanged 이벤트 재사용 가능 · 09-15 브레인스토밍</t>
-  </si>
-  <si>
-    <t>믿는 구석</t>
-  </si>
-  <si>
-    <t>살수의 감 3 소모 → 코인 3개 전부 확정 크리</t>
-  </si>
-  <si>
-    <t>살수의 감 2 소모 → 코인 2개 전부 확정 크리</t>
-  </si>
-  <si>
-    <t>살수의 감 2 소모 → 코인 1개 확정 크리</t>
-  </si>
-  <si>
-    <t>미구현(전체 굴림 강제 크리 처리 신설 필요) · 09-15 브레인스토밍</t>
-  </si>
-  <si>
-    <t>현상수배</t>
-  </si>
-  <si>
-    <t>모든 적에게 쇠약(다음 턴)</t>
-  </si>
-  <si>
-    <t>모든 적에게 골절(다음 턴)</t>
-  </si>
-  <si>
-    <t>모든 적에게 균열(다음 턴)</t>
-  </si>
-  <si>
-    <t>미구현(전체 적 대상 처리 필요) · 09-15 브레인스토밍</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>의뢰 대상</t>
-  </si>
-  <si>
-    <t>승리시 표식 +12 · 바 +15</t>
-  </si>
-  <si>
-    <t>표식 +24 · 바 +15</t>
-  </si>
-  <si>
-    <t>표식 +16 · 바 +15</t>
-  </si>
-  <si>
-    <t>바 +15는 v5 스케일 재확인</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>잔혹한 마무리</t>
-  </si>
-  <si>
-    <t>승리시 살수의 감 1 소비 → 코인, 앞면이면 무저항 추가타 (상한 강화 표)</t>
-  </si>
-  <si>
-    <t>자동 시전</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>목표 지정</t>
-  </si>
-  <si>
-    <t>상대 부위에 「지정」(3턴)</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>그림자 속으로</t>
-  </si>
-  <si>
-    <t>사용시 / 패배시</t>
-  </si>
-  <si>
-    <t>자신에게 방어도 +15. 패배시 살수의 감 +1</t>
-  </si>
-  <si>
-    <t>09-15: 패배시 라이더 추가</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>흔들어놓다</t>
-  </si>
-  <si>
-    <t>승리시(결투 대 결투)</t>
-  </si>
-  <si>
-    <t>살수의 감 +1</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>숨통을 끊다</t>
-  </si>
-  <si>
-    <t>이 타격으로 부위 약화 또는 파괴 시 그 대상 표식 +20</t>
-  </si>
-  <si>
-    <t>타격당 1회 · 잡몹은 처치 = 파괴</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>소문을 내다</t>
-  </si>
-  <si>
-    <t>같은 조건으로 모든 적에게 표식 +8</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>약점을 캐내다</t>
-  </si>
-  <si>
-    <t>상대 쇠약(다음 턴)</t>
-  </si>
-  <si>
-    <t>상대 골절(다음 턴)</t>
   </si>
   <si>
     <t>무기별 분기 첫 사례</t>
@@ -2981,7 +2984,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90C5F7C-03DD-421D-89F6-1E00EA0121EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95A3446-6587-4E45-AAEB-DF46AD7B7A61}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3171,7 +3174,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33565FB0-C4EA-453C-8BA9-CFC616FC051E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E17F28AC-048B-41B4-852A-90C39B682CA5}">
   <dimension ref="A1:T56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4829,16 +4832,16 @@
         <v>100</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="M27" s="9" t="s">
         <v>1</v>
@@ -4853,7 +4856,7 @@
         <v>73</v>
       </c>
       <c r="Q27" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="R27" s="9" t="s">
         <v>1</v>
@@ -4870,10 +4873,10 @@
         <v>184</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>1</v>
@@ -4891,7 +4894,7 @@
         <v>100</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>170</v>
@@ -4953,16 +4956,16 @@
         <v>100</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="M29" s="9" t="s">
         <v>1</v>
@@ -5139,7 +5142,7 @@
         <v>80</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>116</v>
@@ -5263,7 +5266,7 @@
         <v>99</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>116</v>
@@ -6664,14 +6667,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T56" xr:uid="{33565FB0-C4EA-453C-8BA9-CFC616FC051E}"/>
+  <autoFilter ref="A1:T56" xr:uid="{E17F28AC-048B-41B4-852A-90C39B682CA5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F00B95F-8D4B-4D75-9B62-28E919616EAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8088858-2AB3-4EED-A5E0-BF003B80C798}">
   <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7700,7 +7703,7 @@
         <v>403</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>210</v>
+        <v>404</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>1</v>
@@ -7709,7 +7712,7 @@
         <v>49</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7717,10 +7720,10 @@
         <v>184</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>78</v>
@@ -7732,10 +7735,10 @@
         <v>100</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>314</v>
@@ -7758,10 +7761,10 @@
         <v>184</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>78</v>
@@ -7776,7 +7779,7 @@
         <v>152</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>314</v>
@@ -7791,7 +7794,7 @@
         <v>49</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7799,10 +7802,10 @@
         <v>184</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>78</v>
@@ -7817,7 +7820,7 @@
         <v>73</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>314</v>
@@ -7832,7 +7835,7 @@
         <v>49</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7840,10 +7843,10 @@
         <v>184</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>90</v>
@@ -7858,13 +7861,13 @@
         <v>73</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>1</v>
@@ -7873,7 +7876,7 @@
         <v>49</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7881,10 +7884,10 @@
         <v>184</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>90</v>
@@ -7899,7 +7902,7 @@
         <v>152</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>314</v>
@@ -7914,7 +7917,7 @@
         <v>49</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -7922,10 +7925,10 @@
         <v>184</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>78</v>
@@ -7940,13 +7943,13 @@
         <v>73</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>314</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>353</v>
@@ -7955,7 +7958,7 @@
         <v>49</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -7963,10 +7966,10 @@
         <v>184</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>78</v>
@@ -7981,7 +7984,7 @@
         <v>152</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>314</v>
@@ -7996,7 +7999,7 @@
         <v>49</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -8004,10 +8007,10 @@
         <v>184</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>78</v>
@@ -8016,13 +8019,13 @@
         <v>1</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>152</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>314</v>
@@ -8037,7 +8040,7 @@
         <v>49</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -8130,7 +8133,7 @@
         <v>276</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>1</v>
@@ -8145,7 +8148,7 @@
         <v>152</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>314</v>
@@ -8171,7 +8174,7 @@
         <v>276</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>1</v>
@@ -8186,7 +8189,7 @@
         <v>152</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>314</v>
@@ -8212,7 +8215,7 @@
         <v>276</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>1</v>
@@ -8227,13 +8230,13 @@
         <v>326</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>1</v>
@@ -8242,7 +8245,7 @@
         <v>49</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -8253,7 +8256,7 @@
         <v>276</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>1</v>
@@ -8268,7 +8271,7 @@
         <v>326</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>314</v>
@@ -8283,7 +8286,7 @@
         <v>49</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -8294,7 +8297,7 @@
         <v>276</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>1</v>
@@ -8324,7 +8327,7 @@
         <v>49</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -8335,7 +8338,7 @@
         <v>276</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>1</v>
@@ -8350,7 +8353,7 @@
         <v>152</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>314</v>
@@ -8365,7 +8368,7 @@
         <v>49</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -8376,7 +8379,7 @@
         <v>276</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>1</v>
@@ -8391,7 +8394,7 @@
         <v>152</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>314</v>
@@ -8406,7 +8409,7 @@
         <v>49</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -8417,13 +8420,13 @@
         <v>296</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>1</v>
@@ -8432,13 +8435,13 @@
         <v>299</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K43" s="9" t="s">
         <v>1</v>
@@ -8458,13 +8461,13 @@
         <v>301</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>1</v>
@@ -8473,7 +8476,7 @@
         <v>299</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I44" s="10" t="s">
         <v>314</v>
@@ -8499,13 +8502,13 @@
         <v>305</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>1</v>
@@ -8514,7 +8517,7 @@
         <v>299</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I45" s="10" t="s">
         <v>314</v>
@@ -8533,14 +8536,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M45" xr:uid="{0F00B95F-8D4B-4D75-9B62-28E919616EAD}"/>
+  <autoFilter ref="A1:M45" xr:uid="{F8088858-2AB3-4EED-A5E0-BF003B80C798}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC72440-4B50-4472-AF6F-3CD7035E73BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E8106E-CDF5-4C99-9E38-E463CD681677}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8558,201 +8561,201 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>38</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>79</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>136</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>99</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>47</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>100</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>144</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>47</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{8AC72440-4B50-4472-AF6F-3CD7035E73BB}"/>
+  <autoFilter ref="A1:O4" xr:uid="{75E8106E-CDF5-4C99-9E38-E463CD681677}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A98747F9-AF54-4C30-8E77-0E4445E58771}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82887294-92FA-4152-96C8-001B0BF4348B}">
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8843,10 +8846,10 @@
         <v>44</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>1</v>
@@ -8885,7 +8888,7 @@
         <v>47</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="R2" s="13" t="s">
         <v>1</v>
@@ -8894,7 +8897,7 @@
         <v>49</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -8902,10 +8905,10 @@
         <v>66</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>1</v>
@@ -8947,7 +8950,7 @@
         <v>47</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="R3" s="11" t="s">
         <v>1</v>
@@ -8967,7 +8970,7 @@
         <v>58</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>1</v>
@@ -9009,7 +9012,7 @@
         <v>47</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="R4" s="13" t="s">
         <v>1</v>
@@ -9018,7 +9021,7 @@
         <v>49</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="54" x14ac:dyDescent="0.3">
@@ -9026,10 +9029,10 @@
         <v>66</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>1</v>
@@ -9068,10 +9071,10 @@
         <v>1</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="R5" s="11" t="s">
         <v>1</v>
@@ -9091,7 +9094,7 @@
         <v>67</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>1</v>
@@ -9133,13 +9136,13 @@
         <v>73</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="R6" s="11" t="s">
         <v>1</v>
       </c>
       <c r="S6" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="T6" s="12" t="s">
         <v>1</v>
@@ -9153,16 +9156,16 @@
         <v>371</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>84</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>135</v>
@@ -9174,37 +9177,37 @@
         <v>114</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>1</v>
       </c>
       <c r="O7" s="13" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P7" s="13" t="s">
         <v>139</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="R7" s="13" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="S7" s="13" t="s">
         <v>49</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9215,16 +9218,16 @@
         <v>377</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>84</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>99</v>
@@ -9233,13 +9236,13 @@
         <v>100</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L8" s="14" t="s">
         <v>1</v>
@@ -9251,22 +9254,22 @@
         <v>1</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P8" s="13" t="s">
         <v>139</v>
       </c>
       <c r="Q8" s="14" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="R8" s="13" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="S8" s="13" t="s">
         <v>49</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9277,7 +9280,7 @@
         <v>381</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>1</v>
@@ -9298,28 +9301,28 @@
         <v>164</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P9" s="13" t="s">
         <v>152</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="R9" s="13" t="s">
         <v>1</v>
@@ -9328,7 +9331,7 @@
         <v>49</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9336,10 +9339,10 @@
         <v>75</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>1</v>
@@ -9348,7 +9351,7 @@
         <v>84</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>99</v>
@@ -9357,13 +9360,13 @@
         <v>80</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L10" s="12" t="s">
         <v>1</v>
@@ -9375,22 +9378,22 @@
         <v>1</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P10" s="11" t="s">
         <v>139</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="S10" s="11" t="s">
         <v>49</v>
       </c>
       <c r="T10" s="12" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9398,10 +9401,10 @@
         <v>75</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>1</v>
@@ -9422,13 +9425,13 @@
         <v>108</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M11" s="12" t="s">
         <v>1</v>
@@ -9437,13 +9440,13 @@
         <v>1</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="R11" s="11" t="s">
         <v>1</v>
@@ -9587,7 +9590,7 @@
         <v>371</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>1</v>
@@ -9629,7 +9632,7 @@
         <v>152</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="R14" s="13" t="s">
         <v>1</v>
@@ -9638,7 +9641,7 @@
         <v>49</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
@@ -9649,7 +9652,7 @@
         <v>377</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>1</v>
@@ -9691,7 +9694,7 @@
         <v>152</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="R15" s="13" t="s">
         <v>1</v>
@@ -9711,7 +9714,7 @@
         <v>381</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>1</v>
@@ -9753,13 +9756,13 @@
         <v>152</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="R16" s="13" t="s">
         <v>1</v>
       </c>
       <c r="S16" s="13" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="T16" s="14" t="s">
         <v>1</v>
@@ -9770,10 +9773,10 @@
         <v>268</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>1</v>
@@ -9815,7 +9818,7 @@
         <v>152</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="R17" s="13" t="s">
         <v>1</v>
@@ -9824,7 +9827,7 @@
         <v>49</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
@@ -9835,7 +9838,7 @@
         <v>296</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>1</v>
@@ -9844,7 +9847,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>1</v>
@@ -9877,7 +9880,7 @@
         <v>299</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="R18" s="11" t="s">
         <v>1</v>
@@ -9897,7 +9900,7 @@
         <v>301</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>1</v>
@@ -9906,7 +9909,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>1</v>
@@ -9939,7 +9942,7 @@
         <v>299</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="R19" s="11" t="s">
         <v>1</v>
@@ -9959,7 +9962,7 @@
         <v>305</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>1</v>
@@ -10001,7 +10004,7 @@
         <v>299</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="R20" s="11" t="s">
         <v>1</v>
@@ -10014,14 +10017,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T20" xr:uid="{A98747F9-AF54-4C30-8E77-0E4445E58771}"/>
+  <autoFilter ref="A1:T20" xr:uid="{82887294-92FA-4152-96C8-001B0BF4348B}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96CBB6C7-525A-4F0E-95E3-7F07E1034BD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88C7AD8-723B-4B94-A72D-E147194B839F}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10036,7 +10039,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>26</v>
@@ -10045,13 +10048,13 @@
         <v>24</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>43</v>
@@ -10059,91 +10062,91 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>590</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>591</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>1</v>
@@ -10151,22 +10154,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>1</v>
@@ -10174,22 +10177,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>1</v>
@@ -10197,128 +10200,128 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12" xr:uid="{96CBB6C7-525A-4F0E-95E3-7F07E1034BD0}"/>
+  <autoFilter ref="A1:G12" xr:uid="{E88C7AD8-723B-4B94-A72D-E147194B839F}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A59096FA-140B-4BF1-B7E7-CE7C321DFA0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998880AF-C2B7-4014-BBE4-ED004B21BFD9}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10332,19 +10335,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>40</v>
@@ -10355,22 +10358,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>49</v>
@@ -10378,22 +10381,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>49</v>
@@ -10401,22 +10404,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>49</v>
@@ -10424,22 +10427,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>49</v>
@@ -10447,22 +10450,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>49</v>
@@ -10470,22 +10473,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>49</v>
@@ -10493,22 +10496,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>49</v>
@@ -10516,22 +10519,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>49</v>
@@ -10539,22 +10542,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>49</v>
@@ -10562,13 +10565,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>100</v>
@@ -10577,7 +10580,7 @@
         <v>185</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>49</v>
@@ -10585,22 +10588,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>49</v>
@@ -10608,22 +10611,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>49</v>
@@ -10631,22 +10634,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>49</v>
@@ -10654,22 +10657,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>49</v>
@@ -10677,22 +10680,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>49</v>
@@ -10700,45 +10703,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>49</v>
@@ -10746,22 +10749,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>49</v>
@@ -10769,22 +10772,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>49</v>
@@ -10792,22 +10795,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>49</v>
@@ -10815,22 +10818,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>49</v>
@@ -10838,22 +10841,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>49</v>
@@ -10861,22 +10864,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>49</v>
@@ -10884,22 +10887,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>49</v>
@@ -10907,22 +10910,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>49</v>
@@ -10930,22 +10933,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>49</v>
@@ -10953,183 +10956,183 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>696</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>49</v>
@@ -11137,68 +11140,68 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>49</v>
@@ -11206,22 +11209,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>49</v>
@@ -11229,22 +11232,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>49</v>
@@ -11252,22 +11255,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>49</v>
@@ -11275,22 +11278,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>49</v>
@@ -11298,22 +11301,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>49</v>
@@ -11321,45 +11324,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>49</v>
@@ -11367,22 +11370,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>49</v>
@@ -11390,10 +11393,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>295</v>
@@ -11402,10 +11405,10 @@
         <v>100</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>49</v>
@@ -11413,10 +11416,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>295</v>
@@ -11425,10 +11428,10 @@
         <v>100</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>49</v>
@@ -11436,10 +11439,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>295</v>
@@ -11448,10 +11451,10 @@
         <v>100</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>49</v>
@@ -11459,10 +11462,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>295</v>
@@ -11471,10 +11474,10 @@
         <v>99</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>49</v>
@@ -11482,10 +11485,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>295</v>
@@ -11494,10 +11497,10 @@
         <v>99</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>49</v>
@@ -11505,10 +11508,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>295</v>
@@ -11517,10 +11520,10 @@
         <v>99</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>49</v>
@@ -11528,10 +11531,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>295</v>
@@ -11540,10 +11543,10 @@
         <v>79</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>49</v>
@@ -11551,10 +11554,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>295</v>
@@ -11563,10 +11566,10 @@
         <v>79</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>49</v>
@@ -11574,10 +11577,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>295</v>
@@ -11586,10 +11589,10 @@
         <v>79</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>49</v>
@@ -11597,68 +11600,68 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>756</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>757</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>49</v>
@@ -11666,22 +11669,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>49</v>
@@ -11689,22 +11692,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>49</v>
@@ -11712,22 +11715,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>49</v>
@@ -11735,22 +11738,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>49</v>
@@ -11758,22 +11761,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>49</v>
@@ -11781,36 +11784,36 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>49</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{A59096FA-140B-4BF1-B7E7-CE7C321DFA0F}"/>
+  <autoFilter ref="A1:G64" xr:uid="{998880AF-C2B7-4014-BBE4-ED004B21BFD9}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD57149B-6272-446B-B134-BE871BBCC578}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F827CD-E8A9-4A16-8B43-5082F79E211D}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11824,10 +11827,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>30</v>
@@ -11839,7 +11842,7 @@
         <v>184</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>43</v>
@@ -11847,10 +11850,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>79</v>
@@ -11859,21 +11862,21 @@
         <v>81</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>47</v>
@@ -11882,21 +11885,21 @@
         <v>108</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
@@ -11908,18 +11911,18 @@
         <v>47</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>47</v>
@@ -11931,18 +11934,18 @@
         <v>47</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>79</v>
@@ -11951,21 +11954,21 @@
         <v>164</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>99</v>
@@ -11974,21 +11977,21 @@
         <v>108</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>47</v>
@@ -12000,14 +12003,14 @@
         <v>47</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{FD57149B-6272-446B-B134-BE871BBCC578}"/>
+  <autoFilter ref="A1:G8" xr:uid="{03F827CD-E8A9-4A16-8B43-5082F79E211D}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\rules0920\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D42C7F3F-5361-4231-AA05-7487D852E88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F80F2711-9417-400A-9990-AE607EAE15F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{C3F1349F-CDDF-4C54-A7A7-1DCD15F95085}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{DA4AF4AC-8132-476A-911B-61D631AEFE8F}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -786,7 +786,7 @@
     <t>사용시 / 매칭시</t>
   </si>
   <si>
-    <t>1 사용시 자신 출혈 4 · 2 매칭시 자기 출혈 0~4 / 5~9 / 10+ → 상대 균열(다음 턴) +0 / +1 / +2</t>
+    <t>1 사용시 자신 출혈 4 · 2 매칭시 자기 출혈 0~4 / 5~9 / 10+ → 다음 턴 자신에게 힘 1 / 2 / 3만큼 3턴 부여</t>
   </si>
   <si>
     <t>피를 흡수하다</t>
@@ -2984,7 +2984,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95A3446-6587-4E45-AAEB-DF46AD7B7A61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D62E67B8-44E8-4D2B-9741-6FE27A26FB7B}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3174,7 +3174,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E17F28AC-048B-41B4-852A-90C39B682CA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD015EF3-AA50-467D-94EA-9FD14434E6B1}">
   <dimension ref="A1:T56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6667,14 +6667,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T56" xr:uid="{E17F28AC-048B-41B4-852A-90C39B682CA5}"/>
+  <autoFilter ref="A1:T56" xr:uid="{FD015EF3-AA50-467D-94EA-9FD14434E6B1}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8088858-2AB3-4EED-A5E0-BF003B80C798}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6F0D953-91D5-49AD-8D4C-4CA51841DC62}">
   <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8536,14 +8536,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M45" xr:uid="{F8088858-2AB3-4EED-A5E0-BF003B80C798}"/>
+  <autoFilter ref="A1:M45" xr:uid="{D6F0D953-91D5-49AD-8D4C-4CA51841DC62}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E8106E-CDF5-4C99-9E38-E463CD681677}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8174A24B-6841-4F72-8CE9-5A6BFD5DF5DB}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8748,14 +8748,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{75E8106E-CDF5-4C99-9E38-E463CD681677}"/>
+  <autoFilter ref="A1:O4" xr:uid="{8174A24B-6841-4F72-8CE9-5A6BFD5DF5DB}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82887294-92FA-4152-96C8-001B0BF4348B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E0ADDE-40BA-4A61-9AAB-66E9F829273A}">
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10017,14 +10017,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T20" xr:uid="{82887294-92FA-4152-96C8-001B0BF4348B}"/>
+  <autoFilter ref="A1:T20" xr:uid="{B7E0ADDE-40BA-4A61-9AAB-66E9F829273A}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88C7AD8-723B-4B94-A72D-E147194B839F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773347AF-DDFA-4B79-A42D-F01B49E27F7E}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10314,14 +10314,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12" xr:uid="{E88C7AD8-723B-4B94-A72D-E147194B839F}"/>
+  <autoFilter ref="A1:G12" xr:uid="{773347AF-DDFA-4B79-A42D-F01B49E27F7E}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998880AF-C2B7-4014-BBE4-ED004B21BFD9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD494A91-F35B-49C9-B44F-AEE561CC93EF}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11806,14 +11806,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{998880AF-C2B7-4014-BBE4-ED004B21BFD9}"/>
+  <autoFilter ref="A1:G64" xr:uid="{BD494A91-F35B-49C9-B44F-AEE561CC93EF}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F827CD-E8A9-4A16-8B43-5082F79E211D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF10550-676B-49DE-8D84-0DBF5911EA88}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12010,7 +12010,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{03F827CD-E8A9-4A16-8B43-5082F79E211D}"/>
+  <autoFilter ref="A1:G8" xr:uid="{1DF10550-676B-49DE-8D84-0DBF5911EA88}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\rules0920\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\rules0921\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F80F2711-9417-400A-9990-AE607EAE15F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{494FE809-51BE-4979-9F51-E913C029A9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{DA4AF4AC-8132-476A-911B-61D631AEFE8F}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{731E2743-826B-4A13-BF59-6E68C628C44A}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="805">
   <si>
     <t>Project Abyss — 캐릭터 스킬 스펙 (2026-09-13)</t>
   </si>
@@ -732,202 +732,205 @@
     <t>09-15 조정(위력 12 → 15, 자해 50% → 25%)</t>
   </si>
   <si>
+    <t>굳히기</t>
+  </si>
+  <si>
+    <t>자신 힘(다음 턴) — 상대 출혈 0~4 / 5~9 / 10+ → +1 / +2 / +3</t>
+  </si>
+  <si>
+    <t>몸을 사리다</t>
+  </si>
+  <si>
+    <t>다음 턴 자신에게 보호 1만큼 1턴 부여</t>
+  </si>
+  <si>
+    <t>빛 09-20 조정(2 -&gt; 1)</t>
+  </si>
+  <si>
+    <t>허를 찌르다</t>
+  </si>
+  <si>
+    <t>상대 균열 / 골절 / 쇠약 무작위 1 (다음 턴). 이 스킬로 부위 파괴 · 처치 시 빛 +1 즉시 + 광기 +2</t>
+  </si>
+  <si>
+    <t>신규</t>
+  </si>
+  <si>
+    <t>전부 걸다</t>
+  </si>
+  <si>
+    <t>11~18</t>
+  </si>
+  <si>
+    <t>승리시 / 매칭시</t>
+  </si>
+  <si>
+    <t>1 승리시 출혈 +2 · 2 승리시 상대 쇠약(다음 턴) · 3 매칭시 상대 방어도 전부 제거</t>
+  </si>
+  <si>
+    <t>위력 09-15 조정(15 → 14)</t>
+  </si>
+  <si>
+    <t>피의 대가</t>
+  </si>
+  <si>
+    <t>21~28</t>
+  </si>
+  <si>
+    <t>사용시 / 매칭시</t>
+  </si>
+  <si>
+    <t>1 사용시 자신 출혈 4 · 2 매칭시 자기 출혈 0~4 / 5~9 / 10+ → 다음 턴 자신에게 힘 1 / 2 / 3만큼 3턴 부여</t>
+  </si>
+  <si>
+    <t>피를 흡수하다</t>
+  </si>
+  <si>
+    <t>15~20</t>
+  </si>
+  <si>
+    <t>상대 출혈 5 이상이면 5 제거하고 빛 +2</t>
+  </si>
+  <si>
+    <t>효과 09-20 조정</t>
+  </si>
+  <si>
+    <t>닥치는 대로</t>
+  </si>
+  <si>
+    <t>4 (가변)</t>
+  </si>
+  <si>
+    <t>쓸 때마다 이 스킬 빛 비용 −1 (전투 내 누적 · 최소 1) · 사용시 광기 +1</t>
+  </si>
+  <si>
+    <t>명예로운 전투</t>
+  </si>
+  <si>
+    <t>17~23</t>
+  </si>
+  <si>
+    <t>매칭시</t>
+  </si>
+  <si>
+    <t>매칭시 상대 스킬을 이 스킬로 강제 교체(양쪽 모두 이 스킬의 굴림 1개) · 버프 · 디버프는 그대로 적용 · 동점 무한 재굴림</t>
+  </si>
+  <si>
+    <t>09-16 개정(19~21 버프 면역 → 17~23 버프 적용) · 위력은 공식 이탈(의도)</t>
+  </si>
+  <si>
+    <t>피의 맹세</t>
+  </si>
+  <si>
+    <t>파괴형(조건부)</t>
+  </si>
+  <si>
+    <t>자기 출혈 전부 제거. 제거 직전 수치 — 0~4: 파괴 권한 없음 / 5~9: 파괴형 + 위력 +4 + 사용시 재생 4만큼 3턴 + 1굴림 승리시 상대 출혈 +3 / 10+: 파괴형 + 약화 선행 없이 바로 파괴 + 위력 +8 + 1굴림 승리시 상대 출혈 +3 + 2굴림 승리시 상대 출혈 +3 + 빛 +1</t>
+  </si>
+  <si>
+    <t>파괴 권한(조건부)</t>
+  </si>
+  <si>
+    <t>09-14 브레인스토밍</t>
+  </si>
+  <si>
+    <t>전부 되갚다</t>
+  </si>
+  <si>
+    <t>기세 바가 열세 이하(B ≤ −30)이면 이 스킬의 모든 굴림 위력 +4</t>
+  </si>
+  <si>
+    <t>위력·범위 미정 · 09-16 문턱 −70 → −30 · 보너스 6 → 4 · 09-14 브레인스토밍</t>
+  </si>
+  <si>
+    <t>일기토</t>
+  </si>
+  <si>
+    <t>사용시 / 승리시</t>
+  </si>
+  <si>
+    <t>내 다른 슬롯이 같은 상대 슬롯을 조준해도 그 슬롯들의 일방타격은 무효화(포기) · 승리시 그 부위 출혈 +1</t>
+  </si>
+  <si>
+    <t>위력 09-15 조정(17 → 13, 공식값) · 09-14 브레인스토밍</t>
+  </si>
+  <si>
+    <t>도사림</t>
+  </si>
+  <si>
+    <t>공용</t>
+  </si>
+  <si>
+    <t>웅크리기</t>
+  </si>
+  <si>
+    <t>약한</t>
+  </si>
+  <si>
+    <t>방어도 +12</t>
+  </si>
+  <si>
+    <t>전 캐릭터 공용</t>
+  </si>
+  <si>
+    <t>노려보기</t>
+  </si>
+  <si>
+    <t>그 턴 모든 합 판정값 +1</t>
+  </si>
+  <si>
+    <t>강한</t>
+  </si>
+  <si>
+    <t>블로토</t>
+  </si>
+  <si>
+    <t>blót</t>
+  </si>
+  <si>
+    <t>자기 최저 체력 부위 1개 약화 (동점: 팔 → 다리 → 머리) + 광기 +1 + 적에게 공포</t>
+  </si>
+  <si>
+    <t>전투당 1회 사용 기준 수치</t>
+  </si>
+  <si>
+    <t>피의 서약</t>
+  </si>
+  <si>
+    <t>자신에게 출혈 +3 + 재생 4만큼 3턴</t>
+  </si>
+  <si>
+    <t>피로 사는 숨</t>
+  </si>
+  <si>
+    <t>자신에게 출혈 2 + 빛 +1</t>
+  </si>
+  <si>
+    <t>광기를 가라앉히다</t>
+  </si>
+  <si>
+    <t>광기 2 소모 → 빛 +1</t>
+  </si>
+  <si>
+    <t>상처를 지우다</t>
+  </si>
+  <si>
+    <t>자기 출혈 10 이상이면 10 제거 → 이번 턴 위력 +4 / 미만이면 방어도 +5</t>
+  </si>
+  <si>
+    <t>흐트러짐을 삼키다</t>
+  </si>
+  <si>
+    <t>자기 흐트러짐 20 소모 → 체력 20 회복 (부족하면 있는 만큼)</t>
+  </si>
+  <si>
     <t>위세를 지피다</t>
   </si>
   <si>
-    <t>위세 게이지 충전 — 상대 출혈 0~4 / 5~9 / 10+ → +3 / +6 / +10</t>
-  </si>
-  <si>
-    <t>굳히기</t>
-  </si>
-  <si>
-    <t>자신 힘(다음 턴) — 상대 출혈 0~4 / 5~9 / 10+ → +1 / +2 / +3</t>
-  </si>
-  <si>
-    <t>몸을 사리다</t>
-  </si>
-  <si>
-    <t>다음 턴 자신에게 보호 1만큼 1턴 부여</t>
-  </si>
-  <si>
-    <t>빛 09-20 조정(2 -&gt; 1)</t>
-  </si>
-  <si>
-    <t>허를 찌르다</t>
-  </si>
-  <si>
-    <t>상대 균열 / 골절 / 쇠약 무작위 1 (다음 턴). 이 스킬로 부위 파괴 · 처치 시 빛 +1 즉시 + 광기 +2</t>
-  </si>
-  <si>
-    <t>신규</t>
-  </si>
-  <si>
-    <t>전부 걸다</t>
-  </si>
-  <si>
-    <t>11~18</t>
-  </si>
-  <si>
-    <t>승리시 / 매칭시</t>
-  </si>
-  <si>
-    <t>1 승리시 출혈 +2 · 2 승리시 상대 쇠약(다음 턴) · 3 매칭시 상대 방어도 전부 제거</t>
-  </si>
-  <si>
-    <t>위력 09-15 조정(15 → 14)</t>
-  </si>
-  <si>
-    <t>피의 대가</t>
-  </si>
-  <si>
-    <t>21~28</t>
-  </si>
-  <si>
-    <t>사용시 / 매칭시</t>
-  </si>
-  <si>
-    <t>1 사용시 자신 출혈 4 · 2 매칭시 자기 출혈 0~4 / 5~9 / 10+ → 다음 턴 자신에게 힘 1 / 2 / 3만큼 3턴 부여</t>
-  </si>
-  <si>
-    <t>피를 흡수하다</t>
-  </si>
-  <si>
-    <t>15~20</t>
-  </si>
-  <si>
-    <t>상대 출혈 5 이상이면 5 제거하고 빛 +2</t>
-  </si>
-  <si>
-    <t>효과 09-20 조정</t>
-  </si>
-  <si>
-    <t>닥치는 대로</t>
-  </si>
-  <si>
-    <t>4 (가변)</t>
-  </si>
-  <si>
-    <t>쓸 때마다 이 스킬 빛 비용 −1 (전투 내 누적 · 최소 1) · 사용시 광기 +1</t>
-  </si>
-  <si>
-    <t>명예로운 전투</t>
-  </si>
-  <si>
-    <t>17~23</t>
-  </si>
-  <si>
-    <t>매칭시</t>
-  </si>
-  <si>
-    <t>매칭시 상대 스킬을 이 스킬로 강제 교체(양쪽 모두 이 스킬의 굴림 1개) · 버프 · 디버프는 그대로 적용 · 동점 무한 재굴림</t>
-  </si>
-  <si>
-    <t>09-16 개정(19~21 버프 면역 → 17~23 버프 적용) · 위력은 공식 이탈(의도)</t>
-  </si>
-  <si>
-    <t>피의 맹세</t>
-  </si>
-  <si>
-    <t>파괴형(조건부)</t>
-  </si>
-  <si>
-    <t>자기 출혈 전부 제거. 제거 직전 수치 — 0~4: 유틸형(파괴 권한 없음) / 5~9: 파괴형(일반) / 10+: 파괴형 + 약화 선행 없이 바로 파괴</t>
-  </si>
-  <si>
-    <t>파괴 권한(조건부)</t>
-  </si>
-  <si>
-    <t>09-14 브레인스토밍</t>
-  </si>
-  <si>
-    <t>전부 되갚다</t>
-  </si>
-  <si>
-    <t>기세 바가 열세 이하(B ≤ −30)이면 이 스킬의 모든 굴림 위력 +4</t>
-  </si>
-  <si>
-    <t>위력·범위 미정 · 09-16 문턱 −70 → −30 · 보너스 6 → 4 · 09-14 브레인스토밍</t>
-  </si>
-  <si>
-    <t>일기토</t>
-  </si>
-  <si>
-    <t>사용시 / 승리시</t>
-  </si>
-  <si>
-    <t>내 다른 슬롯이 같은 상대 슬롯을 조준해도 그 슬롯들의 일방타격은 무효화(포기) · 승리시 그 부위 출혈 +1</t>
-  </si>
-  <si>
-    <t>위력 09-15 조정(17 → 13, 공식값) · 09-14 브레인스토밍</t>
-  </si>
-  <si>
-    <t>도사림</t>
-  </si>
-  <si>
-    <t>공용</t>
-  </si>
-  <si>
-    <t>웅크리기</t>
-  </si>
-  <si>
-    <t>약한</t>
-  </si>
-  <si>
-    <t>방어도 +12</t>
-  </si>
-  <si>
-    <t>전 캐릭터 공용</t>
-  </si>
-  <si>
-    <t>노려보기</t>
-  </si>
-  <si>
-    <t>그 턴 모든 합 판정값 +1</t>
-  </si>
-  <si>
-    <t>강한</t>
-  </si>
-  <si>
-    <t>블로토</t>
-  </si>
-  <si>
-    <t>blót</t>
-  </si>
-  <si>
-    <t>자기 최저 체력 부위 1개 약화 (동점: 팔 → 다리 → 머리) + 광기 +1 + 적에게 공포</t>
-  </si>
-  <si>
-    <t>전투당 1회 사용 기준 수치</t>
-  </si>
-  <si>
-    <t>피의 서약</t>
-  </si>
-  <si>
-    <t>자신에게 출혈 3 + 재생 4 (둘 다 1씩 감쇠)</t>
-  </si>
-  <si>
-    <t>피로 사는 숨</t>
-  </si>
-  <si>
-    <t>자신에게 출혈 2 + 빛 +1</t>
-  </si>
-  <si>
-    <t>광기를 가라앉히다</t>
-  </si>
-  <si>
-    <t>광기 2 소모 → 빛 +1</t>
-  </si>
-  <si>
-    <t>상처를 지우다</t>
-  </si>
-  <si>
-    <t>자기 출혈 10 이상이면 10 제거 → 이번 턴 위력 +4 / 미만이면 방어도 +5</t>
-  </si>
-  <si>
-    <t>흐트러짐을 삼키다</t>
-  </si>
-  <si>
-    <t>자기 흐트러짐 20 소모 → 체력 20 회복 (부족하면 있는 만큼)</t>
+    <t>그 턴 전체 — 모든 적과의 이긴 교환마다 그 상대의 현재 출혈 구간(0~4 / 5~9 / 10+)으로 위세 충전. 충전량 미정</t>
+  </si>
+  <si>
+    <t>09-21 결투에서 도사림으로 이동</t>
   </si>
   <si>
     <t>최후의 저항</t>
@@ -2984,7 +2987,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D62E67B8-44E8-4D2B-9741-6FE27A26FB7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CDFD8C7-AFB5-4BB6-B1EA-3E7E71401E6E}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3174,7 +3177,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD015EF3-AA50-467D-94EA-9FD14434E6B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA7CA0F1-626B-48A0-97BB-597D41EB4380}">
   <dimension ref="A1:T56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5198,22 +5201,22 @@
         <v>194</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="H33" s="9" t="s">
-        <v>100</v>
-      </c>
       <c r="I33" s="9" t="s">
-        <v>108</v>
+        <v>202</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="M33" s="9" t="s">
         <v>1</v>
@@ -5260,22 +5263,22 @@
         <v>194</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="M34" s="9" t="s">
         <v>1</v>
@@ -5299,10 +5302,10 @@
         <v>95</v>
       </c>
       <c r="T34" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>184</v>
       </c>
@@ -5310,22 +5313,22 @@
         <v>221</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G35" s="9" t="s">
         <v>99</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>108</v>
@@ -5352,16 +5355,16 @@
         <v>73</v>
       </c>
       <c r="Q35" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="R35" s="9" t="s">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="S35" s="9" t="s">
         <v>95</v>
       </c>
       <c r="T35" s="10" t="s">
-        <v>231</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -5369,10 +5372,10 @@
         <v>184</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>1</v>
@@ -5381,25 +5384,25 @@
         <v>78</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G36" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H36" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="H36" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="I36" s="9" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>120</v>
+        <v>234</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="M36" s="9" t="s">
         <v>1</v>
@@ -5411,19 +5414,19 @@
         <v>84</v>
       </c>
       <c r="P36" s="9" t="s">
-        <v>73</v>
+        <v>235</v>
       </c>
       <c r="Q36" s="10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="R36" s="9" t="s">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="S36" s="9" t="s">
         <v>95</v>
       </c>
       <c r="T36" s="10" t="s">
-        <v>1</v>
+        <v>237</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -5431,37 +5434,37 @@
         <v>184</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>194</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>99</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>151</v>
+        <v>239</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="M37" s="9" t="s">
         <v>1</v>
@@ -5473,10 +5476,10 @@
         <v>84</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q37" s="10" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="R37" s="9" t="s">
         <v>1</v>
@@ -5485,18 +5488,18 @@
         <v>95</v>
       </c>
       <c r="T37" s="10" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" ht="27" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>184</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>1</v>
@@ -5511,16 +5514,16 @@
         <v>99</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L38" s="9" t="s">
         <v>1</v>
@@ -5535,10 +5538,10 @@
         <v>84</v>
       </c>
       <c r="P38" s="9" t="s">
-        <v>242</v>
+        <v>152</v>
       </c>
       <c r="Q38" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="R38" s="9" t="s">
         <v>1</v>
@@ -5547,7 +5550,7 @@
         <v>95</v>
       </c>
       <c r="T38" s="10" t="s">
-        <v>1</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
@@ -5555,43 +5558,43 @@
         <v>184</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>100</v>
+        <v>247</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>245</v>
+        <v>171</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>84</v>
@@ -5600,27 +5603,27 @@
         <v>152</v>
       </c>
       <c r="Q39" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="R39" s="9" t="s">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="S39" s="9" t="s">
         <v>95</v>
       </c>
       <c r="T39" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>184</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>1</v>
@@ -5632,37 +5635,37 @@
         <v>188</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>171</v>
+        <v>1</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>171</v>
+        <v>1</v>
       </c>
       <c r="N40" s="9" t="s">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="O40" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P40" s="9" t="s">
-        <v>152</v>
+        <v>251</v>
       </c>
       <c r="Q40" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="R40" s="9" t="s">
         <v>220</v>
@@ -5671,18 +5674,18 @@
         <v>95</v>
       </c>
       <c r="T40" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" ht="27" x14ac:dyDescent="0.3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="54" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
         <v>184</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>1</v>
@@ -5691,22 +5694,22 @@
         <v>78</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>188</v>
+        <v>255</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="H41" s="9" t="s">
-        <v>79</v>
-      </c>
       <c r="I41" s="9" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>252</v>
+        <v>166</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>1</v>
+        <v>189</v>
       </c>
       <c r="L41" s="9" t="s">
         <v>1</v>
@@ -5721,19 +5724,19 @@
         <v>84</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>253</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="R41" s="9" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="S41" s="9" t="s">
         <v>95</v>
       </c>
       <c r="T41" s="10" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -5741,10 +5744,10 @@
         <v>184</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>1</v>
@@ -5753,7 +5756,7 @@
         <v>78</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>257</v>
+        <v>194</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>99</v>
@@ -5762,13 +5765,13 @@
         <v>100</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="L42" s="9" t="s">
         <v>1</v>
@@ -5786,16 +5789,16 @@
         <v>152</v>
       </c>
       <c r="Q42" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="R42" s="9" t="s">
-        <v>259</v>
+        <v>1</v>
       </c>
       <c r="S42" s="9" t="s">
         <v>95</v>
       </c>
       <c r="T42" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -5803,10 +5806,10 @@
         <v>184</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>1</v>
@@ -5815,25 +5818,25 @@
         <v>78</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="H43" s="9" t="s">
         <v>100</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="M43" s="9" t="s">
         <v>1</v>
@@ -5845,107 +5848,107 @@
         <v>84</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="Q43" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="R43" s="9" t="s">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="S43" s="9" t="s">
         <v>95</v>
       </c>
       <c r="T43" s="10" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" ht="27" x14ac:dyDescent="0.3">
-      <c r="A44" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="K44" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="L44" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="M44" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="N44" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="O44" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="P44" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="Q44" s="10" t="s">
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="R44" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="S44" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="T44" s="10" t="s">
+      <c r="B44" s="7" t="s">
         <v>267</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="O44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P44" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q44" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="R44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="S44" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="T44" s="8" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B45" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>271</v>
-      </c>
       <c r="G45" s="7" t="s">
         <v>1</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I45" s="7" t="s">
         <v>1</v>
@@ -5966,13 +5969,13 @@
         <v>1</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="P45" s="7" t="s">
         <v>152</v>
       </c>
       <c r="Q45" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="R45" s="7" t="s">
         <v>1</v>
@@ -5981,27 +5984,27 @@
         <v>49</v>
       </c>
       <c r="T45" s="8" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C46" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="7" t="s">
         <v>274</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>271</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>1</v>
@@ -6034,7 +6037,7 @@
         <v>152</v>
       </c>
       <c r="Q46" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="R46" s="7" t="s">
         <v>1</v>
@@ -6043,27 +6046,27 @@
         <v>49</v>
       </c>
       <c r="T46" s="8" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" ht="27" x14ac:dyDescent="0.3">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>278</v>
+        <v>1</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>1</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>1</v>
@@ -6096,24 +6099,24 @@
         <v>152</v>
       </c>
       <c r="Q47" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="R47" s="7" t="s">
         <v>1</v>
       </c>
       <c r="S47" s="7" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="T47" s="8" t="s">
-        <v>280</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>281</v>
@@ -6125,13 +6128,13 @@
         <v>1</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>1</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>1</v>
@@ -6172,10 +6175,10 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>283</v>
@@ -6187,7 +6190,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>1</v>
@@ -6234,10 +6237,10 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>285</v>
@@ -6249,13 +6252,13 @@
         <v>1</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>1</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>1</v>
@@ -6296,10 +6299,10 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>287</v>
@@ -6311,7 +6314,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>1</v>
@@ -6356,12 +6359,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>289</v>
@@ -6373,7 +6376,7 @@
         <v>1</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>1</v>
@@ -6415,18 +6418,18 @@
         <v>95</v>
       </c>
       <c r="T52" s="8" t="s">
-        <v>1</v>
+        <v>291</v>
       </c>
     </row>
     <row r="53" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>1</v>
@@ -6435,7 +6438,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>1</v>
@@ -6465,30 +6468,30 @@
         <v>1</v>
       </c>
       <c r="P53" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q53" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R53" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="S53" s="7" t="s">
         <v>95</v>
       </c>
       <c r="T53" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>1</v>
@@ -6497,7 +6500,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>1</v>
@@ -6527,10 +6530,10 @@
         <v>1</v>
       </c>
       <c r="P54" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q54" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R54" s="9" t="s">
         <v>1</v>
@@ -6544,13 +6547,13 @@
     </row>
     <row r="55" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>1</v>
@@ -6559,7 +6562,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>1</v>
@@ -6589,10 +6592,10 @@
         <v>1</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q55" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R55" s="9" t="s">
         <v>1</v>
@@ -6606,13 +6609,13 @@
     </row>
     <row r="56" spans="1:20" ht="27" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>1</v>
@@ -6621,7 +6624,7 @@
         <v>1</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>1</v>
@@ -6651,10 +6654,10 @@
         <v>1</v>
       </c>
       <c r="P56" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q56" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R56" s="9" t="s">
         <v>1</v>
@@ -6667,14 +6670,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T56" xr:uid="{FD015EF3-AA50-467D-94EA-9FD14434E6B1}"/>
+  <autoFilter ref="A1:T56" xr:uid="{BA7CA0F1-626B-48A0-97BB-597D41EB4380}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6F0D953-91D5-49AD-8D4C-4CA51841DC62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65353E3D-F3FB-4916-B858-568950D65868}">
   <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6713,13 +6716,13 @@
         <v>39</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>41</v>
@@ -6739,7 +6742,7 @@
         <v>44</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>1</v>
@@ -6754,13 +6757,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>1</v>
@@ -6769,7 +6772,7 @@
         <v>49</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -6780,7 +6783,7 @@
         <v>51</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>1</v>
@@ -6795,13 +6798,13 @@
         <v>1</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>1</v>
@@ -6810,7 +6813,7 @@
         <v>49</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -6821,7 +6824,7 @@
         <v>51</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>1</v>
@@ -6833,16 +6836,16 @@
         <v>1</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>1</v>
@@ -6859,10 +6862,10 @@
         <v>50</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>1</v>
@@ -6874,16 +6877,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>1</v>
@@ -6892,7 +6895,7 @@
         <v>49</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="67.5" x14ac:dyDescent="0.3">
@@ -6900,10 +6903,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>1</v>
@@ -6918,13 +6921,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>1</v>
@@ -6933,7 +6936,7 @@
         <v>49</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -6941,10 +6944,10 @@
         <v>66</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>1</v>
@@ -6965,7 +6968,7 @@
         <v>47</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>1</v>
@@ -6982,10 +6985,10 @@
         <v>66</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>1</v>
@@ -7006,7 +7009,7 @@
         <v>47</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>220</v>
@@ -7026,7 +7029,7 @@
         <v>47</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>78</v>
@@ -7041,13 +7044,13 @@
         <v>73</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>1</v>
@@ -7067,7 +7070,7 @@
         <v>47</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>90</v>
@@ -7082,13 +7085,13 @@
         <v>73</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>1</v>
@@ -7108,7 +7111,7 @@
         <v>47</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>78</v>
@@ -7123,13 +7126,13 @@
         <v>152</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>1</v>
@@ -7138,7 +7141,7 @@
         <v>49</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -7149,7 +7152,7 @@
         <v>47</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>90</v>
@@ -7167,10 +7170,10 @@
         <v>175</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>1</v>
@@ -7179,7 +7182,7 @@
         <v>49</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7190,7 +7193,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>78</v>
@@ -7205,22 +7208,22 @@
         <v>73</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -7231,7 +7234,7 @@
         <v>47</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>78</v>
@@ -7246,13 +7249,13 @@
         <v>73</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>1</v>
@@ -7261,7 +7264,7 @@
         <v>49</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -7272,7 +7275,7 @@
         <v>47</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>90</v>
@@ -7287,13 +7290,13 @@
         <v>152</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>1</v>
@@ -7302,7 +7305,7 @@
         <v>49</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7313,7 +7316,7 @@
         <v>47</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>78</v>
@@ -7328,22 +7331,22 @@
         <v>152</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7354,7 +7357,7 @@
         <v>47</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>90</v>
@@ -7369,22 +7372,22 @@
         <v>73</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -7392,10 +7395,10 @@
         <v>184</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>78</v>
@@ -7410,13 +7413,13 @@
         <v>73</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K18" s="9" t="s">
         <v>1</v>
@@ -7425,7 +7428,7 @@
         <v>49</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7433,10 +7436,10 @@
         <v>184</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>78</v>
@@ -7451,13 +7454,13 @@
         <v>73</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>1</v>
@@ -7466,7 +7469,7 @@
         <v>49</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -7474,10 +7477,10 @@
         <v>184</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>90</v>
@@ -7492,13 +7495,13 @@
         <v>152</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>1</v>
@@ -7515,10 +7518,10 @@
         <v>184</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>90</v>
@@ -7530,16 +7533,16 @@
         <v>100</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>1</v>
@@ -7548,7 +7551,7 @@
         <v>49</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -7556,10 +7559,10 @@
         <v>184</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>90</v>
@@ -7571,16 +7574,16 @@
         <v>100</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>1</v>
@@ -7597,10 +7600,10 @@
         <v>184</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>78</v>
@@ -7615,13 +7618,13 @@
         <v>73</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>1</v>
@@ -7630,7 +7633,7 @@
         <v>49</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -7638,10 +7641,10 @@
         <v>184</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>78</v>
@@ -7656,13 +7659,13 @@
         <v>73</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>1</v>
@@ -7679,10 +7682,10 @@
         <v>184</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>90</v>
@@ -7697,13 +7700,13 @@
         <v>73</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>1</v>
@@ -7712,7 +7715,7 @@
         <v>49</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7720,10 +7723,10 @@
         <v>184</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>78</v>
@@ -7735,16 +7738,16 @@
         <v>100</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>1</v>
@@ -7761,10 +7764,10 @@
         <v>184</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>78</v>
@@ -7779,13 +7782,13 @@
         <v>152</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>1</v>
@@ -7794,7 +7797,7 @@
         <v>49</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7802,10 +7805,10 @@
         <v>184</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>78</v>
@@ -7820,13 +7823,13 @@
         <v>73</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>1</v>
@@ -7835,7 +7838,7 @@
         <v>49</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7843,10 +7846,10 @@
         <v>184</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>90</v>
@@ -7861,13 +7864,13 @@
         <v>73</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>1</v>
@@ -7876,7 +7879,7 @@
         <v>49</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="27" x14ac:dyDescent="0.3">
@@ -7884,10 +7887,10 @@
         <v>184</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>90</v>
@@ -7902,13 +7905,13 @@
         <v>152</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>1</v>
@@ -7917,7 +7920,7 @@
         <v>49</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -7925,10 +7928,10 @@
         <v>184</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>78</v>
@@ -7943,22 +7946,22 @@
         <v>73</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L31" s="9" t="s">
         <v>49</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -7966,10 +7969,10 @@
         <v>184</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>78</v>
@@ -7984,13 +7987,13 @@
         <v>152</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>1</v>
@@ -7999,7 +8002,7 @@
         <v>49</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
@@ -8007,10 +8010,10 @@
         <v>184</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>78</v>
@@ -8019,19 +8022,19 @@
         <v>1</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>152</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>1</v>
@@ -8040,24 +8043,24 @@
         <v>49</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="D34" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="7" t="s">
         <v>269</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>271</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>80</v>
@@ -8066,13 +8069,13 @@
         <v>152</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K34" s="7" t="s">
         <v>1</v>
@@ -8086,19 +8089,19 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>269</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>271</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>100</v>
@@ -8107,13 +8110,13 @@
         <v>152</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>1</v>
@@ -8127,19 +8130,19 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>100</v>
@@ -8148,13 +8151,13 @@
         <v>152</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>1</v>
@@ -8168,19 +8171,19 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>100</v>
@@ -8189,13 +8192,13 @@
         <v>152</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>1</v>
@@ -8209,34 +8212,34 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>100</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>1</v>
@@ -8245,39 +8248,39 @@
         <v>49</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>100</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>1</v>
@@ -8286,24 +8289,24 @@
         <v>49</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>80</v>
@@ -8312,13 +8315,13 @@
         <v>152</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>1</v>
@@ -8327,24 +8330,24 @@
         <v>49</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>80</v>
@@ -8353,13 +8356,13 @@
         <v>152</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>1</v>
@@ -8368,24 +8371,24 @@
         <v>49</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>80</v>
@@ -8394,13 +8397,13 @@
         <v>152</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K42" s="7" t="s">
         <v>1</v>
@@ -8409,39 +8412,39 @@
         <v>49</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K43" s="9" t="s">
         <v>1</v>
@@ -8455,34 +8458,34 @@
     </row>
     <row r="44" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K44" s="9" t="s">
         <v>1</v>
@@ -8496,34 +8499,34 @@
     </row>
     <row r="45" spans="1:13" ht="27" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>1</v>
@@ -8536,14 +8539,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M45" xr:uid="{D6F0D953-91D5-49AD-8D4C-4CA51841DC62}"/>
+  <autoFilter ref="A1:M45" xr:uid="{65353E3D-F3FB-4916-B858-568950D65868}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8174A24B-6841-4F72-8CE9-5A6BFD5DF5DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F41A63-D94E-4F7B-8F3F-F683B7891A87}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8561,201 +8564,201 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>38</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>79</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>136</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>99</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>47</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>100</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>144</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>47</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{8174A24B-6841-4F72-8CE9-5A6BFD5DF5DB}"/>
+  <autoFilter ref="A1:O4" xr:uid="{12F41A63-D94E-4F7B-8F3F-F683B7891A87}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E0ADDE-40BA-4A61-9AAB-66E9F829273A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309047DA-5A38-4E5A-8C49-57889D2B7380}">
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8846,10 +8849,10 @@
         <v>44</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>1</v>
@@ -8888,7 +8891,7 @@
         <v>47</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R2" s="13" t="s">
         <v>1</v>
@@ -8897,7 +8900,7 @@
         <v>49</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -8905,10 +8908,10 @@
         <v>66</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>1</v>
@@ -8950,7 +8953,7 @@
         <v>47</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R3" s="11" t="s">
         <v>1</v>
@@ -8970,7 +8973,7 @@
         <v>58</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>1</v>
@@ -9012,7 +9015,7 @@
         <v>47</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="R4" s="13" t="s">
         <v>1</v>
@@ -9021,7 +9024,7 @@
         <v>49</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="54" x14ac:dyDescent="0.3">
@@ -9029,10 +9032,10 @@
         <v>66</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>1</v>
@@ -9071,10 +9074,10 @@
         <v>1</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="R5" s="11" t="s">
         <v>1</v>
@@ -9094,7 +9097,7 @@
         <v>67</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>1</v>
@@ -9136,13 +9139,13 @@
         <v>73</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="R6" s="11" t="s">
         <v>1</v>
       </c>
       <c r="S6" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="T6" s="12" t="s">
         <v>1</v>
@@ -9153,19 +9156,19 @@
         <v>184</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>84</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>135</v>
@@ -9177,37 +9180,37 @@
         <v>114</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>1</v>
       </c>
       <c r="O7" s="13" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P7" s="13" t="s">
         <v>139</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="R7" s="13" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S7" s="13" t="s">
         <v>49</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9215,19 +9218,19 @@
         <v>184</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>84</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>99</v>
@@ -9236,13 +9239,13 @@
         <v>100</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L8" s="14" t="s">
         <v>1</v>
@@ -9254,22 +9257,22 @@
         <v>1</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P8" s="13" t="s">
         <v>139</v>
       </c>
       <c r="Q8" s="14" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="R8" s="13" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="S8" s="13" t="s">
         <v>49</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9277,10 +9280,10 @@
         <v>184</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>1</v>
@@ -9301,28 +9304,28 @@
         <v>164</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P9" s="13" t="s">
         <v>152</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="R9" s="13" t="s">
         <v>1</v>
@@ -9331,7 +9334,7 @@
         <v>49</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9339,10 +9342,10 @@
         <v>75</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>1</v>
@@ -9351,7 +9354,7 @@
         <v>84</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>99</v>
@@ -9360,13 +9363,13 @@
         <v>80</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L10" s="12" t="s">
         <v>1</v>
@@ -9378,22 +9381,22 @@
         <v>1</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P10" s="11" t="s">
         <v>139</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S10" s="11" t="s">
         <v>49</v>
       </c>
       <c r="T10" s="12" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -9401,10 +9404,10 @@
         <v>75</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>1</v>
@@ -9425,13 +9428,13 @@
         <v>108</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M11" s="12" t="s">
         <v>1</v>
@@ -9440,13 +9443,13 @@
         <v>1</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="R11" s="11" t="s">
         <v>1</v>
@@ -9460,22 +9463,22 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="D12" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>269</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>271</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>1</v>
@@ -9508,7 +9511,7 @@
         <v>152</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="R12" s="13" t="s">
         <v>1</v>
@@ -9522,22 +9525,22 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B13" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>269</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>271</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>1</v>
@@ -9570,7 +9573,7 @@
         <v>152</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="R13" s="13" t="s">
         <v>1</v>
@@ -9584,13 +9587,13 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>1</v>
@@ -9599,7 +9602,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>1</v>
@@ -9632,7 +9635,7 @@
         <v>152</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="R14" s="13" t="s">
         <v>1</v>
@@ -9641,18 +9644,18 @@
         <v>49</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>1</v>
@@ -9661,7 +9664,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>1</v>
@@ -9694,7 +9697,7 @@
         <v>152</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="R15" s="13" t="s">
         <v>1</v>
@@ -9708,13 +9711,13 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>1</v>
@@ -9723,7 +9726,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>1</v>
@@ -9756,13 +9759,13 @@
         <v>152</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="R16" s="13" t="s">
         <v>1</v>
       </c>
       <c r="S16" s="13" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="T16" s="14" t="s">
         <v>1</v>
@@ -9770,13 +9773,13 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>1</v>
@@ -9785,7 +9788,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>1</v>
@@ -9818,7 +9821,7 @@
         <v>152</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="R17" s="13" t="s">
         <v>1</v>
@@ -9827,18 +9830,18 @@
         <v>49</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>1</v>
@@ -9847,7 +9850,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>1</v>
@@ -9877,10 +9880,10 @@
         <v>1</v>
       </c>
       <c r="P18" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="R18" s="11" t="s">
         <v>1</v>
@@ -9894,13 +9897,13 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>1</v>
@@ -9909,7 +9912,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>1</v>
@@ -9939,10 +9942,10 @@
         <v>1</v>
       </c>
       <c r="P19" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="R19" s="11" t="s">
         <v>1</v>
@@ -9956,13 +9959,13 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>1</v>
@@ -9971,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>1</v>
@@ -10001,10 +10004,10 @@
         <v>1</v>
       </c>
       <c r="P20" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="R20" s="11" t="s">
         <v>1</v>
@@ -10017,14 +10020,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T20" xr:uid="{B7E0ADDE-40BA-4A61-9AAB-66E9F829273A}"/>
+  <autoFilter ref="A1:T20" xr:uid="{309047DA-5A38-4E5A-8C49-57889D2B7380}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773347AF-DDFA-4B79-A42D-F01B49E27F7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C2960E-3FF7-43AF-B3B4-74CE1E6F29F9}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10039,7 +10042,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>26</v>
@@ -10048,13 +10051,13 @@
         <v>24</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>43</v>
@@ -10062,91 +10065,91 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>591</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>592</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>589</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>1</v>
@@ -10154,22 +10157,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>1</v>
@@ -10177,22 +10180,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>1</v>
@@ -10200,128 +10203,128 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12" xr:uid="{773347AF-DDFA-4B79-A42D-F01B49E27F7E}"/>
+  <autoFilter ref="A1:G12" xr:uid="{12C2960E-3FF7-43AF-B3B4-74CE1E6F29F9}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD494A91-F35B-49C9-B44F-AEE561CC93EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97CC6593-7EF8-476D-9BF3-5071D1B0DE71}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10335,19 +10338,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>40</v>
@@ -10358,22 +10361,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>49</v>
@@ -10381,22 +10384,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>49</v>
@@ -10404,22 +10407,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>49</v>
@@ -10427,22 +10430,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>49</v>
@@ -10450,22 +10453,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>49</v>
@@ -10473,22 +10476,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>49</v>
@@ -10496,22 +10499,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>49</v>
@@ -10519,22 +10522,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>49</v>
@@ -10542,22 +10545,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>49</v>
@@ -10565,13 +10568,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>100</v>
@@ -10580,7 +10583,7 @@
         <v>185</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>49</v>
@@ -10588,22 +10591,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>49</v>
@@ -10611,22 +10614,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>49</v>
@@ -10634,22 +10637,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>49</v>
@@ -10657,22 +10660,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>49</v>
@@ -10680,22 +10683,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>49</v>
@@ -10703,45 +10706,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>49</v>
@@ -10749,22 +10752,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>49</v>
@@ -10772,22 +10775,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>49</v>
@@ -10795,22 +10798,22 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>49</v>
@@ -10818,22 +10821,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>49</v>
@@ -10841,22 +10844,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>49</v>
@@ -10864,22 +10867,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>49</v>
@@ -10887,22 +10890,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>49</v>
@@ -10910,22 +10913,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>49</v>
@@ -10933,22 +10936,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>49</v>
@@ -10956,183 +10959,183 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>697</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>698</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>49</v>
@@ -11140,68 +11143,68 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>49</v>
@@ -11209,22 +11212,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>49</v>
@@ -11232,22 +11235,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>49</v>
@@ -11255,22 +11258,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>49</v>
@@ -11278,22 +11281,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>49</v>
@@ -11301,22 +11304,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>49</v>
@@ -11324,45 +11327,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>49</v>
@@ -11370,22 +11373,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>49</v>
@@ -11393,22 +11396,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>49</v>
@@ -11416,22 +11419,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>49</v>
@@ -11439,22 +11442,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>49</v>
@@ -11462,22 +11465,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>49</v>
@@ -11485,22 +11488,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>49</v>
@@ -11508,22 +11511,22 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>49</v>
@@ -11531,22 +11534,22 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>49</v>
@@ -11554,22 +11557,22 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>49</v>
@@ -11577,22 +11580,22 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>79</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>49</v>
@@ -11600,68 +11603,68 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>759</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>757</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>758</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>49</v>
@@ -11669,22 +11672,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>49</v>
@@ -11692,22 +11695,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>49</v>
@@ -11715,22 +11718,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>49</v>
@@ -11738,22 +11741,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>49</v>
@@ -11761,22 +11764,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>49</v>
@@ -11784,36 +11787,36 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>49</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{BD494A91-F35B-49C9-B44F-AEE561CC93EF}"/>
+  <autoFilter ref="A1:G64" xr:uid="{97CC6593-7EF8-476D-9BF3-5071D1B0DE71}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF10550-676B-49DE-8D84-0DBF5911EA88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19E418AB-E59F-478B-9258-09E92E136816}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11827,10 +11830,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>30</v>
@@ -11842,7 +11845,7 @@
         <v>184</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>43</v>
@@ -11850,10 +11853,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>79</v>
@@ -11862,21 +11865,21 @@
         <v>81</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>47</v>
@@ -11885,21 +11888,21 @@
         <v>108</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>47</v>
@@ -11911,18 +11914,18 @@
         <v>47</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>47</v>
@@ -11934,18 +11937,18 @@
         <v>47</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>79</v>
@@ -11954,21 +11957,21 @@
         <v>164</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>99</v>
@@ -11977,21 +11980,21 @@
         <v>108</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>47</v>
@@ -12003,14 +12006,14 @@
         <v>47</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{1DF10550-676B-49DE-8D84-0DBF5911EA88}"/>
+  <autoFilter ref="A1:G8" xr:uid="{19E418AB-E59F-478B-9258-09E92E136816}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/캐릭터 스킬 스펙.xlsx
+++ b/Docs/캐릭터 스킬 스펙.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0103\AppData\Local\Temp\claude\C--Users-a0103-OneDrive-Desktop-Poem-Of-Machine\34655a05-bcd9-45dd-9f4c-0a3c6b4a43fb\scratchpad\rules0921\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{494FE809-51BE-4979-9F51-E913C029A9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE22C326-5B28-498D-9E8F-523CE60444A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{731E2743-826B-4A13-BF59-6E68C628C44A}"/>
+    <workbookView xWindow="2685" yWindow="2625" windowWidth="16770" windowHeight="15345" xr2:uid="{4B2176CF-BF59-4E64-A8BF-15ACF6BF7E2C}"/>
   </bookViews>
   <sheets>
     <sheet name="읽는 법" sheetId="1" r:id="rId1"/>
@@ -330,147 +330,150 @@
     <t>BLUE</t>
   </si>
   <si>
-    <t>10~28</t>
+    <t>12</t>
+  </si>
+  <si>
+    <t>11~29</t>
+  </si>
+  <si>
+    <t>13~20</t>
+  </si>
+  <si>
+    <t>13~16</t>
+  </si>
+  <si>
+    <t>승리시 짓눌린 상태면 광기 +1 추가</t>
+  </si>
+  <si>
+    <t>잠정</t>
+  </si>
+  <si>
+    <t>09-16 굴림 역순(강 → 약)</t>
+  </si>
+  <si>
+    <t>#3</t>
+  </si>
+  <si>
+    <t>쪼개기</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17~22</t>
+  </si>
+  <si>
+    <t>17~26</t>
+  </si>
+  <si>
+    <t>없음 (순수 화력)</t>
+  </si>
+  <si>
+    <t>위력 09-16 조정(+2)</t>
+  </si>
+  <si>
+    <t>#4</t>
+  </si>
+  <si>
+    <t>버텨내기</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>22~27</t>
+  </si>
+  <si>
+    <t>7~18</t>
+  </si>
+  <si>
+    <t>광기 +2 (기본 +1 대신)</t>
+  </si>
+  <si>
+    <t>#5</t>
+  </si>
+  <si>
+    <t>후려치기</t>
+  </si>
+  <si>
+    <t>13~18</t>
+  </si>
+  <si>
+    <t>16~23</t>
+  </si>
+  <si>
+    <t>출혈에 더해 광기 +1</t>
+  </si>
+  <si>
+    <t>#6</t>
+  </si>
+  <si>
+    <t>받아넘기기</t>
+  </si>
+  <si>
+    <t>15~22</t>
+  </si>
+  <si>
+    <t>16~21</t>
+  </si>
+  <si>
+    <t>없음 (순수 안정)</t>
+  </si>
+  <si>
+    <t>#7</t>
+  </si>
+  <si>
+    <t>몰아치기</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>13~19</t>
+  </si>
+  <si>
+    <t>12~17</t>
+  </si>
+  <si>
+    <t>10~16</t>
+  </si>
+  <si>
+    <t>8~14</t>
+  </si>
+  <si>
+    <t>1번째 승리시 출혈 +2 추가 · 2~5번째 승리시 출혈 +1 추가</t>
+  </si>
+  <si>
+    <t>09-16 굴림 역순(강 → 약) · 효과도 굴림을 따라 옮김</t>
+  </si>
+  <si>
+    <t>#8</t>
+  </si>
+  <si>
+    <t>다시 일어서다</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>3~10</t>
   </si>
   <si>
     <t>12~19</t>
   </si>
   <si>
-    <t>12~15</t>
-  </si>
-  <si>
-    <t>승리시 짓눌린 상태면 광기 +1 추가</t>
-  </si>
-  <si>
-    <t>잠정</t>
-  </si>
-  <si>
-    <t>09-16 굴림 역순(강 → 약)</t>
-  </si>
-  <si>
-    <t>#3</t>
-  </si>
-  <si>
-    <t>쪼개기</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17~22</t>
-  </si>
-  <si>
-    <t>17~26</t>
-  </si>
-  <si>
-    <t>없음 (순수 화력)</t>
-  </si>
-  <si>
-    <t>위력 09-16 조정(+2)</t>
-  </si>
-  <si>
-    <t>#4</t>
-  </si>
-  <si>
-    <t>버텨내기</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>22~27</t>
-  </si>
-  <si>
-    <t>7~18</t>
-  </si>
-  <si>
-    <t>광기 +2 (기본 +1 대신)</t>
-  </si>
-  <si>
-    <t>#5</t>
-  </si>
-  <si>
-    <t>후려치기</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13~18</t>
-  </si>
-  <si>
-    <t>16~23</t>
-  </si>
-  <si>
-    <t>출혈에 더해 광기 +1</t>
-  </si>
-  <si>
-    <t>#6</t>
-  </si>
-  <si>
-    <t>받아넘기기</t>
-  </si>
-  <si>
-    <t>15~22</t>
-  </si>
-  <si>
-    <t>16~21</t>
-  </si>
-  <si>
-    <t>없음 (순수 안정)</t>
-  </si>
-  <si>
-    <t>#7</t>
-  </si>
-  <si>
-    <t>몰아치기</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>13~19</t>
-  </si>
-  <si>
-    <t>12~17</t>
-  </si>
-  <si>
-    <t>10~16</t>
-  </si>
-  <si>
-    <t>8~14</t>
-  </si>
-  <si>
-    <t>1번째 승리시 출혈 +2 추가 · 2~5번째 승리시 출혈 +1 추가</t>
-  </si>
-  <si>
-    <t>09-16 굴림 역순(강 → 약) · 효과도 굴림을 따라 옮김</t>
-  </si>
-  <si>
-    <t>#8</t>
-  </si>
-  <si>
-    <t>다시 일어서다</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>3~10</t>
-  </si>
-  <si>
     <t>4~11</t>
   </si>
   <si>
@@ -540,6 +543,12 @@
     <t>선수치기</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>18~23</t>
+  </si>
+  <si>
     <t>다음 턴 이 슬롯 속도 굴림을 최댓값으로 고정</t>
   </si>
   <si>
@@ -549,16 +558,10 @@
     <t>약점을 노리다</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>18~25</t>
   </si>
   <si>
-    <t>13~20</t>
-  </si>
-  <si>
-    <t>1번째 승리시 상대 쇠약(다음 턴) · 2번째 승리시 상대 출혈 5+면 균열(다음 턴) · 3번째 위력 = 상대 부정적 상태 개수당 +1</t>
+    <t>1번째 승리시 다음 턴 상대에게 쇠약 1만큼 3턴 부여 · 2번째 승리시 상대 출혈 5+면 균열(다음 턴) · 3번째 위력 = 상대 부정적 상태 개수당 +1</t>
   </si>
   <si>
     <t>#15</t>
@@ -570,9 +573,6 @@
     <t>17~24</t>
   </si>
   <si>
-    <t>18~23</t>
-  </si>
-  <si>
     <t>상대에게 고통</t>
   </si>
   <si>
@@ -603,7 +603,7 @@
     <t>20~32</t>
   </si>
   <si>
-    <t>2번째 승리시 상대 출혈 +1 추가 + 자신 출혈 1</t>
+    <t>2번째 승리시 상대 출혈 +2 추가 + 자신 출혈 1</t>
   </si>
   <si>
     <t>위력 09-16 조정(+3)</t>
@@ -2987,7 +2987,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CDFD8C7-AFB5-4BB6-B1EA-3E7E71401E6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{365B63C1-F8B9-4195-9D6A-85A0F60E5959}">
   <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3177,7 +3177,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA7CA0F1-626B-48A0-97BB-597D41EB4380}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5EC2AC1-BCB5-437C-A346-AEDF6AB2CA86}">
   <dimension ref="A1:T56"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3719,16 +3719,16 @@
         <v>80</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>1</v>
@@ -3743,16 +3743,16 @@
         <v>73</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R9" s="7" t="s">
         <v>1</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
@@ -3760,10 +3760,10 @@
         <v>75</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>1</v>
@@ -3775,19 +3775,19 @@
         <v>1</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>1</v>
@@ -3805,16 +3805,16 @@
         <v>47</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R10" s="7" t="s">
         <v>1</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
@@ -3822,10 +3822,10 @@
         <v>75</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>1</v>
@@ -3837,19 +3837,19 @@
         <v>1</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>1</v>
@@ -3867,13 +3867,13 @@
         <v>73</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R11" s="7" t="s">
         <v>1</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T11" s="8" t="s">
         <v>1</v>
@@ -3884,10 +3884,10 @@
         <v>75</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>1</v>
@@ -3899,13 +3899,13 @@
         <v>1</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>80</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>115</v>
@@ -3935,7 +3935,7 @@
         <v>1</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T12" s="8" t="s">
         <v>1</v>
@@ -3961,13 +3961,13 @@
         <v>1</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>80</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>120</v>
@@ -3997,10 +3997,10 @@
         <v>1</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T13" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="27" x14ac:dyDescent="0.3">
@@ -4026,7 +4026,7 @@
         <v>125</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>126</v>
@@ -4059,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T14" s="8" t="s">
         <v>132</v>
@@ -4088,7 +4088,7 @@
         <v>135</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>136</v>
@@ -4100,10 +4100,10 @@
         <v>137</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N15" s="7" t="s">
         <v>1</v>
@@ -4112,19 +4112,19 @@
         <v>84</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R15" s="7" t="s">
         <v>1</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T15" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
@@ -4132,10 +4132,10 @@
         <v>75</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>1</v>
@@ -4147,16 +4147,16 @@
         <v>1</v>
       </c>
       <c r="G16" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>99</v>
-      </c>
       <c r="I16" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>1</v>
@@ -4177,16 +4177,16 @@
         <v>73</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R16" s="7" t="s">
         <v>1</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T16" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -4194,10 +4194,10 @@
         <v>75</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>1</v>
@@ -4209,19 +4209,19 @@
         <v>1</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>1</v>
@@ -4236,16 +4236,16 @@
         <v>84</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R17" s="7" t="s">
         <v>1</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T17" s="8" t="s">
         <v>1</v>
@@ -4256,10 +4256,10 @@
         <v>75</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>1</v>
@@ -4274,10 +4274,10 @@
         <v>79</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>115</v>
@@ -4286,7 +4286,7 @@
         <v>120</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>1</v>
@@ -4301,16 +4301,16 @@
         <v>73</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R18" s="7" t="s">
         <v>1</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -4318,10 +4318,10 @@
         <v>75</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>1</v>
@@ -4333,19 +4333,19 @@
         <v>1</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>80</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>1</v>
@@ -4363,13 +4363,13 @@
         <v>73</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="R19" s="7" t="s">
         <v>1</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T19" s="8" t="s">
         <v>1</v>
@@ -4380,10 +4380,10 @@
         <v>75</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>1</v>
@@ -4398,19 +4398,19 @@
         <v>79</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>128</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>1</v>
@@ -4425,13 +4425,13 @@
         <v>73</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="R20" s="7" t="s">
         <v>1</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T20" s="8" t="s">
         <v>1</v>
@@ -4442,10 +4442,10 @@
         <v>75</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>1</v>
@@ -4457,19 +4457,19 @@
         <v>1</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>1</v>
@@ -4493,10 +4493,10 @@
         <v>1</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T21" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
@@ -4519,19 +4519,19 @@
         <v>1</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>1</v>
@@ -4546,7 +4546,7 @@
         <v>84</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q22" s="8" t="s">
         <v>175</v>
@@ -4555,7 +4555,7 @@
         <v>1</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T22" s="8" t="s">
         <v>176</v>
@@ -4581,10 +4581,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>179</v>
@@ -4617,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="S23" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T23" s="8" t="s">
         <v>183</v>
@@ -4643,16 +4643,16 @@
         <v>188</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>189</v>
@@ -4679,7 +4679,7 @@
         <v>191</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T24" s="10" t="s">
         <v>1</v>
@@ -4708,10 +4708,10 @@
         <v>79</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>120</v>
@@ -4741,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T25" s="10" t="s">
         <v>1</v>
@@ -4767,13 +4767,13 @@
         <v>188</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>198</v>
@@ -4803,7 +4803,7 @@
         <v>191</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T26" s="10" t="s">
         <v>199</v>
@@ -4832,7 +4832,7 @@
         <v>79</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>202</v>
@@ -4865,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T27" s="10" t="s">
         <v>1</v>
@@ -4891,19 +4891,19 @@
         <v>194</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>202</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="L28" s="9" t="s">
         <v>1</v>
@@ -4927,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T28" s="10" t="s">
         <v>1</v>
@@ -4956,19 +4956,19 @@
         <v>79</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I29" s="9" t="s">
         <v>202</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>116</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M29" s="9" t="s">
         <v>1</v>
@@ -4989,7 +4989,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T29" s="10" t="s">
         <v>1</v>
@@ -5015,19 +5015,19 @@
         <v>194</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="L30" s="9" t="s">
         <v>1</v>
@@ -5051,7 +5051,7 @@
         <v>1</v>
       </c>
       <c r="S30" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T30" s="10" t="s">
         <v>1</v>
@@ -5077,13 +5077,13 @@
         <v>188</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>217</v>
@@ -5113,7 +5113,7 @@
         <v>220</v>
       </c>
       <c r="S31" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T31" s="10" t="s">
         <v>1</v>
@@ -5139,7 +5139,7 @@
         <v>188</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>80</v>
@@ -5151,7 +5151,7 @@
         <v>116</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L32" s="9" t="s">
         <v>1</v>
@@ -5175,7 +5175,7 @@
         <v>220</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T32" s="10" t="s">
         <v>224</v>
@@ -5204,7 +5204,7 @@
         <v>79</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>202</v>
@@ -5213,7 +5213,7 @@
         <v>116</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L33" s="9" t="s">
         <v>116</v>
@@ -5237,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="S33" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T33" s="10" t="s">
         <v>1</v>
@@ -5263,13 +5263,13 @@
         <v>194</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>120</v>
@@ -5299,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="S34" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T34" s="10" t="s">
         <v>229</v>
@@ -5325,13 +5325,13 @@
         <v>188</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>120</v>
@@ -5361,7 +5361,7 @@
         <v>220</v>
       </c>
       <c r="S35" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T35" s="10" t="s">
         <v>1</v>
@@ -5390,19 +5390,19 @@
         <v>79</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>234</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M36" s="9" t="s">
         <v>1</v>
@@ -5423,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="S36" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T36" s="10" t="s">
         <v>237</v>
@@ -5449,13 +5449,13 @@
         <v>194</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>189</v>
@@ -5485,7 +5485,7 @@
         <v>1</v>
       </c>
       <c r="S37" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T37" s="10" t="s">
         <v>1</v>
@@ -5511,16 +5511,16 @@
         <v>194</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K38" s="9" t="s">
         <v>243</v>
@@ -5538,7 +5538,7 @@
         <v>84</v>
       </c>
       <c r="P38" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q38" s="10" t="s">
         <v>244</v>
@@ -5547,7 +5547,7 @@
         <v>1</v>
       </c>
       <c r="S38" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T38" s="10" t="s">
         <v>245</v>
@@ -5579,28 +5579,28 @@
         <v>247</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K39" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="L39" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="L39" s="9" t="s">
-        <v>170</v>
-      </c>
       <c r="M39" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="N39" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="N39" s="9" t="s">
-        <v>170</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q39" s="10" t="s">
         <v>248</v>
@@ -5609,7 +5609,7 @@
         <v>220</v>
       </c>
       <c r="S39" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T39" s="10" t="s">
         <v>1</v>
@@ -5635,7 +5635,7 @@
         <v>188</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>79</v>
@@ -5671,7 +5671,7 @@
         <v>220</v>
       </c>
       <c r="S40" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T40" s="10" t="s">
         <v>253</v>
@@ -5697,16 +5697,16 @@
         <v>255</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>189</v>
@@ -5724,7 +5724,7 @@
         <v>84</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="10" t="s">
         <v>256</v>
@@ -5733,7 +5733,7 @@
         <v>257</v>
       </c>
       <c r="S41" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T41" s="10" t="s">
         <v>258</v>
@@ -5759,19 +5759,19 @@
         <v>194</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="L42" s="9" t="s">
         <v>1</v>
@@ -5786,7 +5786,7 @@
         <v>84</v>
       </c>
       <c r="P42" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q42" s="10" t="s">
         <v>260</v>
@@ -5795,7 +5795,7 @@
         <v>1</v>
       </c>
       <c r="S42" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T42" s="10" t="s">
         <v>261</v>
@@ -5824,19 +5824,19 @@
         <v>79</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="K43" s="9" t="s">
         <v>189</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="M43" s="9" t="s">
         <v>1</v>
@@ -5857,7 +5857,7 @@
         <v>220</v>
       </c>
       <c r="S43" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T43" s="10" t="s">
         <v>265</v>
@@ -5910,7 +5910,7 @@
         <v>47</v>
       </c>
       <c r="P44" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q44" s="8" t="s">
         <v>270</v>
@@ -5948,7 +5948,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I45" s="7" t="s">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         <v>1</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q45" s="8" t="s">
         <v>273</v>
@@ -6010,7 +6010,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>1</v>
@@ -6034,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="P46" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q46" s="8" t="s">
         <v>277</v>
@@ -6072,7 +6072,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I47" s="7" t="s">
         <v>1</v>
@@ -6096,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="P47" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q47" s="8" t="s">
         <v>280</v>
@@ -6105,7 +6105,7 @@
         <v>1</v>
       </c>
       <c r="S47" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T47" s="8" t="s">
         <v>1</v>
@@ -6158,7 +6158,7 @@
         <v>1</v>
       </c>
       <c r="P48" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q48" s="8" t="s">
         <v>282</v>
@@ -6167,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T48" s="8" t="s">
         <v>1</v>
@@ -6220,7 +6220,7 @@
         <v>1</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q49" s="8" t="s">
         <v>284</v>
@@ -6229,7 +6229,7 @@
         <v>1</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T49" s="8" t="s">
         <v>1</v>
@@ -6258,7 +6258,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>1</v>
@@ -6282,7 +6282,7 @@
         <v>1</v>
       </c>
       <c r="P50" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q50" s="8" t="s">
         <v>286</v>
@@ -6291,7 +6291,7 @@
         <v>1</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T50" s="8" t="s">
         <v>1</v>
@@ -6320,7 +6320,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I51" s="7" t="s">
         <v>1</v>
@@ -6344,7 +6344,7 @@
         <v>1</v>
       </c>
       <c r="P51" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q51" s="8" t="s">
         <v>288</v>
@@ -6353,7 +6353,7 @@
         <v>1</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T51" s="8" t="s">
         <v>1</v>
@@ -6382,7 +6382,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>1</v>
@@ -6406,7 +6406,7 @@
         <v>1</v>
       </c>
       <c r="P52" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q52" s="8" t="s">
         <v>290</v>
@@ -6415,7 +6415,7 @@
         <v>1</v>
       </c>
       <c r="S52" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T52" s="8" t="s">
         <v>291</v>
@@ -6444,7 +6444,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I53" s="7" t="s">
         <v>1</v>
@@ -6477,7 +6477,7 @@
         <v>295</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T53" s="8" t="s">
         <v>258</v>
@@ -6670,14 +6670,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T56" xr:uid="{BA7CA0F1-626B-48A0-97BB-597D41EB4380}"/>
+  <autoFilter ref="A1:T56" xr:uid="{A5EC2AC1-BCB5-437C-A346-AEDF6AB2CA86}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65353E3D-F3FB-4916-B858-568950D65868}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930AD1B0-9E63-4DE8-BC85-679883A62810}">
   <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6874,7 +6874,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>327</v>
@@ -7079,7 +7079,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>73</v>
@@ -7123,7 +7123,7 @@
         <v>80</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>346</v>
@@ -7164,7 +7164,7 @@
         <v>80</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>175</v>
@@ -7202,7 +7202,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>73</v>
@@ -7243,7 +7243,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>73</v>
@@ -7287,7 +7287,7 @@
         <v>80</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>360</v>
@@ -7325,10 +7325,10 @@
         <v>1</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>363</v>
@@ -7366,7 +7366,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>73</v>
@@ -7407,7 +7407,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>73</v>
@@ -7448,7 +7448,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>73</v>
@@ -7489,10 +7489,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>384</v>
@@ -7530,7 +7530,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>387</v>
@@ -7571,7 +7571,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>392</v>
@@ -7612,7 +7612,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>73</v>
@@ -7653,7 +7653,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>73</v>
@@ -7694,7 +7694,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>73</v>
@@ -7735,7 +7735,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>409</v>
@@ -7776,10 +7776,10 @@
         <v>1</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>413</v>
@@ -7817,7 +7817,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>73</v>
@@ -7858,7 +7858,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>73</v>
@@ -7899,10 +7899,10 @@
         <v>1</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>427</v>
@@ -7940,7 +7940,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>73</v>
@@ -7981,10 +7981,10 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>436</v>
@@ -8025,7 +8025,7 @@
         <v>440</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>441</v>
@@ -8066,7 +8066,7 @@
         <v>80</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>270</v>
@@ -8104,10 +8104,10 @@
         <v>269</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>273</v>
@@ -8145,10 +8145,10 @@
         <v>274</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>444</v>
@@ -8186,10 +8186,10 @@
         <v>274</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>446</v>
@@ -8227,7 +8227,7 @@
         <v>274</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>327</v>
@@ -8268,7 +8268,7 @@
         <v>274</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>327</v>
@@ -8312,7 +8312,7 @@
         <v>80</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>393</v>
@@ -8353,7 +8353,7 @@
         <v>80</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H41" s="8" t="s">
         <v>458</v>
@@ -8394,7 +8394,7 @@
         <v>80</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H42" s="8" t="s">
         <v>461</v>
@@ -8539,14 +8539,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M45" xr:uid="{65353E3D-F3FB-4916-B858-568950D65868}"/>
+  <autoFilter ref="A1:M45" xr:uid="{930AD1B0-9E63-4DE8-BC85-679883A62810}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F41A63-D94E-4F7B-8F3F-F683B7891A87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD572FC2-C59F-4D76-B8FA-F3278C5AA96B}">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8664,7 +8664,7 @@
         <v>499</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>488</v>
@@ -8711,13 +8711,13 @@
         <v>507</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>508</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>509</v>
@@ -8751,14 +8751,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O4" xr:uid="{12F41A63-D94E-4F7B-8F3F-F683B7891A87}"/>
+  <autoFilter ref="A1:O4" xr:uid="{BD572FC2-C59F-4D76-B8FA-F3278C5AA96B}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309047DA-5A38-4E5A-8C49-57889D2B7380}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D829C5-F7B3-4494-8142-438EFD969B52}">
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9174,10 +9174,10 @@
         <v>135</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="J7" s="14" t="s">
         <v>535</v>
@@ -9198,7 +9198,7 @@
         <v>536</v>
       </c>
       <c r="P7" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q7" s="14" t="s">
         <v>537</v>
@@ -9233,10 +9233,10 @@
         <v>526</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>541</v>
@@ -9260,7 +9260,7 @@
         <v>543</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q8" s="14" t="s">
         <v>544</v>
@@ -9298,10 +9298,10 @@
         <v>125</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J9" s="14" t="s">
         <v>547</v>
@@ -9322,7 +9322,7 @@
         <v>548</v>
       </c>
       <c r="P9" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q9" s="14" t="s">
         <v>549</v>
@@ -9357,7 +9357,7 @@
         <v>526</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>80</v>
@@ -9384,7 +9384,7 @@
         <v>553</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q10" s="12" t="s">
         <v>554</v>
@@ -9422,10 +9422,10 @@
         <v>79</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J11" s="12" t="s">
         <v>558</v>
@@ -9508,7 +9508,7 @@
         <v>47</v>
       </c>
       <c r="P12" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q12" s="14" t="s">
         <v>270</v>
@@ -9546,7 +9546,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>1</v>
@@ -9570,7 +9570,7 @@
         <v>1</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q13" s="14" t="s">
         <v>273</v>
@@ -9608,7 +9608,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>1</v>
@@ -9632,7 +9632,7 @@
         <v>1</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q14" s="14" t="s">
         <v>563</v>
@@ -9670,7 +9670,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>1</v>
@@ -9694,7 +9694,7 @@
         <v>1</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q15" s="14" t="s">
         <v>566</v>
@@ -9732,7 +9732,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>1</v>
@@ -9756,7 +9756,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q16" s="14" t="s">
         <v>568</v>
@@ -9818,7 +9818,7 @@
         <v>1</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q17" s="14" t="s">
         <v>572</v>
@@ -10020,14 +10020,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T20" xr:uid="{309047DA-5A38-4E5A-8C49-57889D2B7380}"/>
+  <autoFilter ref="A1:T20" xr:uid="{08D829C5-F7B3-4494-8142-438EFD969B52}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C2960E-3FF7-43AF-B3B4-74CE1E6F29F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EA4FF82-855F-43AB-BB04-F50F8E139CB4}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10317,14 +10317,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12" xr:uid="{12C2960E-3FF7-43AF-B3B4-74CE1E6F29F9}"/>
+  <autoFilter ref="A1:G12" xr:uid="{2EA4FF82-855F-43AB-BB04-F50F8E139CB4}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97CC6593-7EF8-476D-9BF3-5071D1B0DE71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD0B6B0-4500-4DA3-BDDA-44A4E54B231D}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10370,7 +10370,7 @@
         <v>633</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>617</v>
@@ -10393,7 +10393,7 @@
         <v>633</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>635</v>
@@ -10416,7 +10416,7 @@
         <v>633</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>637</v>
@@ -10439,7 +10439,7 @@
         <v>633</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>639</v>
@@ -10462,7 +10462,7 @@
         <v>633</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>641</v>
@@ -10485,7 +10485,7 @@
         <v>633</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>643</v>
@@ -10577,7 +10577,7 @@
         <v>653</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>185</v>
@@ -10600,7 +10600,7 @@
         <v>653</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>655</v>
@@ -10623,7 +10623,7 @@
         <v>653</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>657</v>
@@ -10646,7 +10646,7 @@
         <v>653</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>659</v>
@@ -10669,7 +10669,7 @@
         <v>653</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>661</v>
@@ -10692,7 +10692,7 @@
         <v>653</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>663</v>
@@ -10784,7 +10784,7 @@
         <v>673</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>674</v>
@@ -10807,7 +10807,7 @@
         <v>673</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>676</v>
@@ -10830,7 +10830,7 @@
         <v>673</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>678</v>
@@ -10853,7 +10853,7 @@
         <v>673</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>680</v>
@@ -10876,7 +10876,7 @@
         <v>673</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>682</v>
@@ -10899,7 +10899,7 @@
         <v>673</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>684</v>
@@ -10991,7 +10991,7 @@
         <v>694</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>695</v>
@@ -11014,7 +11014,7 @@
         <v>694</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>698</v>
@@ -11037,7 +11037,7 @@
         <v>694</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>700</v>
@@ -11060,7 +11060,7 @@
         <v>694</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>702</v>
@@ -11083,7 +11083,7 @@
         <v>694</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>704</v>
@@ -11106,7 +11106,7 @@
         <v>694</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>706</v>
@@ -11198,7 +11198,7 @@
         <v>717</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>718</v>
@@ -11221,7 +11221,7 @@
         <v>717</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>720</v>
@@ -11244,7 +11244,7 @@
         <v>717</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>722</v>
@@ -11267,7 +11267,7 @@
         <v>717</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>724</v>
@@ -11290,7 +11290,7 @@
         <v>717</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>726</v>
@@ -11313,7 +11313,7 @@
         <v>717</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>728</v>
@@ -11405,7 +11405,7 @@
         <v>296</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>738</v>
@@ -11428,7 +11428,7 @@
         <v>296</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>740</v>
@@ -11451,7 +11451,7 @@
         <v>296</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>742</v>
@@ -11474,7 +11474,7 @@
         <v>296</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>601</v>
@@ -11497,7 +11497,7 @@
         <v>296</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>745</v>
@@ -11520,7 +11520,7 @@
         <v>296</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>659</v>
@@ -11612,7 +11612,7 @@
         <v>754</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>755</v>
@@ -11635,7 +11635,7 @@
         <v>754</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>758</v>
@@ -11658,7 +11658,7 @@
         <v>754</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>760</v>
@@ -11681,7 +11681,7 @@
         <v>754</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>762</v>
@@ -11704,7 +11704,7 @@
         <v>754</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>764</v>
@@ -11727,7 +11727,7 @@
         <v>754</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>766</v>
@@ -11809,14 +11809,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64" xr:uid="{97CC6593-7EF8-476D-9BF3-5071D1B0DE71}"/>
+  <autoFilter ref="A1:G64" xr:uid="{AAD0B6B0-4500-4DA3-BDDA-44A4E54B231D}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19E418AB-E59F-478B-9258-09E92E136816}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB59CCF0-A813-4F6C-AAE1-885F38E731F5}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11885,7 +11885,7 @@
         <v>47</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>784</v>
@@ -11954,7 +11954,7 @@
         <v>79</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>784</v>
@@ -11974,10 +11974,10 @@
         <v>799</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>784</v>
@@ -12013,7 +12013,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{19E418AB-E59F-478B-9258-09E92E136816}"/>
+  <autoFilter ref="A1:G8" xr:uid="{BB59CCF0-A813-4F6C-AAE1-885F38E731F5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
